--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$N$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,11 @@
           <t>fotos/002_nova_autopartes/streetview_1.jpg; fotos/002_nova_autopartes/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M3" s="3" t="n"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>En la carpeta 002_nova_autopartes, deje un ejemplo de como se tienen que guardar las fotos del street view (ejemplo_foto_street_view)</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -772,7 +776,11 @@
           <t>fotos/004_acumuladores_neza_limited_parque/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M5" s="3" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>La foto tiene que estar mas centrada, deje el ejemplo de foto en la carpeta (004_acumuladores_neza_limited_parque)</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -868,7 +876,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -892,7 +900,11 @@
           <t>fotos/006_venta_de_baterias_para_auto/streetview_1.jpg; fotos/006_venta_de_baterias_para_auto/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M7" s="3" t="n"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Este Id no cumple con las reglas de validacion de que venda baterias</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -946,7 +958,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Street View muestra fachada residencial con vista parcial obstruida. Foto de Maps confirma letrero 'ESPECIALISTAS EN BATERIAS iNO PAGUES MAS!', toldo de 'Miranda Acumuladores', rack con baterias junto a motocicletas, logo LTH, y foto de una bateria individual.</t>
+          <t>Street View muestra fachada residencial con vista parcial obstruida. Foto de Maps confirma letrero 'ESPECIALISTAS EN BATERIAS iNO PAGUES MAS!', toldo de 'Miranda Acumuladores', rack con baterias junto a motocicletas, logo LTH, y foto de una bateria individual. Revision adicional: si existe una captura de Street View (fecha distinta a la primera consultada) que muestra la fachada MIRANDA ESPECIALISTAS EN BATERIAS con cajas de baterias apiladas -- confirma independientemente de la foto de Maps.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -954,7 +966,11 @@
           <t>fotos/007_acumuladores_miranda/streetview_1.jpg; fotos/007_acumuladores_miranda/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M8" s="3" t="n"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>En lla carpeta de este id deje una foto foto_ejemplo</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1143,8 +1159,592 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Baterias "El Güero"</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Av. Bordo de Xochiaca 123, Estado de Mexico, 57210 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>19.4256067</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>-99.0371372</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Street View bloqueado por un arbol y un puesto de comida en primer plano; fachada no visible. No hay fotos adicionales de Maps. Se confirma por resena de cliente: 'No sirven sus baterias' (2 anos) -- confirma que el negocio vende baterias, aunque cuestiona la calidad. Otras resenas ('Economicas y buenas, recomendable al 100') tambien consistentes con venta de baterias.</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>fotos/011_baterias_el_guero/streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Baterías para carro la primera</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Av. Adolfo López Mateos 88, Metropolitana 1ra Secc, 57730 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>19.3941026</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>-99.0325577</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LA PRIMERA</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>LTH, FULL POWER, ACDELCO, GONHER, AMERICA</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Street View original (foto estatica) mostraba un local de 'Carnitas' vecino, sin relacion. Foto de Maps (mar 2024, mejor encuadre) confirma letrero 'ACUMULADORES LA PRIMERA', anaquel con baterias LTH/Full Power/ACDelco/Gonher/America, letrero 'COMPRO CASCOS DE BATERIA' y 'GARANTIA directamente con nosotros'. Resenas tambien confirman ('adquiri una excelente bateria para mi Ford Fiesta', 'checo mi bateria y la cambio').</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>fotos/012_baterias_para_carro_la_primera/streetview_1.jpg; fotos/012_baterias_para_carro_la_primera/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ROBERTO</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Av. Pantitlán 593, Gral Vicente Villada, 57710 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>19.3881719</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-99.00434869999999</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ROBERTO</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Letrero 'ACUMULADORES ROBERTO' visible en el borde derecho de la foto, logo LTH, anaquel con productos visible a traves del aparador.</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>fotos/013_acumuladores_roberto/streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA DE REFACCIONES EDA</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Julián de Los Reyes 3, Juan Escutia, Iztapalapa, 09100 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>19.3974297</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-99.0563259</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA DE REFACCIONES EDA</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Mural grande de LTH pintado directamente en la fachada del edificio, junto al letrero 'EDA Distribuidora de Refacciones'. No se aprecia mostrador desde la calle pero la evidencia de marca es contundente.</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>fotos/014_distribuidora_de_refacciones_eda/streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO AUTORIZADO GONHER</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Autopartes Protone, Benito Juárez, 57000 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>19.4004742</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>-99.00321169999999</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO GONHER / NOVA AUTOPARTES</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>GONHER</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Esta es la MISMA ubicacion fisica que CASE ID 2 (Nova Autopartes) -- Google Maps tiene dos fichas separadas para el mismo local. Letrero 'CENTRO DE SERVICIO GONHER' y 'NOVA AUTOPARTES', anaquel con productos visible.</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>fotos/015_centro_de_servicio_autorizado_gonher/streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "GALECH"</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Av. Texcoco 398, Metropolitana 3ra Secc, 57750 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>19.3854851</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-99.0240204</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GALECH / Electronica Automotriz</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>LTH, GONHER, AMERICA, XTREME</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Street View original mostraba principalmente el letrero de 'Electronica Automotriz' (diagnostico, afinaciones) con un logo LTH pequeno y parcial. Fotos de Maps (propietario, ago 2025) confirman anaquel completo de baterias con marcas LTH, Gonher, America, Xtreme.</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>fotos/016_acumuladores_galech/streetview_1.jpg; fotos/016_acumuladores_galech/maps_foto_1.jpg; fotos/016_acumuladores_galech/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES OSO</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Av. Pantitlán 766, Reforma, 57849 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>19.3772501</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>-98.98116709999999</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES OSO</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>GONHER, TBS</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Mural grande 'GONHER', letrero 'GONHER DISTRIBUIDOR', logo 'TBS - Total Battery Solutions', letrero 'BATERIAS', anaqueles a ambos lados de la entrada visiblemente llenos de baterias.</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>fotos/017_acumuladores_oso/streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>BATTERY CLUB DURACELL</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Av. Texcoco 60, Metropolitana 1ra Secc, 57730 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>19.392061</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>-99.0385402</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS PARA AUTO ...DURACELL (parcialmente cubierto por grafiti)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>DURACELL (probable, parcialmente ilegible)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra un letrero 'BATERIAS PARA AUTO' con texto adicional parcialmente cubierto por grafiti que podria decir 'DURACELL', cortina metalica cerrada con grafiti extenso (aspecto de abandono). Google Maps marca el negocio como 'Cerrado temporalmente'. PREGUNTA ABIERTA PARA EL EQUIPO: como clasificar negocios con evidencia de fachada pero marcados 'Cerrado temporalmente' -- se dejo en PENDIENTE en vez de asumir SI o NO.</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>fotos/018_battery_club_duracell/streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Venta De Baterías De Carros</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Av. Pantitlán 15, Evolucion, 57700 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>19.3991633</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-99.0260605</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra una gasolinera y una agencia de motocicletas en esa esquina, sin relacion aparente con venta de baterias -- posible que el local haya cambiado de giro. Resenas SI confirman venta de baterias en el pasado ('tienen un poco elevados los precios de sus baterias', 'muy buen servicio y precio'). Google Maps marca el negocio como 'Cerrado temporalmente'. Mismo caso abierto que CASE ID 18: evidencia historica de venta de baterias pero negocio actualmente cerrado.</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>fotos/019_venta_de_baterias_de_carros/streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>FRANQUICIA DURACELL "NEZA"</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Av. Pantitlán 153, Mexico 2da Secc, 57620 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>19.4051119</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-99.0411563</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra 'TECATE Mini Super Hawai', una tienda de instrumentos musicales y el bar 'MIKEL'S' en ese domicilio -- ninguna relacion con baterias, sugiere que el local cambio de giro/ocupante. Unica resena (hace 8 anos) es generica, no menciona baterias. Google Maps marca el negocio como 'Cerrado temporalmente'. De los 3 'Cerrado temporalmente' de este lote, este es el que tiene MENOS evidencia de haber sido realmente una tienda de baterias en ese domicilio.</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>fotos/020_franquicia_duracell_neza/streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N11"/>
+  <autoFilter ref="A1:N21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -1156,6 +1756,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$O$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -455,8 +455,9 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,10 +523,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>FOTO PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FECHA VALIDACION</t>
         </is>
@@ -586,8 +592,13 @@
           <t>fotos/001_acumuladores_neza_limited/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -648,12 +659,17 @@
           <t>fotos/002_nova_autopartes/streetview_1.jpg; fotos/002_nova_autopartes/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ejemplo_foto_street_view.png</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>En la carpeta 002_nova_autopartes, deje un ejemplo de como se tienen que guardar las fotos del street view (ejemplo_foto_street_view)</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -714,8 +730,13 @@
           <t>fotos/003_raly_acumuladores/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -776,12 +797,17 @@
           <t>fotos/004_acumuladores_neza_limited_parque/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>ejemplo_foto_final.png</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>La foto tiene que estar mas centrada, deje el ejemplo de foto en la carpeta (004_acumuladores_neza_limited_parque)</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -842,8 +868,13 @@
           <t>fotos/005_energycentro/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -900,12 +931,17 @@
           <t>fotos/006_venta_de_baterias_para_auto/streetview_1.jpg; fotos/006_venta_de_baterias_para_auto/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Este Id no cumple con las reglas de validacion de que venda baterias</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -966,12 +1002,17 @@
           <t>fotos/007_acumuladores_miranda/streetview_1.jpg; fotos/007_acumuladores_miranda/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>foto_ejemplo.png</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>En lla carpeta de este id deje una foto foto_ejemplo</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1032,8 +1073,13 @@
           <t>fotos/008_acumuladores_miranda/streetview_1.jpg; fotos/008_acumuladores_miranda/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1090,8 +1136,13 @@
           <t>fotos/009_acumuladores_nezahualcoyotl/streetview_1.jpg; fotos/009_acumuladores_nezahualcoyotl/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1152,8 +1203,13 @@
           <t>fotos/010_baterias_para_autos_samar/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1202,8 +1258,13 @@
           <t>fotos/011_baterias_el_guero/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1264,8 +1325,13 @@
           <t>fotos/012_baterias_para_carro_la_primera/streetview_1.jpg; fotos/012_baterias_para_carro_la_primera/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1308,7 +1374,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>LTH, POWER CONNECTION, FULL POWER</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1318,16 +1384,21 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Letrero 'ACUMULADORES ROBERTO' visible en el borde derecho de la foto, logo LTH, anaquel con productos visible a traves del aparador.</t>
+          <t>Letrero 'ACUMULADORES ROBERTO' visible en el borde derecho de la foto, logo LTH, anaquel con productos visible a traves del aparador. Foto adicional de Maps (cortesia del negocio) muestra de cerca baterias POWER CONNECTION y FULL POWER en anaquel -- mejor evidencia de producto que la fachada (parcialmente cortada en Street View).</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>fotos/013_acumuladores_roberto/streetview_1.jpg</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="2" t="inlineStr">
+          <t>fotos/013_acumuladores_roberto/streetview_1.jpg; fotos/013_acumuladores_roberto/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1388,8 +1459,13 @@
           <t>fotos/014_distribuidora_de_refacciones_eda/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1450,8 +1526,13 @@
           <t>fotos/015_centro_de_servicio_autorizado_gonher/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1494,7 +1575,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>LTH, GONHER, AMERICA, XTREME</t>
+          <t>LTH, CA-LE, GONHER, AMERICA, XTREME, FULL POWER</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1504,7 +1585,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Street View original mostraba principalmente el letrero de 'Electronica Automotriz' (diagnostico, afinaciones) con un logo LTH pequeno y parcial. Fotos de Maps (propietario, ago 2025) confirman anaquel completo de baterias con marcas LTH, Gonher, America, Xtreme.</t>
+          <t>Street View original mostraba principalmente el letrero de 'Electronica Automotriz' (diagnostico, afinaciones) con un logo LTH pequeno y parcial. Fotos de Maps (propietario, ago 2025) confirman anaquel completo de baterias con marcas LTH, Gonher, America, Xtreme. Foto adicional (maps_foto_1) confirma letrero explicito: VENTA DE BATERIAS NUEVAS Y USADAS CON GARANTIA, logos LTH y CA-LE.</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1512,8 +1593,13 @@
           <t>fotos/016_acumuladores_galech/streetview_1.jpg; fotos/016_acumuladores_galech/maps_foto_1.jpg; fotos/016_acumuladores_galech/maps_foto_2.jpg</t>
         </is>
       </c>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1574,8 +1660,13 @@
           <t>fotos/017_acumuladores_oso/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1636,8 +1727,13 @@
           <t>fotos/018_battery_club_duracell/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1686,8 +1782,13 @@
           <t>fotos/019_venta_de_baterias_de_carros/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1736,15 +1837,20 @@
           <t>fotos/020_franquicia_duracell_neza/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N21"/>
+  <autoFilter ref="A1:O21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$O$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$P$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -453,11 +453,12 @@
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,25 +514,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>BATERIAS VISIBLES EN FOTOS MAPS</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>EVIDENCIA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FOTOS ARCHIVO</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>FOTO PRINCIPAL</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FECHA VALIDACION</t>
         </is>
@@ -584,21 +590,26 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
+          <t>Anaquel visible en la fachada con baterias apiladas (colores variados), junto a mostrador de motocicletas.</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
           <t>Fachada con letrero 'ACUMULADORES NEZA LIMITED' y 'COMPRAMOS BATERIAS USADAS'; logos LTH/America Racing/Optima; anaquel con baterias apiladas visible a la izquierda del local.</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>fotos/001_acumuladores_neza_limited/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>streetview_1.jpg</t>
         </is>
       </c>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -651,25 +662,30 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>Anaquel con baterias apiladas bajo el letrero GONHER, junto a la entrada del local.</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>Street View bloqueado por arboles. Foto del propietario en Maps muestra letrero 'CENTRO DE SERVICIO BATERIAS GONHER', toldo/banner GONHER, logo 'Pro One' (franquicia de refaccionaria, no es marca de bateria), y anaquel con baterias visible.</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>fotos/002_nova_autopartes/streetview_1.jpg; fotos/002_nova_autopartes/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>ejemplo_foto_street_view.png</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>En la carpeta 002_nova_autopartes, deje un ejemplo de como se tienen que guardar las fotos del street view (ejemplo_foto_street_view)</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -722,21 +738,26 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>Mostrador de tienda con productos diversos visibles; no se distinguen baterias individuales con claridad en la foto disponible.</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>Letrero 'Raly Acumuladores' y 'Pro One' (franquicia). Torre publicitaria grande con logos LTH/America Racing/Full Power/Gonher. Mostrador de tienda visible con productos.</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>fotos/003_raly_acumuladores/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>streetview_1.jpg</t>
         </is>
       </c>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -789,25 +810,30 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>Exhibidor/gabinete con bateria LTH junto a la entrada del local.</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>Letrero coincide 'Acumuladores Neza Limited'. Logos LTH y America en fachada, pequeno aparador con productos visible.</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>fotos/004_acumuladores_neza_limited_parque/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>ejemplo_foto_final.png</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>La foto tiene que estar mas centrada, deje el ejemplo de foto en la carpeta (004_acumuladores_neza_limited_parque)</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -860,21 +886,26 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
+          <t>No se distinguen baterias individuales en la foto disponible (cortina de seguridad cerrada).</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
           <t>Letrero 'ENERGYCENTRO' con logos LTH y America Racing, rotulo adicional (parcialmente cubierto por publicidad) que menciona 'BATERIAS'. No se aprecia mostrador interior desde la fachada (cortina de seguridad cerrada).</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>fotos/005_energycentro/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>streetview_1.jpg</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -923,25 +954,30 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
+          <t>No se aprecian baterias en las fotos disponibles (fachada de taller de cerrajeria/reparacion de puertas).</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
           <t>Street View y foto de Maps muestran un taller de cerrajeria/reparacion de puertas corredizas, chapas y elevadores; el interior es un taller de herramientas. Se observa un aparato que podria ser un cargador de bateria y un objeto rojo que podria ser una bateria aislada, pero no hay anuncio ni mostrador claro de venta de baterias. Requiere confirmacion adicional (revisar resenas o visita).</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>fotos/006_venta_de_baterias_para_auto/streetview_1.jpg; fotos/006_venta_de_baterias_para_auto/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>streetview_1.jpg</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Este Id no cumple con las reglas de validacion de que venda baterias</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -994,25 +1030,30 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
+          <t>Rack con baterias apiladas visible bajo el toldo del negocio, junto a las motocicletas estacionadas.</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
           <t>Street View muestra fachada residencial con vista parcial obstruida. Foto de Maps confirma letrero 'ESPECIALISTAS EN BATERIAS iNO PAGUES MAS!', toldo de 'Miranda Acumuladores', rack con baterias junto a motocicletas, logo LTH, y foto de una bateria individual. Revision adicional: si existe una captura de Street View (fecha distinta a la primera consultada) que muestra la fachada MIRANDA ESPECIALISTAS EN BATERIAS con cajas de baterias apiladas -- confirma independientemente de la foto de Maps.</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>fotos/007_acumuladores_miranda/streetview_1.jpg; fotos/007_acumuladores_miranda/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>foto_ejemplo.png</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>En lla carpeta de este id deje una foto foto_ejemplo</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1065,21 +1106,26 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
+          <t>Anaquel completo cubierto de baterias apiladas en varias filas, con banner LTH anunciando 'nueva linea de baterias'.</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
           <t>Street View bloqueado por un camion de carga. Foto de Maps (segunda sucursal) muestra gran cantidad de baterias apiladas en anaqueles bajo banner 'LTH - la nueva linea de baterias', rotulo 'Acumuladores Miranda'.</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>fotos/008_acumuladores_miranda/streetview_1.jpg; fotos/008_acumuladores_miranda/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1128,21 +1174,26 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
+          <t>Anaquel interior con baterias apiladas (cajas rojas y negras) visible junto al letrero BATERIAS.</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>Street View muestra cortina de seguridad cerrada sin letrero visible. Foto de Maps muestra letrero azul 'BATERIAS' y 'RAPIDA Y LENTA' (servicio de carga), anaquel interior con baterias apiladas (rojas y negras). Marca no legible con claridad en la foto.</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>fotos/009_acumuladores_nezahualcoyotl/streetview_1.jpg; fotos/009_acumuladores_nezahualcoyotl/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1195,21 +1246,26 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t>No se aprecian baterias fisicas en la foto (cortina cerrada); solo la ilustracion de una bateria pintada en el letrero.</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
           <t>Letrero 'SAMAR' con ilustracion de bateria, banner 'DURACELL BATERIAS PARA AUTO', logos LTH y OPTIMA en cortina de seguridad. Cortina cerrada, no se aprecia mostrador interior.</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>fotos/010_baterias_para_autos_samar/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>streetview_2.jpg</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1250,21 +1306,26 @@
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
+          <t>No hay foto que muestre baterias; la fachada esta bloqueada por un arbol y un puesto de comida.</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
           <t>Street View bloqueado por un arbol y un puesto de comida en primer plano; fachada no visible. No hay fotos adicionales de Maps. Se confirma por resena de cliente: 'No sirven sus baterias' (2 anos) -- confirma que el negocio vende baterias, aunque cuestiona la calidad. Otras resenas ('Economicas y buenas, recomendable al 100') tambien consistentes con venta de baterias.</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>fotos/011_baterias_el_guero/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>streetview_2.jpg</t>
         </is>
       </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1317,21 +1378,26 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
+          <t>Aparador y anaqueles con multiples baterias apiladas (cajas visibles de varias marcas), mas un exhibidor exterior con productos de bateria.</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
           <t>Street View original (foto estatica) mostraba un local de 'Carnitas' vecino, sin relacion. Foto de Maps (mar 2024, mejor encuadre) confirma letrero 'ACUMULADORES LA PRIMERA', anaquel con baterias LTH/Full Power/ACDelco/Gonher/America, letrero 'COMPRO CASCOS DE BATERIA' y 'GARANTIA directamente con nosotros'. Resenas tambien confirman ('adquiri una excelente bateria para mi Ford Fiesta', 'checo mi bateria y la cambio').</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>fotos/012_baterias_para_carro_la_primera/streetview_1.jpg; fotos/012_baterias_para_carro_la_primera/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1384,21 +1450,26 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
+          <t>Foto de cerca muestra 2 baterias en anaquel, una roja y una amarilla, con etiquetas de marca legibles.</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
           <t>Letrero 'ACUMULADORES ROBERTO' visible en el borde derecho de la foto, logo LTH, anaquel con productos visible a traves del aparador. Foto adicional de Maps (cortesia del negocio) muestra de cerca baterias POWER CONNECTION y FULL POWER en anaquel -- mejor evidencia de producto que la fachada (parcialmente cortada en Street View).</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>fotos/013_acumuladores_roberto/streetview_1.jpg; fotos/013_acumuladores_roberto/maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1451,21 +1522,26 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
+          <t>Mural pintado con ilustracion de bateria de gran tamano (no es foto de producto real).</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
           <t>Mural grande de LTH pintado directamente en la fachada del edificio, junto al letrero 'EDA Distribuidora de Refacciones'. No se aprecia mostrador desde la calle pero la evidencia de marca es contundente.</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>fotos/014_distribuidora_de_refacciones_eda/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>streetview_1.jpg</t>
         </is>
       </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1518,21 +1594,26 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
+          <t>Pequeno anaquel con baterias apiladas visible bajo el letrero de AUTOPARTES, junto a la entrada.</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
           <t>Esta es la MISMA ubicacion fisica que CASE ID 2 (Nova Autopartes) -- Google Maps tiene dos fichas separadas para el mismo local. Letrero 'CENTRO DE SERVICIO GONHER' y 'NOVA AUTOPARTES', anaquel con productos visible.</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>fotos/015_centro_de_servicio_autorizado_gonher/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>streetview_1.jpg</t>
         </is>
       </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1585,21 +1666,26 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>Anaquel completo con baterias apiladas en varias filas, con logos de multiples marcas legibles en las cajas.</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>Street View original mostraba principalmente el letrero de 'Electronica Automotriz' (diagnostico, afinaciones) con un logo LTH pequeno y parcial. Fotos de Maps (propietario, ago 2025) confirman anaquel completo de baterias con marcas LTH, Gonher, America, Xtreme. Foto adicional (maps_foto_1) confirma letrero explicito: VENTA DE BATERIAS NUEVAS Y USADAS CON GARANTIA, logos LTH y CA-LE.</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>fotos/016_acumuladores_galech/streetview_1.jpg; fotos/016_acumuladores_galech/maps_foto_1.jpg; fotos/016_acumuladores_galech/maps_foto_2.jpg</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>maps_foto_1.jpg</t>
         </is>
       </c>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1652,21 +1738,26 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
+          <t>Anaqueles a ambos lados de la entrada, completamente llenos de baterias apiladas y visibles desde la calle.</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
           <t>Mural grande 'GONHER', letrero 'GONHER DISTRIBUIDOR', logo 'TBS - Total Battery Solutions', letrero 'BATERIAS', anaqueles a ambos lados de la entrada visiblemente llenos de baterias.</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>fotos/017_acumuladores_oso/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>streetview_1.jpg</t>
         </is>
       </c>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1719,21 +1810,30 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Street View muestra un letrero 'BATERIAS PARA AUTO' con texto adicional parcialmente cubierto por grafiti que podria decir 'DURACELL', cortina metalica cerrada con grafiti extenso (aspecto de abandono). Google Maps marca el negocio como 'Cerrado temporalmente'. PREGUNTA ABIERTA PARA EL EQUIPO: como clasificar negocios con evidencia de fachada pero marcados 'Cerrado temporalmente' -- se dejo en PENDIENTE en vez de asumir SI o NO.</t>
+          <t>No se aprecian baterias fisicas en la foto disponible; solo el letrero, parcialmente cubierto por grafiti.</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
+          <t>Street View muestra un letrero 'BATERIAS PARA AUTO' con texto adicional parcialmente cubierto por grafiti que podria decir 'DURACELL', cortina metalica cerrada con grafiti extenso (aspecto de abandono). Google Maps marca el negocio como 'Cerrado temporalmente'. PREGUNTA ABIERTA PARA EL EQUIPO: como clasificar negocios con evidencia de fachada pero marcados 'Cerrado temporalmente' -- se dejo en PENDIENTE en vez de asumir SI o NO. Confirmado con Ricardo: se deja en PENDIENTE para revision en conjunto con el equipo (la foto disponible no da suficiente evidencia).</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
           <t>fotos/018_battery_club_duracell/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>streetview_2.jpg</t>
         </is>
       </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En estos casos, como no ayuda mucho la foto se va a revision con el equipo para tomar una decision en conjunto </t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1766,7 +1866,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H20" s="2" t="n"/>
@@ -1774,21 +1874,30 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Street View muestra una gasolinera y una agencia de motocicletas en esa esquina, sin relacion aparente con venta de baterias -- posible que el local haya cambiado de giro. Resenas SI confirman venta de baterias en el pasado ('tienen un poco elevados los precios de sus baterias', 'muy buen servicio y precio'). Google Maps marca el negocio como 'Cerrado temporalmente'. Mismo caso abierto que CASE ID 18: evidencia historica de venta de baterias pero negocio actualmente cerrado.</t>
+          <t>No se aprecian baterias en la foto disponible (el domicilio actual muestra una gasolinera y una agencia de motocicletas).</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
+          <t>Street View muestra una gasolinera y una agencia de motocicletas en esa esquina, sin relacion aparente con venta de baterias -- posible que el local haya cambiado de giro. Resenas SI confirman venta de baterias en el pasado ('tienen un poco elevados los precios de sus baterias', 'muy buen servicio y precio'). Google Maps marca el negocio como 'Cerrado temporalmente'. Mismo caso abierto que CASE ID 18: evidencia historica de venta de baterias pero negocio actualmente cerrado. Aprobado por Ricardo: cumple los requisitos del equipo (resenas confirman venta de baterias) aunque Maps lo marque Cerrado temporalmente -- ese estatus por si solo NO descalifica un negocio.</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
           <t>fotos/019_venta_de_baterias_de_carros/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>streetview_2.jpg</t>
         </is>
       </c>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esta apruebala, tiene los requerimentos que solicita el equipo aunque en maps diga cerrado temporarmente </t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -1829,28 +1938,37 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Street View muestra 'TECATE Mini Super Hawai', una tienda de instrumentos musicales y el bar 'MIKEL'S' en ese domicilio -- ninguna relacion con baterias, sugiere que el local cambio de giro/ocupante. Unica resena (hace 8 anos) es generica, no menciona baterias. Google Maps marca el negocio como 'Cerrado temporalmente'. De los 3 'Cerrado temporalmente' de este lote, este es el que tiene MENOS evidencia de haber sido realmente una tienda de baterias en ese domicilio.</t>
+          <t>No se aprecian baterias en la foto disponible (el domicilio actual tiene otros negocios sin relacion).</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
+          <t>Street View muestra 'TECATE Mini Super Hawai', una tienda de instrumentos musicales y el bar 'MIKEL'S' en ese domicilio -- ninguna relacion con baterias, sugiere que el local cambio de giro/ocupante. Unica resena (hace 8 anos) es generica, no menciona baterias. Google Maps marca el negocio como 'Cerrado temporalmente'. De los 3 'Cerrado temporalmente' de este lote, este es el que tiene MENOS evidencia de haber sido realmente una tienda de baterias en ese domicilio. Ricardo senala que en la esquina de enfrente hay otro negocio que vende baterias. Se investigo: "Acumuladores LEO" (Av. Pantitlan 155, ~30m de distancia, https://www.google.com/maps/place/Acumuladores+LEO/@19.4049156,-99.0408877) tiene fotos claras de anaquel con baterias LTH y letrero "ACUMULADORES LEO", inauguracion tipo carpa en mayo 2025 -- posible que sea el mismo negocio reubicado/renombrado, o un negocio nuevo no listado en la base. Se deja en PENDIENTE para revision del equipo; se sugiere agregar Acumuladores LEO como candidato nuevo si no esta ya en la base.</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
           <t>fotos/020_franquicia_duracell_neza/streetview_1.jpg</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>streetview_2.jpg</t>
         </is>
       </c>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>Esta queda en revision en con el equipo, porque parece ser que cambiaron de ubicación. En contra esquina aparece otro negocio que se ve que vende baterias.</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
+  <autoFilter ref="A1:P21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Street View muestra un letrero 'BATERIAS PARA AUTO' con texto adicional parcialmente cubierto por grafiti que podria decir 'DURACELL', cortina metalica cerrada con grafiti extenso (aspecto de abandono). Google Maps marca el negocio como 'Cerrado temporalmente'. PREGUNTA ABIERTA PARA EL EQUIPO: como clasificar negocios con evidencia de fachada pero marcados 'Cerrado temporalmente' -- se dejo en PENDIENTE en vez de asumir SI o NO. Confirmado con Ricardo: se deja en PENDIENTE para revision en conjunto con el equipo (la foto disponible no da suficiente evidencia).</t>
+          <t>Street View muestra un letrero 'BATERIAS PARA AUTO' con texto adicional parcialmente cubierto por grafiti que podria decir 'DURACELL', cortina metalica cerrada con grafiti extenso (aspecto de abandono). Google Maps marca el negocio como 'Cerrado temporalmente'. PREGUNTA ABIERTA PARA EL EQUIPO: como clasificar negocios con evidencia de fachada pero marcados 'Cerrado temporalmente' -- se dejo en PENDIENTE en vez de asumir SI o NO. Confirmado con Ricardo: se deja en PENDIENTE para revision en conjunto con el equipo (la foto disponible no da suficiente evidencia). Decision final de Ricardo: SI, se alcanza a apreciar la marca de bateria en el letrero pese al grafiti.</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">En estos casos, como no ayuda mucho la foto se va a revision con el equipo para tomar una decision en conjunto </t>
+          <t>En este caso si se aprueba porque se alcanza a apreciar la marca de bateria</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H21" s="2" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Street View muestra 'TECATE Mini Super Hawai', una tienda de instrumentos musicales y el bar 'MIKEL'S' en ese domicilio -- ninguna relacion con baterias, sugiere que el local cambio de giro/ocupante. Unica resena (hace 8 anos) es generica, no menciona baterias. Google Maps marca el negocio como 'Cerrado temporalmente'. De los 3 'Cerrado temporalmente' de este lote, este es el que tiene MENOS evidencia de haber sido realmente una tienda de baterias en ese domicilio. Ricardo senala que en la esquina de enfrente hay otro negocio que vende baterias. Se investigo: "Acumuladores LEO" (Av. Pantitlan 155, ~30m de distancia, https://www.google.com/maps/place/Acumuladores+LEO/@19.4049156,-99.0408877) tiene fotos claras de anaquel con baterias LTH y letrero "ACUMULADORES LEO", inauguracion tipo carpa en mayo 2025 -- posible que sea el mismo negocio reubicado/renombrado, o un negocio nuevo no listado en la base. Se deja en PENDIENTE para revision del equipo; se sugiere agregar Acumuladores LEO como candidato nuevo si no esta ya en la base.</t>
+          <t>Street View muestra 'TECATE Mini Super Hawai', una tienda de instrumentos musicales y el bar 'MIKEL'S' en ese domicilio -- ninguna relacion con baterias, sugiere que el local cambio de giro/ocupante. Unica resena (hace 8 anos) es generica, no menciona baterias. Google Maps marca el negocio como 'Cerrado temporalmente'. De los 3 'Cerrado temporalmente' de este lote, este es el que tiene MENOS evidencia de haber sido realmente una tienda de baterias en ese domicilio. Ricardo senala que en la esquina de enfrente hay otro negocio que vende baterias. Se investigo: "Acumuladores LEO" (Av. Pantitlan 155, ~30m de distancia, https://www.google.com/maps/place/Acumuladores+LEO/@19.4049156,-99.0408877) tiene fotos claras de anaquel con baterias LTH y letrero "ACUMULADORES LEO", inauguracion tipo carpa en mayo 2025 -- posible que sea el mismo negocio reubicado/renombrado, o un negocio nuevo no listado en la base. Se deja en PENDIENTE para revision del equipo; se sugiere agregar Acumuladores LEO como candidato nuevo si no esta ya en la base. Decision final de Ricardo: NO. Regla aplicada: si el Street View en el pin exacto no muestra el nombre del negocio registrado, se clasifica NO aunque haya otros negocios de baterias cerca -- el pin podria estar mal, y no se debe acreditar evidencia de un negocio distinto (ej. Acumuladores LEO) a esta ficha.</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Esta queda en revision en con el equipo, porque parece ser que cambiaron de ubicación. En contra esquina aparece otro negocio que se ve que vende baterias.</t>
+          <t>Esta no porque en el street view no se aprecia ese nombre del negocio, hay negocios cerca pero mientras no cumpla con el nombre, que el el pin en maps este mal, se clasifica como NO</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>LTH, AMERICA</t>
+          <t>LTH, AMERICA, ACDELCO, HELLA</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -886,22 +886,22 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>No se distinguen baterias individuales en la foto disponible (cortina de seguridad cerrada).</t>
+          <t>Foto adicional de Maps muestra letrero ENERGYCENTRO con icono de bateria dibujado, y cajas/logos de America Racing, ACDelco y Hella en la fachada.</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Letrero 'ENERGYCENTRO' con logos LTH y America Racing, rotulo adicional (parcialmente cubierto por publicidad) que menciona 'BATERIAS'. No se aprecia mostrador interior desde la fachada (cortina de seguridad cerrada).</t>
+          <t>Letrero 'ENERGYCENTRO' con logos LTH y America Racing, rotulo adicional (parcialmente cubierto por publicidad) que menciona 'BATERIAS'. No se aprecia mostrador interior desde la fachada (cortina de seguridad cerrada). Foto adicional de Maps (propietario) confirma icono de bateria y logos ACDelco/Hella/America en la fachada -- mejor evidencia visual que solo el letrero.</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>fotos/005_energycentro/streetview_1.jpg</t>
+          <t>fotos/005_energycentro/streetview_1.jpg; fotos/005_energycentro/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>streetview_1.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O6" s="3" t="n"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>DURACELL, LTH, OPTIMA</t>
+          <t>DURACELL, LTH, OPTIMA, FULL POWER</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1246,22 +1246,22 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterias fisicas en la foto (cortina cerrada); solo la ilustracion de una bateria pintada en el letrero.</t>
+          <t>Foto adicional de Maps (dic 2021, cortina abierta) muestra el local en operacion: letrero SAMAR MAYOREO Y MENUDEO DE ACUMULADORES, DURACELL BATERIAS PARA AUTO, cajas de FULL POWER apiladas afuera, y anaquel con producto visible adentro.</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Letrero 'SAMAR' con ilustracion de bateria, banner 'DURACELL BATERIAS PARA AUTO', logos LTH y OPTIMA en cortina de seguridad. Cortina cerrada, no se aprecia mostrador interior.</t>
+          <t>Letrero 'SAMAR' con ilustracion de bateria, banner 'DURACELL BATERIAS PARA AUTO', logos LTH y OPTIMA en cortina de seguridad. Cortina cerrada, no se aprecia mostrador interior. Foto adicional de Maps (dic 2021) muestra el local con cortina abierta y producto real visible (FULL POWER apilado, anaquel interior) -- mejor evidencia que la foto con cortina cerrada.</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>fotos/010_baterias_para_autos_samar/streetview_1.jpg</t>
+          <t>fotos/010_baterias_para_autos_samar/streetview_1.jpg; fotos/010_baterias_para_autos_samar/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>streetview_2.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O11" s="3" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Street View bloqueado por un arbol y un puesto de comida en primer plano; fachada no visible. No hay fotos adicionales de Maps. Se confirma por resena de cliente: 'No sirven sus baterias' (2 anos) -- confirma que el negocio vende baterias, aunque cuestiona la calidad. Otras resenas ('Economicas y buenas, recomendable al 100') tambien consistentes con venta de baterias.</t>
+          <t>Street View bloqueado por un arbol y un puesto de comida en primer plano; fachada no visible. No hay fotos adicionales de Maps. Se confirma por resena de cliente: 'No sirven sus baterias' (2 anos) -- confirma que el negocio vende baterias, aunque cuestiona la calidad. Otras resenas ('Economicas y buenas, recomendable al 100') tambien consistentes con venta de baterias. LIMITACION: no existe ninguna foto (ni Street View ni de Maps) que muestre baterias o la fachada con claridad para este negocio -- solo hay 1 foto de Street View bloqueada. El veredicto SI se sostiene unicamente en la resena de texto ("No sirven sus baterias"), sin respaldo fotografico. Senalado para que el equipo lo confirme si lo considera insuficiente.</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Anaquel completo con baterias apiladas en varias filas, con logos de multiples marcas legibles en las cajas.</t>
+          <t>Foto de Maps (maps_foto_2) muestra un anaquel completo con decenas de baterias de multiples marcas claramente legibles: LTH, GONHER, AMERICA RACING, XTREME, WESTERN, TOTAL.</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_1.jpg</t>
+          <t>maps_foto_2.jpg</t>
         </is>
       </c>
       <c r="O17" s="3" t="n"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Street View muestra un letrero 'BATERIAS PARA AUTO' con texto adicional parcialmente cubierto por grafiti que podria decir 'DURACELL', cortina metalica cerrada con grafiti extenso (aspecto de abandono). Google Maps marca el negocio como 'Cerrado temporalmente'. PREGUNTA ABIERTA PARA EL EQUIPO: como clasificar negocios con evidencia de fachada pero marcados 'Cerrado temporalmente' -- se dejo en PENDIENTE en vez de asumir SI o NO. Confirmado con Ricardo: se deja en PENDIENTE para revision en conjunto con el equipo (la foto disponible no da suficiente evidencia). Decision final de Ricardo: SI, se alcanza a apreciar la marca de bateria en el letrero pese al grafiti.</t>
+          <t>Street View muestra un letrero 'BATERIAS PARA AUTO' con texto adicional parcialmente cubierto por grafiti que podria decir 'DURACELL', cortina metalica cerrada con grafiti extenso (aspecto de abandono). Google Maps marca el negocio como 'Cerrado temporalmente'. PREGUNTA ABIERTA PARA EL EQUIPO: como clasificar negocios con evidencia de fachada pero marcados 'Cerrado temporalmente' -- se dejo en PENDIENTE en vez de asumir SI o NO. Confirmado con Ricardo: se deja en PENDIENTE para revision en conjunto con el equipo (la foto disponible no da suficiente evidencia). Decision final de Ricardo: SI, se alcanza a apreciar la marca de bateria en el letrero pese al grafiti. LIMITACION: no hay mas fotos disponibles en Maps para este negocio (solo 1 foto de Street View, la misma ya usada) -- no se pudo conseguir una foto mejor que muestre el producto con mas claridad.</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1870,26 +1870,30 @@
         </is>
       </c>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>LTH, AMERICA</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterias en la foto disponible (el domicilio actual muestra una gasolinera y una agencia de motocicletas).</t>
+          <t>Foto de Maps (propietario) muestra un anaquel con baterias LTH y America claramente visibles, mural grande de LTH, y banner Centro de Ventas LTH -- prueba visual clara de venta de baterias.</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Street View muestra una gasolinera y una agencia de motocicletas en esa esquina, sin relacion aparente con venta de baterias -- posible que el local haya cambiado de giro. Resenas SI confirman venta de baterias en el pasado ('tienen un poco elevados los precios de sus baterias', 'muy buen servicio y precio'). Google Maps marca el negocio como 'Cerrado temporalmente'. Mismo caso abierto que CASE ID 18: evidencia historica de venta de baterias pero negocio actualmente cerrado. Aprobado por Ricardo: cumple los requisitos del equipo (resenas confirman venta de baterias) aunque Maps lo marque Cerrado temporalmente -- ese estatus por si solo NO descalifica un negocio.</t>
+          <t>Street View muestra una gasolinera y una agencia de motocicletas en esa esquina, sin relacion aparente con venta de baterias -- posible que el local haya cambiado de giro. Resenas SI confirman venta de baterias en el pasado ('tienen un poco elevados los precios de sus baterias', 'muy buen servicio y precio'). Google Maps marca el negocio como 'Cerrado temporalmente'. Mismo caso abierto que CASE ID 18: evidencia historica de venta de baterias pero negocio actualmente cerrado. Aprobado por Ricardo: cumple los requisitos del equipo (resenas confirman venta de baterias) aunque Maps lo marque Cerrado temporalmente -- ese estatus por si solo NO descalifica un negocio. Se encontro foto de Maps del propietario (no detectada en la primera revision) que muestra claramente un anaquel con baterias LTH/America -- corrige la evidencia previa que solo tenia resenas de texto.</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>fotos/019_venta_de_baterias_de_carros/streetview_1.jpg</t>
+          <t>fotos/019_venta_de_baterias_de_carros/streetview_1.jpg; fotos/019_venta_de_baterias_de_carros/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>streetview_2.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$P$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$P$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1971,8 +1971,7708 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Pantitlán</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Av. Pantitlán ＃679, La Perla, 57830 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>19.380773</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-98.9891693</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES PANTITLAN</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>América, Cronos</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterías físicas porque la cortina metálica está cerrada; la evidencia es el rótulo pintado en la fachada con el nombre del negocio y logos de marcas.</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>El letrero de la fachada dice 'BATERIAS P/AUTO' y, debajo, 'ACUMULADORES PANTITLAN', coincidiendo exactamente con el nombre registrado, junto con logos pintados de las marcas América y Cronos. La cortina metálica está cerrada (sin actividad visible) en ambas fotos, por lo que no hay mostrador ni baterías físicas visibles, pero el rótulo es nítido y suficiente para confirmar el giro.</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>fotos/021_acumuladores_pantitlan/streetview_1.jpg; fotos/021_acumuladores_pantitlan/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>DIST. DE BATERÍAS CRUZ</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Av. Pantitlán 187-Loc A, entre Calle Juan de Dios Peza y Av. Cuauhtémoc, Mexico 2da Secc, 57620 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>19.4059999</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-99.0421022</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías; en las coordenadas exactas del pin se ve un local de 'Abarrotes Vinos y Licores' con anuncios de refrescos y cervezas, sin relación con baterías.</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>En las coordenadas exactas del pin, ambas fotos de Street View muestran un negocio de 'Abarrotes Vinos y Licores' con letrero grande, sin ningún rastro del nombre 'DIST. DE BATERIAS CRUZ' en la fachada. La ficha de Google Maps de este negocio aparece como 'Cerrado temporalmente', sin fotos útiles en su galería (la única foto disponible muestra un mostrador tipo tortillería/masa no relacionado con baterías), y sus 2 reseñas (de hace 8 años) son genéricas ('Calidad y excelente trato', 'Excelente calidad e higiene') sin mencionar baterías. Según la regla del PIN exacto, se clasifica NO.</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>fotos/022_dist_de_baterias_cruz/streetview_1.jpg; fotos/022_dist_de_baterias_cruz/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ ESPINO MARIA DEL ROCIO</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Marieta 194, Benito Juárez, 57000 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>19.4012704</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-98.9958216</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en la foto disponible; la vista está bloqueada por una planta de plátano grande y no se distingue ninguna fachada comercial.</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ambas fotos de Street View muestran la vista bloqueada por una planta de plátano de gran tamaño frente al domicilio; no se distingue ningún rótulo ni fachada comercial (solo un edificio tipo vivienda y, parcialmente, una tienda de electrodomésticos vecina). La ficha de Maps aparece 'Cerrado temporalmente', sin fotos en la galería, y su única reseña (hace 5 años) dice 'Excelente servicio y reparación de mis licuadoras y lavadora', lo que sugiere un giro de reparación de electrodomésticos y no menciona baterías en absoluto. La evidencia es insuficiente y ambigua para confirmar o descartar la venta de baterías.</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>fotos/023_sanchez_espino_maria_del_rocio/streetview_1.jpg; fotos/023_sanchez_espino_maria_del_rocio/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidor de Acumuladores López</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Av. Floresta 190, Reforma, 57840 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>19.3727011</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>-98.98251380000001</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "LOPEZ"</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterías físicas individuales; la fachada está cubierta por un toldo/estructura y no se distingue un aparador claro en la foto.</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>En la foto de contexto (streetview_2.jpg, fov 90) se lee claramente el letrero 'ACUMULADORES LOPEZ' junto al logo de la marca LTH, en el mismo predio donde la foto de zoom (streetview_1.jpg, fov 50) enfocó por error el negocio vecino ('Rock School Music' / 'AquaMatic Lavanderías'). El nombre coincide exactamente con el registrado.</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>fotos/024_distribuidor_de_acumuladores_lopez/streetview_1.jpg; fotos/024_distribuidor_de_acumuladores_lopez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>La casa de la Batería Car 100</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Av. Simon Bolívar 16, Los Reyes, 56400 Los Reyes Acaquilpan, Méx., México</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>19.359548</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>-98.9795479</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS ECONOMICAS CAR 100</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Duracell</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Se aprecia un aparador/persiana semiabierta con anaqueles oscuros detrás, pero los productos individuales no se distinguen con claridad por la iluminación de la foto.</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>El letrero de la fachada dice 'BATERIAS ECONOMICAS CAR 100' y, al lado, un anuncio de 'DURACELL - BATERIAS PARA AUTO - DE VENTA AQUI', coincidiendo exactamente con el nombre registrado ('La casa de la Batería Car 100'). Ambas fotos de Street View confirman el mismo rótulo en la misma ubicación.</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>fotos/025_la_casa_de_la_bateria_car_100/streetview_1.jpg; fotos/025_la_casa_de_la_bateria_car_100/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LTH LAS ZAPATAS</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Av. Valle de las Zapatas # 139, Campestre Guadalupana, 57120 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>19.4861945</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>-99.0527005</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterías físicas; la cortina metálica de este local está cerrada, solo se ve el banner de marca LTH sobre ella.</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Ambas fotos de Street View muestran un banner de la marca LTH (con número telefónico propio) colocado directamente sobre la cortina metálica cerrada de este local específico, ubicado entre 'Closets y Puertas / Agua Inmaculada' y 'Carpintería', coincidiendo con la dirección registrada (Av. Valle de las Zapatas #139). No se lee el nombre completo 'Acumuladores LTH Las Zapatas' en la fachada, pero el banner de marca en el sitio exacto es evidencia suficiente del giro.</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>fotos/026_acumuladores_lth_las_zapatas/streetview_1.jpg; fotos/026_acumuladores_lth_las_zapatas/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LAGO</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Av Aeropuerto 14, Cd Lago, 57180 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>19.4541298</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>-99.0484987</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "JORGE"</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Se distingue una batería física de la marca América Racing (carcasa azul/roja) exhibida sobre un banco metálico junto a la puerta de entrada, además de un gráfico pintado de una batería LTH en la pared del local.</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>El rótulo de la fachada dice 'ACUMULADORES JORGE' (difiere del nombre registrado 'Acumuladores Lago'), pero el giro y la ubicación coinciden plenamente: hay letreros de 'CARGA DE BATERIAS' y 'OFERTA DE BATERIAS', gráficos de las marcas LTH y América Racing, y una batería física real exhibida en la entrada. Se prioriza la evidencia visual del giro sobre el nombre registrado, dejando constancia de la discrepancia de nombre.</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>fotos/027_acumuladores_lago/streetview_1.jpg; fotos/027_acumuladores_lago/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores López</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Av. Taxímetros 26, Bosques de Aragon, 57170 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>19.4615001</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>-99.0539407</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Duracell, América, X-Power, Voltar</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>La foto subida por el propietario (Cesar López) en Google Maps muestra un aparador completo con decenas de baterías físicas apiladas en anaqueles metálicos, de las marcas Duracell, LTH, América, X-Power y Voltar, bajo un letrero que dice 'Diagnóstico, Venta e Instalación'.</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ambas fotos de Street View en las coordenadas exactas del pin muestran solo la fachada blanca de una construcción tipo bodega/vivienda con una puerta numerada '15', sin ningún rótulo ni evidencia de negocio (probablemente la entrada comercial está en otro punto del predio). Sin embargo, en la ficha de Google Maps de 'Acumuladores López' (mismo lugar según el enlace proporcionado en el Excel) se encontró una foto subida por el propietario que muestra claramente un aparador lleno de baterías físicas de múltiples marcas con el letrero 'Diagnóstico, Venta e Instalación', respaldada además por reseñas de clientes que confirman la compra de baterías con instalación a domicilio. Se usa esta foto de Maps como evidencia principal ya que el Street View resultó insuficiente.</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>fotos/028_acumuladores_lopez/streetview_1.jpg; fotos/028_acumuladores_lopez/streetview_2.jpg; fotos/028_acumuladores_lopez/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH SUC. NEZA-ORIENTE</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Narvarte 292, Jose Vicente Villada, 57760 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>19.3936833</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>-99.015778</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>La foto oficial de la ficha de Maps muestra la fachada con el logo grande de LTH y, detrás de una reja de seguridad, anaqueles con baterías físicas de las marcas LTH y América apiladas.</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: en las coordenadas exactas del pin, ambas fotos de Street View muestran negocios distintos ('Tintorería y Planchaduría', 'Miscelánea La Chiquis', 'Servicio Peña' de reparación de puertas/chapas), sin ningún rastro del centro de servicio LTH. Sin embargo, la ficha de Google Maps de 'Centro de Servicio LTH suc. Neza-Oriente' (mismo enlace registrado) aparece como negocio patrocinado oficial de Johnson Controls/LTH, con estatus 'Abierto', 25 reseñas (varias confirmando compra e instalación de baterías, ej. 'Compré una batería... la instalaron a domicilio'), y una foto oficial que muestra la fachada con el logo LTH y anaqueles llenos de baterías físicas. Se prioriza esta evidencia de Maps ya que el Street View del domicilio exacto parece desactualizado o mal referenciado.</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>fotos/029_centro_de_servicio_lth_suc_neza_oriente/streetview_1.jpg; fotos/029_centro_de_servicio_lth_suc_neza_oriente/streetview_2.jpg; fotos/029_centro_de_servicio_lth_suc_neza_oriente/maps_foto_1.jpg; fotos/029_centro_de_servicio_lth_suc_neza_oriente/maps_foto_2.jpg; fotos/029_centro_de_servicio_lth_suc_neza_oriente/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MI AUTO</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Av. Carlos Hank González 77, Impulsora Popular Avicola, 57130 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>19.4814077</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>-99.0508166</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Cronos, América</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>La foto de la ficha de Maps muestra un local con murales pintados de las marcas LTH y Cronos, y adentro anaqueles repletos de baterías físicas de las marcas LTH, América y Cronos/X-Power.</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: en las coordenadas exactas del pin, ambas fotos de Street View muestran un terreno baldío cercado sin ninguna construcción ni negocio visible (el Street View de ese tramo de Av. Carlos Hank González no capta ningún local). Sin embargo, la ficha de Maps de 'Acumuladores mi auto' (mismo enlace registrado) tiene reseñas recientes (hasta hace 1 mes) que confirman explícitamente la compra de baterías ('Ya he comprado un par de veces de diferentes vehículos... una batería me duró casi los seis años', 'Cuentan con gran variedad de baterías'), y una foto subida a la ficha que muestra un local real con murales de LTH y Cronos y anaqueles llenos de baterías físicas. Se prioriza esta evidencia de Maps sobre el Street View, que no resultó útil para este domicilio.</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>fotos/030_acumuladores_mi_auto/streetview_1.jpg; fotos/030_acumuladores_mi_auto/streetview_2.jpg; fotos/030_acumuladores_mi_auto/maps_foto_1.jpg; fotos/030_acumuladores_mi_auto/maps_foto_2.jpg; fotos/030_acumuladores_mi_auto/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores León</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>C. 19 40, Campestre Guadalupana, 57120 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>19.4828412</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>-99.0599186</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LEÓN</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel completo con al menos 20 baterías de auto de marcas LTH y América apiladas en dos niveles bajo el rótulo 'ACUMULADORES LEÓN'; también hay garrafas de refrigerante Bardahl en el piso (no cuenta como marca de batería).</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas solo muestra un muro residencial sin fachada visible (calle/ángulo distinto). Sin embargo, las fotos propias de la ficha de Google Maps de este mismo negocio muestran la fachada completa con el rótulo 'ACUMULADORES LEÓN' (coincide exacto con el nombre registrado) y anaqueles llenos de baterías LTH y América, confirmando la venta de baterías.</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>fotos/031_acumuladores_leon/streetview_1.jpg; fotos/031_acumuladores_leon/streetview_2.jpg; fotos/031_acumuladores_leon/maps_foto_1.jpg; fotos/031_acumuladores_leon/maps_foto_2.jpg; fotos/031_acumuladores_leon/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Calle Coronel Simón Elías González 6, Juan Escutia, Iztapalapa, 09100 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>19.3969907</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>-99.0551624</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías físicas con claridad en las fotos de Street View disponibles (el interior se ve oscuro, sin producto visible en anaqueles), pero el rótulo grande 'Centro de Servicio LTH' identifica un centro de servicio oficial de la marca de baterías LTH.</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>El nombre en la fachada coincide exactamente con el registrado ('CENTRO DE SERVICIO LTH ZARAGOZA'), con el logo oficial de la marca LTH grande y visible en ambas fotos de Street View; es un centro de servicio autorizado de baterías, aunque el interior no se distingue con claridad por el ángulo/luz disponibles.</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>fotos/032_centro_de_servicio_lth_zaragoza/streetview_1.jpg; fotos/032_centro_de_servicio_lth_zaragoza/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores América Car</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Blvd. Joyas de Aragón 24, Joyas de Aragon, 57158 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>19.4699257</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>-99.0566953</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES AMERICA CAR'S</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Mostrador con anaquel de cajas de producto (baterías y refrigerantes) bajo múltiples letreros y toldos de marca LTH; se distinguen cajas de colores en los estantes junto a la vitrina.</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>El nombre en el toldo coincide exactamente con el registrado ('ACUMULADORES AMERICA CAR'S'), con varios logos LTH visibles en el toldo, la vitrina y el interior de la tienda, confirmando la venta de baterías en el sitio exacto.</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>fotos/033_acumuladores_america_car/streetview_1.jpg; fotos/033_acumuladores_america_car/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS OSONIX</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Av. Morelos, Avenida Valle De Santiago 73, El Chamizal, 55270 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>19.4974053</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>-99.0522309</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>No se puede confirmar con certeza: la foto principal por defecto de la ficha de Maps es irrelevante (un exhibidor de soportes para bicicleta, sin relación con baterías). La única foto de baterías disponible proviene de una reseña sin texto (usuario 'Salathiel 034') y muestra un anaquel con baterías de varias marcas (LTH, Full Power, Battery Club, Voltarr) y letrero 'SE COMPRA BATERIAS VIEJAS', pero sin ningún rótulo que confirme el nombre 'Osonix' ni que certifique que es la fachada de este PIN exacto.</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE: el Street View en las coordenadas exactas solo muestra una calle lejana sin ningún negocio identificable. La ficha de Maps categoriza el lugar como 'Tienda de baterías para automóvil' con 'Entrega a domicilio' y tiene 1 reseña (5.0) con una foto adjunta de un anaquel de baterías, pero esa foto no muestra el nombre del negocio y la foto principal por defecto de la ficha es de otro objeto sin relación (soportes de bicicleta), lo que genera duda sobre la fiabilidad del set de fotos de esta ficha. No hay evidencia suficiente para confirmar con certeza que se trate de este negocio en este domicilio exacto -- se requiere revisión adicional (visita en persona o más fotos).</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>fotos/034_baterias_osonix/streetview_1.jpg; fotos/034_baterias_osonix/streetview_2.jpg; fotos/034_baterias_osonix/maps_foto_1.jpg; fotos/034_baterias_osonix/maps_foto_2_review.jpg</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2_review.jpg</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES RANCING</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Constitución de la República 94, Jardines de Guadalupe, 57140 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>19.4789439</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>-99.05799450000001</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Duracell, América, Full Power, Xtra, Voltarr</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel de piso a techo con decenas de baterías de auto de varias marcas (LTH, Duracell, América, Full Power, Xtra, Voltarr) bajo el rótulo 'Diagnóstico, Venta e Instalación'.</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos propias de la ficha de Maps de este negocio muestran un anaquel completo de baterías de múltiples marcas bajo el rótulo 'Diagnóstico, Venta e Instalación'. Aunque el nombre 'Rancing' no aparece explícito en las fotos, las 10 reseñas de esta misma ficha confirman explícitamente la venta de baterías ('te ponen batería en 700 y sale en 1300, sean honestos', 'mejor marca de baterías', 'buen trato y buen precio'), lo que en conjunto confirma la venta de baterías en este negocio.</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>fotos/035_acumuladores_rancing/streetview_1.jpg; fotos/035_acumuladores_rancing/streetview_2.jpg; fotos/035_acumuladores_rancing/maps_foto_1.jpg; fotos/035_acumuladores_rancing/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="n"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LA CHINA</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Av. Taxímetros 68, Bosques de Aragon, 57170 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>19.4606494</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>-99.0497903</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LA CHINA</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América, Gonher, Xtreme, Checker</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel de baterías de auto con marcas LTH, América, Gonher, Xtreme y Checker visibles en cajas, bajo el toldo 'ACUMULADORES LA CHINA' con logo LTH y la leyenda 'Energía que no se detiene'.</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos propias de la ficha de Maps de este negocio muestran el toldo con el nombre exacto 'ACUMULADORES LA CHINA' junto al logo LTH y un anaquel lleno de baterías de varias marcas. Las reseñas también confirman la venta de baterías ('me salió mal la batería y usé mi garantía... que mal servicio', 'buenas baterías'). El Street View en el PIN exacto mostraba un negocio distinto (Auto Pinturas América / Salón de belleza / Barbería), pero las fotos propias de esta ficha de Maps confirman la fachada real con el nombre coincidente en esa misma dirección.</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>fotos/036_acumuladores_la_china/streetview_1.jpg; fotos/036_acumuladores_la_china/streetview_2.jpg; fotos/036_acumuladores_la_china/maps_foto_1.jpg; fotos/036_acumuladores_la_china/maps_foto_2.jpg; fotos/036_acumuladores_la_china/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>LA CHISPA ADECUADA ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Av. Texcoco 293, Juan Escutia, Iztapalapa, 09100 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>19.3962919</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>-99.0485406</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América, Full Power</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel interior con cajas de baterías etiquetadas 'AMÉRICA' y 'LTH'; también foto de una batería física de marca Full Power sin su empaque.</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el PIN exacto mostraba un despacho jurídico contable y una farmacia genéricos, sin ningún negocio de baterías visible en la fachada. Sin embargo, las fotos subidas directamente a esta ficha de Maps muestran, en la misma construcción (se reconoce la misma cortina azul del despacho jurídico contable al costado izquierdo), una entrada con banderines 'BATERIAS AMÉRICA' y rótulo LTH, además de un interior con anaquel de baterías América/LTH y una batería física Full Power de cerca. El nombre 'La Chispa Adecuada' no aparece en ninguna foto, pero el giro y la ubicación exacta (fotos vinculadas directamente a esta ficha de Maps, contigua al despacho jurídico visto en Street View) corresponden razonablemente.</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>fotos/037_la_chispa_adecuada_acumuladores/streetview_1.jpg; fotos/037_la_chispa_adecuada_acumuladores/streetview_2.jpg; fotos/037_la_chispa_adecuada_acumuladores/maps_foto_1.jpg; fotos/037_la_chispa_adecuada_acumuladores/maps_foto_2.jpg; fotos/037_la_chispa_adecuada_acumuladores/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="n"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>BISA ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Av. Simon Bolívar 26, Los Reyes, 56400 Los Reyes Acaquilpan, Méx., México</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>19.3576534</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>-98.9797214</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES BISA</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel de baterías de auto marca LTH visible en el mostrador de la tienda, bajo el rótulo 'LTH ACUMULADORES BISA'.</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>El Street View (streetview_2.jpg) muestra claramente el rótulo 'LTH ACUMULADORES BISA', que coincide exactamente con el nombre registrado, con anaquel de baterías físicas visibles en el mostrador de la tienda.</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>fotos/038_bisa_acumuladores/streetview_1.jpg; fotos/038_bisa_acumuladores/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Baterías a domicilio para autos "BANZAI ARAGÓN"</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>C. 619 227, San Juan de Aragón IV Secc, Gustavo A. Madero, 07979 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>19.458782</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>-99.0678755</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>América, Duralast, LTH</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Foto real de una batería física marca Duralast Gold de un servicio de instalación/retiro; material promocional oficial del negocio 'BATERIAS BANZAI' mostrando baterías América Racing y el texto 'Haz tu pedido'.</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Es un servicio de baterías a domicilio (sin local físico de venta al público), por lo que el Street View del domicilio registrado no muestra ningún rótulo de negocio -- esto es consistente con el modelo de negocio y no indica un PIN incorrecto. La ficha de Maps tiene 232 reseñas (4.9 estrellas) que confirman explícitamente el servicio de instalación de baterías a domicilio ('llegó muy rápido a mi domicilio a cambiar la batería', 'vienen a tu domicilio y te instalan la batería, te explican todas tus dudas'), y las fotos propias del negocio muestran una batería física real (Duralast) y material promocional de marca 'BATERIAS BANZAI' con baterías América, coincidiendo con el nombre registrado ('BANZAI ARAGÓN').</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>fotos/039_baterias_a_domicilio_para_autos_banzai_aragon/streetview_1.jpg; fotos/039_baterias_a_domicilio_para_autos_banzai_aragon/streetview_2.jpg; fotos/039_baterias_a_domicilio_para_autos_banzai_aragon/maps_foto_1.jpg; fotos/039_baterias_a_domicilio_para_autos_banzai_aragon/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="n"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>DURACEL LAS ZAPATAS</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Av. Plaza Central 61D, Plazas de Aragon, 57139 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>19.4841784</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>-99.0395784</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>BATTERY CLUB - Centro de Servicio DURACELL</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Duracell, Battery Club, V8, Automat</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel con múltiples baterías de auto de marcas Duracell, Battery Club, V8 y Automat, con letreros de promociones y garantías, bajo el rótulo 'BATTERY CLUB - Centro de Servicio DURACELL'.</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el PIN exacto mostraba un despacho jurídico ('SOTO') en un inmueble de fachada amarilla, sin relación aparente con baterías. Sin embargo, las fotos propias de esta misma ficha de Maps muestran, en un inmueble también de fachada amarilla, un local con el rótulo 'BATTERY CLUB - Centro de Servicio DURACELL' y anaquel lleno de baterías físicas de varias marcas -- coincide con el nombre 'Duracel Las Zapatas' registrado (la marca Duracell y el domicilio 61D corresponden) y confirma claramente la venta de baterías.</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>fotos/040_duracel_las_zapatas/streetview_1.jpg; fotos/040_duracel_las_zapatas/streetview_2.jpg; fotos/040_duracel_las_zapatas/maps_foto_1.jpg; fotos/040_duracel_las_zapatas/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>🔋ACUMULADORES ARAGÓN 🔋Tienda de Baterías para Autos Motos y Servicio Pesado en CDMX</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Av. José Loreto Fabela 670, San Juan de Aragón VII Secc, Gustavo A. Madero, 07910 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>19.4700384</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>-99.07948140000001</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ARAGÓN</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Tauro Force, LTH, América Racing</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>La ficha de Maps para esta misma dirección exacta opera actualmente como 'Acumuladores Tauro'; una foto subida por un cliente muestra una batería marca Tauro Force instalada en un motor, con etiqueta de marca legible (no es foto de mostrador, sino de producto ya instalado).</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>El edificio en las coordenadas exactas tiene pintado en gran formato 'ACUMULADORES ARAGÓN' y el texto 'FUERZA EN SU MAXIMA POTENCIA' junto al logo de América Racing (streetview_1/2), coincidiendo el giro y la ubicación con el registro, aunque la cortina metálica está cerrada y no se ve mostrador. La ficha de Google Maps en esta misma dirección exacta (Av. José Loreto Fabela 670) opera bajo el nombre 'Acumuladores Tauro' -- el cartel 'TAURO' ya se distinguía parcialmente en un póster sobre la cortina cerrada -- y su descripción confirma venta de baterías LTH, América Racing, Full Power, Xtreme y Tauro Force; una foto de cliente confirma una batería Tauro Force real. Se prioriza la evidencia visual y de ubicación (coincide el giro) sobre el nombre exacto registrado, que pudo haber cambiado de operador.</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>fotos/041_acumuladores_aragon_tienda_de_baterias_para_autos_motos_y_servicio_pesado_en_cdmx/streetview_1.jpg; fotos/041_acumuladores_aragon_tienda_de_baterias_para_autos_motos_y_servicio_pesado_en_cdmx/streetview_2.jpg; fotos/041_acumuladores_aragon_tienda_de_baterias_para_autos_motos_y_servicio_pesado_en_cdmx/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>WIN RACE</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Constitución de la República 17, Jardines de Guadalupe, 57140 Cdad. Nezahualcóyotl, Méx., México</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>19.4788012</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>-99.0577858</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>La foto principal de la ficha de Maps de 'Win Race' muestra un local con rótulo grande 'LTH' en la fachada y, tras una reja de seguridad, varias filas de baterías físicas apiladas (LTH y América Racing) en anaqueles.</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View en las coordenadas EXACTAS del pin (19.4788012,-99.0577858) muestra una tienda de materiales de construcción ('Materiales Sunny'/'Cemento Tolteca'), sin relación con baterías ni con el nombre 'Win Race' -- el heading autocalculado de la Static API aparentemente tomó un edificio/panorama distinto al que Google Maps asocia a esta ficha. Se revisó directamente la ficha de Maps de 'Win Race' (mismo ID de lugar y misma dirección: Constitución de la República 17, Jardines de Guadalupe): está categorizada como 'Tienda de baterías para automóvil' y su foto principal (verificada, coincide con el título de la ficha en el momento de la captura) muestra baterías LTH y América Racing físicamente apiladas. No hay reseñas que lo confirmen adicionalmente. El nombre 'Win Race' no se ve escrito en ninguna foto disponible, pero el giro, dirección y categoría de Maps coinciden con el registro.</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>fotos/042_win_race/streetview_1.jpg; fotos/042_win_race/streetview_2.jpg; fotos/042_win_race/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="n"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GAGO</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cuauhtémoc Pte. 11, La Bomba, 56600 Chalco de Díaz Covarrubias, Méx., México</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>19.2724719</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>-98.88870799999999</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "GAGO"</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>La foto de la ficha de Maps muestra el mural de la fachada con dos gráficos de baterías marca LTH pintados a los costados de la cortina metálica cerrada, y el logotipo LTH repetido en el toldo superior; no se aprecia producto físico apilado porque la cortina está cerrada.</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Street View en las coordenadas exactas no mostraba ningún nombre de negocio (solo un muro rojo con un portón negro sin rótulo). Se revisó la ficha de Maps de 'Acumuladores Gago': su foto principal confirma 'ACUMULADORES GAGO' pintado en gran formato junto al letrero de calle 'Cuauhtémoc Poniente' (coincide con la dirección registrada 'Av. Cuauhtémoc Pte. 11'), con gráficos de batería LTH y el eslogan 'ENERGIA QUE NO SE DETIENE'. Las reseñas de la ficha (4.5 estrellas, 29 opiniones) mencionan explícitamente 'sus baterías de buena calidad' y baterías americanas recomendadas, confirmando adicionalmente la venta de baterías.</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>fotos/043_acumuladores_gago/streetview_1.jpg; fotos/043_acumuladores_gago/streetview_2.jpg; fotos/043_acumuladores_gago/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Comercializadora de Acumuladores López Buda</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cuauhtémoc Pte. 7, San Miguel Jacalones, 56604 Chalco de Díaz Covarrubias, Méx., México</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>19.2675929</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>-98.895555</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ACUMULADORES LOPEZ BUDA</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>No se consultó la galería de Maps para este caso (Street View fue concluyente). En las fotos disponibles no se aprecian baterías físicas apiladas con claridad, solo el rótulo con un gráfico genérico de acumulador y los textos de servicio.</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>El rótulo grande en la fachada (streetview_1) dice exactamente 'COMERCIALIZADORA DE ACUM[ULADORES]... LOPEZ BUDA' con un gráfico de batería, y justo debajo se lee explícitamente 'BATERIAS AUTOS CAMIONES CARROS ELECTRICOS' y 'CARGA Y DIAGNOSTICO'; el negocio vecino inmediato tiene además un banner de 'ACUMULADORES DURANGO - EL ARRANQUE DEL TORO'. El nombre coincide exactamente con el registrado y el giro del negocio (venta y carga de baterías) es inequívoco.</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>fotos/044_comercializadora_de_acumuladores_lopez_buda/streetview_1.jpg; fotos/044_comercializadora_de_acumuladores_lopez_buda/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FIGUEROA</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cuauhtémoc Pte. 776-B, San Miguel Jacalones, 56604 Chalco de Díaz Covarrubias, Méx., México</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>19.26956</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>-98.89307100000001</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FIGUEROA</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>No se consultó la galería de Maps para este caso (Street View fue concluyente). Se aprecia un gráfico pintado de una batería LTH en la fachada y el logotipo LTH repetido en un letrero vertical sobre la banqueta, pero la cortina metálica está cerrada por lo que no se ve producto físico apilado.</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>El rótulo dice 'ACUMULADORES FIGUEROA' con el logo de LTH y el texto 'BATERIAS AUTOS MOTOS CAMION', además de un letrero vertical independiente de LTH junto a la entrada (streetview_1 y streetview_2). Nombre y giro coinciden exactamente con el registro.</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>fotos/045_acumuladores_figueroa/streetview_1.jpg; fotos/045_acumuladores_figueroa/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Ixtapaluca, los expertos en baterías</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cuauhtémoc 19-Local B, Geovillas San Jacinto, 56530 Ixtapaluca, Méx., México</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>19.3136089</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>-98.8873572</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power, América Racing, Gonher</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>La foto de la ficha de Maps muestra el rótulo 'CENTRO DE VENTAS' con banners de las marcas LTH, Full Power, América Racing y Gonher, y baterías físicas apiladas en anaqueles rojos y azules visibles a través de la entrada del local ('CARGA DE BATERIA LENTA Y RAPIDA', 'ACUMULADORES... ENERGIA MAS POTENTE').</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View en las coordenadas exactas (Av. Cuauhtémoc 19, Local B) solo muestra un tramo residencial con casas y un enrejado, sin ningún local comercial identificable -- el negocio ocupa un 'Local B' que Street View no capta desde ese ángulo. Se revisó la ficha de Maps de 'Acumuladores Ixtapaluca, los expertos en baterías': su foto principal confirma el giro con rótulo 'CENTRO DE VENTAS' y baterías físicas de varias marcas visibles. Las reseñas (4.7 estrellas, 61 opiniones) confirman explícitamente compras de baterías LTH ('la batería LTH me salió en 2 mil pesos') y servicio de diagnóstico de batería.</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>fotos/046_acumuladores_ixtapaluca_los_expertos_en_baterias/streetview_1.jpg; fotos/046_acumuladores_ixtapaluca_los_expertos_en_baterias/streetview_2.jpg; fotos/046_acumuladores_ixtapaluca_los_expertos_en_baterias/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="n"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ESPECIALES "ACUMES" BATERIAS PARA TODO AUTO.</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>México 115 20, 56535 El Jaral, Méx., México</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>19.3018123</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>-98.8850315</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "ACME" (variante gráfica del rótulo; registrado como ACUMES)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing, Acumix (Grupo Acumix AGM)</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>La foto de la ficha de Maps muestra el frente del local con banners de LTH y América Racing, un anaquel interior con cajas de batería visibles a través de la entrada, y una bandera publicitaria 'LTH Hi-Tec'; el rótulo principal dice 'ACUMULADORES ACME' junto con 'Centro de Diagnóstico' y 'Servicio a domicilio'.</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>PIN: Street View en las coordenadas exactas muestra una oficina de 'GNP SEGUROS' con letrero de 'ARCA', sin relación con baterías -- se observó además un letrero LTH de un negocio DISTINTO más adelante en la misma calle, el cual NO se acredita a esta ficha por tratarse de otro negocio. Se revisó directamente la ficha de Maps de 'Acumuladores Especiales ACUMES Baterias para todo auto' (mismo ID de lugar y mismas coordenadas): su foto principal muestra un local de baterías con rótulo 'ACUMULADORES ACME' (variante del nombre registrado), marcas LTH/América Racing y anaqueles con producto, coincidiendo el giro con el registro aunque el nombre exacto en el rótulo varía levemente respecto a 'ACUMES'.</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>fotos/047_acumuladores_especiales_acumes_baterias_para_todo_auto/streetview_1.jpg; fotos/047_acumuladores_especiales_acumes_baterias_para_todo_auto/streetview_2.jpg; fotos/047_acumuladores_especiales_acumes_baterias_para_todo_auto/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores y Lubricantes Jiménez</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Sur 6, Manzana 015, Niños Heroes, 56610 Xico, Méx., México</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>19.2848366</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>-98.9512862</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES JIMENEZ - NUEVAS Y USADAS</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>La foto de la ficha de Maps (fechada 2019) muestra el rótulo exacto 'ACUMULADORES JIMENEZ - NUEVAS Y USADAS', con los textos 'CARGA DE BATERIAS' y 'ADITIVOS' pintados en la fachada, y un anaquel interior con productos LTH/América Racing visibles tras la reja de seguridad junto a un letrero 'CAMBIO DE ACEITE'.</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>PIN: Street View en las coordenadas exactas muestra 'Compra y Venta López' (compra-venta de tambos/barriles industriales), un negocio totalmente distinto sin relación con baterías. Se revisó la ficha de Maps de 'Acumuladores y Lubricantes Jiménez' (mismo ID de lugar, misma dirección 'Niños Héroes, Valle de Chalco Solidaridad'): su única foto disponible confirma el rótulo exacto 'ACUMULADORES JIMENEZ - NUEVAS Y USADAS' con 'CARGA DE BATERIAS' pintado en la fachada, confirmando que nombre y giro sí corresponden a esta ficha aunque el pin de Street View actual apunte a un negocio vecino distinto (posiblemente por reubicación del pin o cambio del negocio en esa dirección).</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>fotos/048_acumuladores_y_lubricantes_jimenez/streetview_1.jpg; fotos/048_acumuladores_y_lubricantes_jimenez/streetview_2.jpg; fotos/048_acumuladores_y_lubricantes_jimenez/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="n"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES Y LUBRICANTES JIMENEZ</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Av. Solidaridad 336, San Isidro, 56617 Valle de Chalco Solidaridad, Méx., México</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>19.2894363</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>-98.9177826</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES [texto obstruido por poste]</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>No se consultó la galería de Maps para este caso (Street View fue suficiente). No se aprecian baterías físicas apiladas, solo el rótulo pintado con el logo LTH y un anuncio de 'ACEITES Y FILTROS' debajo.</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>El edificio en las coordenadas exactas muestra pintado 'ACUMULADORES' con el logo de LTH y, debajo, un anuncio de 'ACEITES Y FILTROS' (streetview_1 y streetview_2), coincidiendo el giro (acumuladores + lubricantes) con el nombre registrado. Un poste de luz obstruye parte del texto por lo que no se confirma visualmente la palabra 'JIMENEZ', pero la combinación de giro + marca LTH + ubicación es consistente con el registro. Posible sucursal hermana del CASE ID 48 (mismo nombre de negocio, domicilio distinto en Valle de Chalco Solidaridad).</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>fotos/049_acumuladores_y_lubricantes_jimenez/streetview_1.jpg; fotos/049_acumuladores_y_lubricantes_jimenez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GALVÁN - BATERIAS A DOMICILIO LTH TLAHUAC</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Calz. Reforma Agraria 1387, San José, Tláhuac, 13020 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>19.2721603</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>-98.9971558</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GALVAN</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>La foto de la ficha de Maps muestra la fachada completa con el rótulo 'ACUMULADORES GALVAN - BATERIAS AUTOMOTRICES' y seis gráficos pintados de baterías con logo LTH; a través de la puerta de rejas se distinguen cajas apiladas pero no se confirman con claridad como baterías físicas.</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View en las coordenadas exactas solo muestra un mural artístico callejero y una parada de camión, sin ningún rótulo de negocio visible (el negocio es de tipo 'batería a domicilio', por lo que pudiera no tener una fachada muy visible desde ese ángulo específico). Se revisó la ficha de Maps de 'ACUMULADORES GALVÁN - BATERIAS A DOMICILIO LTH TLAHUAC': su foto principal confirma el rótulo exacto 'ACUMULADORES GALVAN - BATERIAS AUTOMOTRICES' con gráficos LTH, y el sitio web propio (bateriaexpressadomicilio.com.mx) junto con 119 reseñas (4.7 estrellas) describen consistentemente el servicio de venta e instalación de baterías a domicilio, con respuestas del propietario firmadas 'En ACUMULADORES GALVÁN'.</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>fotos/050_acumuladores_galvan_baterias_a_domicilio_lth_tlahuac/streetview_1.jpg; fotos/050_acumuladores_galvan_baterias_a_domicilio_lth_tlahuac/streetview_2.jpg; fotos/050_acumuladores_galvan_baterias_a_domicilio_lth_tlahuac/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="n"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Martínez</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Av. Pipila 67, Santa Catarina Yecahuizotl, 56618 Valle de Chalco Solidaridad, Méx., México</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>19.3121487</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>-98.9624943</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MARTINEZ</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías físicas en exhibición en ninguna de las dos fotos de Street View disponibles; la ficha de Maps no aporta fotos adicionales (usa la misma imagen de calle) ni reseñas.</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: no hay foto que muestre baterías físicas o logos de marca. El veredicto SI se basa en que ambas fotos de Street View (streetview_1 zoom y streetview_2 contexto) muestran con claridad el rótulo 'ACUMULADORES' y 'MARTINEZ' pintado en la fachada exacta (coincide con el nombre registrado 'Acumuladores Martínez'), junto con un cartel comercial 'SE COMPRAN BATERIAS USADAS $160' que confirma el giro de compra-venta de baterías para automóvil en este domicilio.</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>fotos/051_acumuladores_martinez/streetview_1.jpg; fotos/051_acumuladores_martinez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="n"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH SANTA CATARINA</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Eje 10 Sur 1527, San Miguel, Tláhuac, 13100 Santa Catarina Yecahuitzotl, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>19.3059802</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>-98.9739526</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>La ficha de Maps de este negocio no tiene ninguna foto propia (aparece el placeholder genérico y la sugerencia 'Agregar una foto') ni reseñas (0 opiniones), por lo que no hay ninguna imagen de Maps que muestre baterías.</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ambas fotos de Street View (streetview_1 fov=50 zoom y streetview_2 fov=90 contexto), tomadas sobre Eje 10 Sur, quedan totalmente bloqueadas por un camión/autobús detenido y árboles justo frente a las coordenadas exactas del negocio; no se distingue ningún rótulo ni fachada. Se investigó la ficha de Maps (mismo link/place-id) y se confirmó que no tiene fotos propias ni reseñas -- solo nombre, categoría 'Tienda de baterías para automóvil', teléfono 55 9339 4700 y sitio web oficial lth.com.mx. No existe evidencia visual ni textual suficiente para confirmar o descartar la venta de baterías en este domicilio exacto; se deja PENDIENTE.</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>fotos/052_centro_de_servicio_lth_santa_catarina/streetview_1.jpg; fotos/052_centro_de_servicio_lth_santa_catarina/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="n"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Lobato</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Av. José María Pino Suárez 15, Revolucion, 56390 Chicoloapan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>19.4047674</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>-98.9251715</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Gonher, America Racing, Voltar, Battery Club, Autobat, CAR100, Duracell</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>La foto de la ficha de Maps muestra el aparador abierto con al menos 20 baterías físicas apiladas en anaqueles de metal, de marcas LTH, Gonher, América Racing, Voltar, Battery Club, Autobat, CAR100 y Duracell, además de carteles 'BATERIAS PRECIOS BAJOS', 'BATERIAS FULL POWER' y 'SE COMPRA BATERIAS VIEJAS'.</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>El Street View muestra la cortina metálica cerrada con el rótulo vertical 'BATERIAS', el logo 'LTH' repetido dos veces y un cartel 'CARGA REVISION BATERIAS LTH', confirmando el giro exacto en esta fachada. La ficha de Maps para este mismo local (mismo edificio, junto a la barbería 'Academia Eclipse' visible también en el Street View) se llama 'Baterías Lobato' (4.7 estrellas, 11 reseñas) y su foto muestra el aparador abierto repleto de baterías físicas de múltiples marcas. El nombre 'Lobato' no está rotulado literalmente en la fachada (solo 'BATERIAS' + LTH), pero el giro, la ubicación y el edificio coinciden inequívocamente con el registro.</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>fotos/053_baterias_lobato/streetview_1.jpg; fotos/053_baterias_lobato/streetview_2.jpg; fotos/053_baterias_lobato/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="n"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>CARGA DE BATERIAS CORTE DE PLACA</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Calle Constitución 1917 11, Revolucion, 56390 Chicoloapan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>19.402677</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>-98.9233581</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>La única foto disponible en la ficha de Maps (subida en 2020) muestra varias horquillas/tenedores de bicicleta apiladas en el piso junto a una bicicleta -- no corresponde a baterías ni a equipo de recarga o corte de placas; no se aprecia ningún producto o equipo relacionado con baterías en ninguna foto disponible.</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el Street View en las coordenadas exactas muestra solo una barda con portón y un árbol, sin ningún rótulo de negocio visible; únicamente se lee una placa de dirección ('Av Pino Suarez Mz 11 Lt 6 Col Revolucion') que coincide con el domicilio registrado. La única foto de la ficha de Maps no muestra baterías (son piezas de bicicleta). Las 2 reseñas con texto disponibles solo dicen 'Buen lugar, soldadura, roscas hasta 2" oxicorte etc' y 'Sucio', sin mencionar venta de baterías. Maps sí marca el atributo 'Reciclaje: Baterías' y categoriza el lugar como 'Tienda de baterías para automóvil', y el nombre registrado incluye 'Carga De Baterias' (recarga) y 'Corte De Placa', pero no hay evidencia visual ni textual que confirme la VENTA de baterías (a diferencia de solo recarga/reciclaje/herrería). Se deja como PENDIENTE por evidencia insuficiente y contradictoria.</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>fotos/054_carga_de_baterias_corte_de_placa/streetview_1.jpg; fotos/054_carga_de_baterias_corte_de_placa/streetview_2.jpg; fotos/054_carga_de_baterias_corte_de_placa/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="n"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Martínez Santa Rosa</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Av Emiliano Zapata 3943, Santa Rosa, 56376 Chicoloapan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>19.4085905</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>-98.90482969999999</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MARTINEZ - VENTA DE BATERIAS</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>La foto de la ficha de Maps muestra un aparador con al menos 20 baterías físicas en anaqueles bajo el toldo 'ACUMULADORES MARTINEZ - VENTA DE BATERIAS', de marcas LTH y América (líneas Xtreme y Racing), además de dos mascotas/ilustraciones de baterías LTH (AGM) pintadas en la fachada.</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra una casa color rosa de dos pisos con cortina metálica cerrada (con un logo circular rojo tipo 'toro'), sin ningún rótulo del negocio visible -- posiblemente una captura desactualizada o con ángulo distinto. Sin embargo, la ficha de Maps de este mismo lugar (mismo link/place-id 0x1380f5fa591da496) tiene una foto que muestra con total claridad la fachada real 'ACUMULADORES MARTINEZ - VENTA DE BATERIAS', con anaqueles llenos de baterías físicas de marca LTH y América, calificación 5.0 (11 reseñas). El nombre coincide exactamente con el registrado.</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>fotos/055_acumuladores_martinez_santa_rosa/streetview_1.jpg; fotos/055_acumuladores_martinez_santa_rosa/streetview_2.jpg; fotos/055_acumuladores_martinez_santa_rosa/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="n"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO GONHER SIDDHARTA</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Encino 12, San Vicente, 56370 Chicoloapan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>19.4121428</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>-98.9205267</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO GONHER - DISTRIBUIDOR SIDDHARTA</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Gonher, LTH</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de la ficha de Maps muestran el rótulo exterior con la ilustración de una batería GONHER (modelo G24-R, '48 meses de garantia') y el texto 'CENTRO DE SERVICIO BATERIAS GONHER'; en el interior, tras la cortina abierta, se aprecia una caja de producto con el rótulo 'LTH' sobre un anaquel junto con aceites y refacciones.</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>El Street View de la vialidad muestra una toma elevada/de azoteas sin ningún rótulo de negocio visible (ángulo de cámara defectuoso), por lo que se investigó la ficha de Maps del mismo link/place-id. Sus fotos muestran con total claridad el rótulo 'CENTRO DE SERVICIO GONHER - DISTRIBUIDOR SIDDHARTA' (coincide exactamente con el nombre registrado), la ilustración de una batería de marca GONHER, y producto de marca LTH visible en el interior de la tienda.</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>fotos/056_centro_de_servicio_gonher_siddharta/streetview_1.jpg; fotos/056_centro_de_servicio_gonher_siddharta/streetview_2.jpg; fotos/056_centro_de_servicio_gonher_siddharta/maps_foto_1.jpg; fotos/056_centro_de_servicio_gonher_siddharta/maps_foto_2.jpg; fotos/056_centro_de_servicio_gonher_siddharta/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>REFACCIONARIA SUPER DIESEL CARRERA</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Carr. Federal Texcoco-México 17, Ejercito del Trabajo, 56390 Chicoloapan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>19.401726</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>-98.9292167</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>REFACCIONARIA DIESEL - SUPER DIESEL CARRERA</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías para automóvil en ninguna de las fotos revisadas (Street View ni las fotos de la ficha de Maps en pestañas 'Todo'/'Interior'/'Del propietario'): se ven anaqueles de filtros y aceites (Delo, Mobil Delvac, Quaker State), refacciones/empaques colgados en panel, un cofre de auto abierto y un tambo azul rotulado 'LTH LUBRICANTES' (aceite, no baterías).</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>El nombre coincide exactamente en la fachada ('Refaccionaria Diesel - Super Diesel Carrera'), y la ficha de Maps la categoriza como 'Tienda de baterías para automóvil' (4.4 estrellas, 30 reseñas), pero tanto el Street View como las fotos revisadas en la galería de Maps (pestañas Todo/Interior/Del propietario) muestran evidentemente una refaccionaria especializada en diésel/tracto-camión enfocada en aceites, filtros y refacciones (Quaker State, Valvoline, Mobil Delvac, Distribuidora Baldwin, LTH Lubricantes); no se identificó ninguna batería física ni logo de marca de batería, y las 3 reseñas con texto revisadas ('Gran surtido, buena atencion', 'Buen servicio y excelente atención', 'Excelente servicio gracias') no mencionan baterías. Se deja como PENDIENTE: la categoría de Maps sugiere venta de baterías pero ninguna evidencia visual o textual concreta lo confirma.</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>fotos/057_refaccionaria_super_diesel_carrera/streetview_1.jpg; fotos/057_refaccionaria_super_diesel_carrera/streetview_2.jpg; fotos/057_refaccionaria_super_diesel_carrera/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="n"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH FAJA DE ORO</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Av. Adolfo López Mateos (R1) Mz.1 Lt.6, Faja de Oro, 55490 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>19.5284605</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>-99.0514877</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH - Diagnostico, venta e instalacion</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>No se descargó foto adicional de la ficha de Maps (el Street View ya resultó concluyente); al hacer zoom sobre la puerta de vidrio de streetview_1 se distinguen cajas de producto apiladas en un exhibidor con el rótulo 'LTH' repetido.</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>El Street View muestra con total claridad el rótulo 'Centro de Servicio LTH - Diagnostico, venta e instalacion' en la fachada (coincide exactamente con el nombre registrado), con el logo LTH y la franja azul/blanca/verde característica de la marca repetidos en la marquesina; al ampliar la imagen se aprecian cajas de producto apiladas con el rótulo 'LTH' en un exhibidor tras la puerta de vidrio junto a la entrada.</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>fotos/058_centro_de_servicio_lth_faja_de_oro/streetview_1.jpg; fotos/058_centro_de_servicio_lth_faja_de_oro/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="n"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH ARAGON</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Av. 510 340, Pueblo de San Juan de Aragón, Gustavo A. Madero, 07950 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>19.4653151</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>-99.0845635</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH - Diagnostico, venta e instalacion</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America Racing</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de la ficha de Maps muestran el exterior con el rótulo 'Centro de Servicio LTH - Diagnostico, venta e instalacion', banderines 'DE VENTA AQUI' con el logo LTH, y el interior con un anaquel rotulado 'LTH BATERIAS' con cajas de producto físico apiladas, además de un exhibidor de la marca 'America Racing' con estuches de batería.</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>IMPORTANTE - discrepancia de coordenadas: el Street View en las coordenadas EXACTAS registradas (19.4653151,-99.0845635) no muestra este negocio, sino un Burger King y 'Gabter's Uniformes Medicos', dentro del mismo complejo comercial ('Plaza Punta Aragón'). Sin embargo, la ficha de Maps correspondiente al mismo link/place-id (0x4d8df390bca1bb6d) del registro -- con la MISMA dirección exacta que consta en la base ('Av. 510 340, Pueblo de San Juan de Aragón, Gustavo A. Madero, 07950 CDMX') y el MISMO nombre registrado 'Centro de Servicio LTH Aragon' -- tiene fotos propias que muestran con total claridad la fachada e interior reales del negocio: rótulo LTH, banderines de venta, y anaquel 'LTH BATERIAS' con producto físico. Tiene 3,710 reseñas y 5.0 estrellas, por lo que es evidentemente un negocio real, activo y muy establecido dentro de esa misma plaza; la discrepancia con el Street View parece ser un error de LAT/LONG dentro del complejo comercial (coordenada apuntando a un local vecino de la misma plaza), no un negocio distinto de nombre diferente. Se recomienda que el equipo revise/corrija el LAT/LONG de este registro.</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>fotos/059_centro_de_servicio_lth_aragon/streetview_1.jpg; fotos/059_centro_de_servicio_lth_aragon/streetview_2.jpg; fotos/059_centro_de_servicio_lth_aragon/maps_foto_1.jpg; fotos/059_centro_de_servicio_lth_aragon/maps_foto_2.jpg; fotos/059_centro_de_servicio_lth_aragon/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="n"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH SUC. LA ROMANA 2</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Av. Hidalgo 120, Hab la Romana, 54030 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>19.551802</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>-99.1936888</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES JEKA</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>No se descargó foto adicional de Maps (el Street View ya resultó concluyente); la ficha de Maps muestra además una foto del área de recepción/estacionamiento de motocicletas con el logo 'ecosteps' (programa oficial de reciclaje de baterías LTH), consistente con un centro de servicio LTH autorizado, aunque sin baterías físicas en exhibición en esa toma.</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>El Street View muestra un mural grande de una batería de marca LTH junto al texto 'FULL POWER', el rótulo 'ACUMULADORES JEKA' y el logo 'LTH' repetido dos veces sobre la cortina metálica cerrada. El nombre exacto registrado ('...suc. La Romana 2') no aparece rotulado en la fachada -- 'Jeka' parece ser el nombre del operador/franquiciatario local de este centro LTH -- pero el giro (venta/servicio de baterías LTH) y la ubicación coinciden con el registro. La ficha de Maps (mismo link/place-id) confirma 4.4 estrellas y 123 reseñas bajo el nombre exacto 'Centro de Servicio LTH suc. La Romana 2', y una de sus fotos muestra el logo 'ecosteps', el mismo programa de reciclaje de baterías LTH visto en otros centros de este lote (CASE ID 58 y 59).</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>fotos/060_centro_de_servicio_lth_suc_la_romana_2/streetview_1.jpg; fotos/060_centro_de_servicio_lth_suc_la_romana_2/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="n"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>LTH CENTRO DE SERVICIO LOMAS VERDES</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Colina de Las Nieves 93, Boulevares, 53140 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>19.4933949</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>-99.245414</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH - Diagnóstico, venta e instalación (Tel. 55 5941 6259)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>LTH, OPTIMA</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>En streetview_2 se ve el escaparate con cajas de batería marca OPTIMA (AGM) y producto LTH acomodado en anaquel junto al mostrador.</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>El letrero de fachada dice 'Centro de Servicio LTH Diagnóstico, venta e instalación' con el mismo teléfono (5941 6259) que el registro 'LTH Centro de Servicio Lomas Verdes'; en el escaparate se aprecian cajas de batería OPTIMA y producto LTH en anaquel.</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>fotos/061_lth_centro_de_servicio_lomas_verdes/streetview_1.jpg; fotos/061_lth_centro_de_servicio_lomas_verdes/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH SAN CRISTOBAL</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Benito Juárez Sur 25, La Mora, 55030 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>19.5977392</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>-99.0494487</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH - Diagnóstico, venta e instalación</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>No se distinguen baterías individualizadas con claridad; se ve un mueble/anaquel dentro de la cortina entreabierta pero sin resolución suficiente para identificar producto físico.</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 (zoom) encuadró el negocio vecino 'City Clean' (lavandería) y no muestra el nombre; en streetview_2 (contexto), más adelante en el mismo edificio, se ve el letrero oficial 'Centro de Servicio LTH Diagnóstico, venta e instalación', que coincide con el nombre registrado 'Centro de Servicio LTH San Cristobal'.</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>fotos/062_centro_de_servicio_lth_san_cristobal/streetview_1.jpg; fotos/062_centro_de_servicio_lth_san_cristobal/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="n"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH SUC. SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Av 3-A 191, Santa Rosa, Gustavo A. Madero, 07620 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>19.5252572</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>-99.17094419999999</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH - Diagnóstico, venta e instalación</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterías físicas apiladas; el interior es una bahía de servicio/diagnóstico con un vehículo SUV adentro, no un anaquel de venta al público.</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Ambas fotos muestran el letrero 'Centro de Servicio LTH Diagnóstico, venta e instalación' y el logo oficial del programa de reciclaje 'ecosteps - Centro Autorizado para la recepción de acumuladores usados' de LTH, coincidiendo con el nombre registrado 'Centro de Servicio LTH Suc. Santa Rosa'.</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>fotos/063_centro_de_servicio_lth_suc_santa_rosa/streetview_1.jpg; fotos/063_centro_de_servicio_lth_suc_santa_rosa/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="n"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ACUMULADORES LTH SUCURSAL PERINORTE</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>México-querétaro, Av. Super 1, San Martin Tepetlixpan, 54870 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>19.6109882</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>-99.1906331</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>LTH (via logo ecosteps)</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>En el acercamiento de streetview_2 se ve, a través de una ventana con cortina metálica semiabierta, un anaquel con varias baterías automotrices apiladas (cajas rectangulares tipo acumulador), aunque no se distingue la marca impresa por la distancia.</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>En la fachada solo se lee el logo oficial 'ecosteps - Centro Autorizado para la recepción de acumuladores usados' (programa de reciclaje exclusivo de LTH), sin el nombre completo del negocio visible; sin embargo, más adelante sobre la misma pared se aprecia un anaquel con baterías físicas apiladas a través de una ventana, lo que confirma venta de baterías en el sitio registrado 'Central de Acumuladores LTH Sucursal Perinorte'.</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>fotos/064_central_de_acumuladores_lth_sucursal_perinorte/streetview_1.jpg; fotos/064_central_de_acumuladores_lth_sucursal_perinorte/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="n"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH CENTRAL DE ABASTOS</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>La Nueva Viga, CEDA, 09040 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>19.3720352</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>-99.09535320000001</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías físicas apiladas con claridad en el anaquel visible; se ven tambos de aceite/lubricante junto a una vitrina. La evidencia de venta proviene de los letreros, no de producto físico visible.</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>El local (dentro de una tornillería/refaccionaria en la Central de Abastos) exhibe el letrero 'DE VENTA AQUI!' con el logo oficial de LTH (bandera a cuadros, 'el alma de tu automóvil') justo sobre la entrada, y el negocio contiguo se anuncia como 'Servicio a Domicilio' con el dominio 'www.bateriasadomicilio.com', confirmando venta de baterías en el sitio aunque no se ven unidades físicas apiladas en la toma.</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>fotos/065_centro_de_servicio_lth_central_de_abastos/streetview_1.jpg; fotos/065_centro_de_servicio_lth_central_de_abastos/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="n"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Venta de Batería San Miguel</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Morelos 78-Loc C, San Miguel, 56270 Chiconcuac de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>19.5553427</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>-98.8898729</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>LTH (pintado a mano) / Full Power - Reparación y Venta - América - Gomher</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>LTH, CALE</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>En el acercamiento se ve un letrero de neón 'SE COMPRAN BATERIAS VIEJAS' flanqueado por los logos oficiales de las marcas de batería LTH (bandera a cuadros) y CALE, con un anaquel de producto apilado visible tras el cristal.</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>La fachada tiene pintado el texto 'LTH' junto con 'Reparación y Venta', y el interior muestra letreros/lonas de las marcas de batería LTH y CALE junto al aviso 'SE COMPRAN BATERIAS VIEJAS', coincidiendo con el giro del negocio registrado 'Venta de Batería San Miguel'.</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>fotos/066_venta_de_bateria_san_miguel/streetview_1.jpg; fotos/066_venta_de_bateria_san_miguel/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="n"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Siddharta (Rey Poeta)</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Av. Juárez Nte. 443, Ejido de Chiconcuac, 56170 Santa María Tulantongo, Méx., México</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>19.5218771</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>-98.88203420000001</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>SIDDHARTA BATERIAS (junto a GONHER Autopartes)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>GONHER, SIDDHARTA</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Se ven numerosas baterías automotrices (cajas negras, forma característica de acumulador) apiladas en anaqueles metálicos dentro de la tienda y también en una caseta/exhibidor exterior adicional junto con productos de la marca Gonher.</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>El rótulo de la fachada dice claramente 'SIDDHARTA BATERIAS' junto con 'GONHER Autopartes', coincidiendo exactamente con el nombre registrado 'Baterías Siddharta (Rey Poeta)'; se aprecian baterías físicas apiladas en múltiples anaqueles tanto dentro del local como en la caseta exterior.</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>fotos/067_baterias_siddharta_rey_poeta/streetview_1.jpg; fotos/067_baterias_siddharta_rey_poeta/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="n"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Baterías para carros</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Av 16 de Septiembre 340, Necapa, 54879 Cuautitlán, Méx., México</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>19.6655886</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>-99.1810291</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Baterías para carros (confirmado en ficha de Google Maps)</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>LAZZARINI</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>En las fotos de la galería de Maps (subidas por el negocio, abril 2019) se ven anaqueles completos, de piso a techo, con decenas de baterías automotrices apiladas, varias con etiqueta de marca 'LAZZARINI' visible, además de carteles de precios por modelo pegados en la cortina metálica.</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Street View en las coordenadas exactas no muestra ninguna fachada relacionada (edificio de consultorio dental y trámites de pensiones, sin relación con baterías); se investigó la ficha de Google Maps del negocio 'Baterías para carros' (4.2 estrellas, 6 opiniones, categoría 'Tienda de baterías para automóvil', dirección Av 16 de Septiembre 340, Necapa, Cuautitlán, que coincide con la dirección y coordenadas registradas), cuyas fotos propias muestran anaqueles llenos de baterías físicas y cuyas reseñas mencionan 'me ayudó a cambiar mi acumulador' y 'buen precio y atención'.</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>fotos/068_baterias_para_carros/maps_foto_1.jpg; fotos/068_baterias_para_carros/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="n"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ACUMULADORES LTH SUCURSAL SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Juan Diego 667, 54810 Cuautitlán, Méx., México</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>19.6752864</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>-99.15789359999999</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH - Diagnóstico, venta e instalación / Ventas Mayoreo LTH</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>En el acercamiento de streetview_2 se ve el rótulo 'Centro de Servicio LTH Diagnóstico, venta e instalación' y 'Ventas Mayoreo LTH', con anaqueles y material de marca LTH visibles tras el cristal del local, aunque no se distinguen unidades individuales con precisión.</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 (zoom) capturó el negocio vecino 'Transmisiones/Velocímetros' sin mostrar el nombre; en streetview_2 (contexto), más adelante sobre la misma calle, se ve claramente el letrero oficial 'Centro de Servicio LTH Diagnóstico, venta e instalación' y 'Ventas Mayoreo LTH', coincidiendo con el negocio registrado 'Central de Acumuladores LTH Sucursal Santa Elena'.</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>fotos/069_central_de_acumuladores_lth_sucursal_santa_elena/streetview_1.jpg; fotos/069_central_de_acumuladores_lth_sucursal_santa_elena/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="n"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ACUMULADORES LTH SUCURSAL TLATLAYA</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Tlatlaya No.5, Centro Urbano, 54720 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>19.6609236</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>-99.2099869</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH - Diagnóstico, venta e instalación / Ventas Mayoreo LTH</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Ambas fotos muestran el letrero 'Centro de Servicio LTH Diagnóstico, venta e instalación' y toldos con 'Ventas Mayoreo LTH'; en el aparador se distingue producto de caja roja/blanca de marca LTH sobre un exhibidor.</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>El letrero de la fachada coincide exactamente con el nombre registrado 'Central de Acumuladores LTH Sucursal Tlatlaya' ('Centro de Servicio LTH Diagnóstico, venta e instalación', 'Ventas Mayoreo LTH'), con producto de marca visible en el aparador del local.</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>fotos/070_central_de_acumuladores_lth_sucursal_tlatlaya/streetview_1.jpg; fotos/070_central_de_acumuladores_lth_sucursal_tlatlaya/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="n"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS IZAGUIRRE OUTLET</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Invernadero 41, San Isidro, 54730 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>19.6592855</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>-99.2070276</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Baterias Izaguirre Outlet</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Se ven cajas de producto (baterias/protección total y motobaterías) apiladas en el mostrador anaranjado dentro del local; no se distingue marca de batería específica en el letrero, solo logos de marcas de vehículos (VW, Volvo, Mercedes-Benz, BMW, Audi) que indican compatibilidad.</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>La fachada tiene el letrero exacto 'BATERIAS IZAGUIRRE OUTLET' junto con 'AUTOPARTES Y BATERIAS' y un anuncio de 'MOTOBATERIAS', y se aprecia mostrador con productos/cajas dentro del local. Nombre y giro coinciden plenamente con el registro.</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>fotos/071_baterias_izaguirre_outlet/streetview_1.jpg; fotos/071_baterias_izaguirre_outlet/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="n"/>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES DE MEXICO SUCURSAL CUAUTITLAN</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Av 16 de Septiembre 319, Necapa, 54879 Cuautitlán, Méx., México</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>19.6661034</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>-99.1811374</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>LTH (venta de acumuladores nuevos)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>El letrero azul muestra el logo 'LTH' y el texto 'VENTA DE ACUMULADORES NUEVOS' con un icono de batería, pero la cortina metálica está cerrada al momento de la toma y no se ven baterías físicas en aparador.</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>El local marcado con el número '319' (coincide con 'Av 16 de Septiembre 319') exhibe letrero LTH con 'VENTA DE ACUMULADORES NUEVOS'; el nombre exacto registrado ('Acumuladores de Mexico sucursal Cuautitlan') no aparece en la fachada, pero el giro y la ubicación corresponden razonablemente, por lo que se prioriza la evidencia visual. Cortina cerrada en ambas tomas de Street View.</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>fotos/072_acumuladores_de_mexico_sucursal_cuautitlan/streetview_1.jpg; fotos/072_acumuladores_de_mexico_sucursal_cuautitlan/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="n"/>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS SR SANTIAGO APOSTOL</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Venustiano Carranza 1, Jorge Jimenez Cantu, 54744 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>19.62686</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>-99.22607739999999</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en las fotos de Street View disponibles (ambas tomas muestran únicamente un muro de block con grafiti, sin fachada de negocio ni producto visible).</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el Street View en las coordenadas exactas solo muestra un muro con grafiti, sin fachada ni letrero del negocio. Sin embargo, la ficha de Google Maps con el nombre EXACTO 'Baterias sr Santiago Apostol' (4.5, 4 opiniones, 'Tienda de baterías para automóvil') confirma la venta: reseñas dicen explícitamente 'me vendió la batería' y que el vendedor 'llegó a mi domicilio', consistente con un negocio de venta/instalación a domicilio. Aparece 'Cerrado temporalmente' en Maps.</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>fotos/073_baterias_sr_santiago_apostol/streetview_1.jpg; fotos/073_baterias_sr_santiago_apostol/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="n"/>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES DE MEXICO</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Cto. Bosques de Bolognia #174-Loc "B, Bosques del Lago, 54765 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>19.6163236</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>-99.23950910000001</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores de Mexico</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>Aparador con letrero 'LTH ACUMULADORES DE MÉXICO' y anuncio vertical 'BATERIA'; se distingue mercancía en anaquel dentro del local a través del cristal, en un local de la Plaza Sol.</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>Fachada con el nombre exacto 'ACUMULADORES DE MÉXICO' bajo la marca LTH y letrero 'BATERIA', en un local de Plaza Sol. Coincide plenamente con el nombre y giro registrados.</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>fotos/074_acumuladores_de_mexico/streetview_1.jpg; fotos/074_acumuladores_de_mexico/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="n"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GM SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Carr. Cuautitlán Melchor Ocampo Km. 2.5, Las Trojes, 54810 Cuautitlán, Méx., México</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>19.6746595</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>-99.1598286</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Minisuper Gus</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en la foto disponible; en las coordenadas exactas el Street View muestra una dulcería/piñatería ('Minisuper Gus'), no una tienda de baterías.</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>En las coordenadas exactas de 'Acumuladores GM Santa Elena' ambas tomas de Street View muestran un negocio distinto ('Minisuper Gus', dulces/piñatas/juguetes), sin ningún letrero, logo o producto relacionado con baterías. Por la regla del pin exacto se clasifica NO, aunque el nombre registrado sugiera una tienda de baterías.</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>fotos/075_acumuladores_gm_santa_elena/streetview_1.jpg; fotos/075_acumuladores_gm_santa_elena/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="n"/>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Acomuladores Gutiérrez</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>P.º del Bosque Mz 49-Lt 19, Bosques de Morelos, 54760 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>19.6288704</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>-99.2307077</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías físicas en las fotos de Street View (cortina metálica cerrada con letrero 'SE RENTA'); no hay fotos propias en la ficha de Maps para verificar visualmente.</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el Street View en el pin exacto muestra el local con cortina cerrada y letrero 'SE RENTA', sin nombre de negocio visible. La ficha de Google Maps para 'Acomuladores Gutiérrez' en la dirección EXACTA registrada (P.º del Bosque Mz 49-Lt 19, Bosques de Morelos, Cuautitlán Izcalli) aparece 'Abierto', con calificación 4.8 (20 opiniones) y reseñas que mencionan explícitamente 'las baterías que venden' y 'entrega a domicilio', confirmando la venta pese a que la foto disponible no la muestra.</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>fotos/076_acomuladores_gutierrez/streetview_1.jpg; fotos/076_acomuladores_gutierrez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="n"/>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GUTIÉRREZ</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Av. los Fresnos 54, Los Morales, 54800 Cuautitlán, Méx., México</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>19.6753547</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>-99.1797397</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Gutiérrez</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Anaqueles metálicos rojos con múltiples baterías LTH apiladas, visibles a través de la cortina abierta del local (foto maps_foto_1.jpg); letrero adicional menciona 'Carga de Baterías' y 'Compra de Carros [chatarra]'.</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos streetview_1/2.jpg descargadas por defecto muestran por error un asilo vecino ('Casa de Reposo Las Maravillas 2') porque el heading automático apunto a la acera de enfrente; al revisar la foto propia de Google Maps del negocio (Street View fechado jun 2024, mismo pin/dirección exacta 'Av. los Fresnos 54, Los Morales, Cuautitlán') se ve con claridad el letrero 'ACUMULADORES GUTIÉRREZ - Diagnóstico, Venta e Instalación' y baterías LTH físicas en anaquel. La ficha está 'Abierto', 4.9 (12 opiniones), y una reseña del propio dueño confirma la reubicación a esta esquina exacta.</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>fotos/077_acumuladores_gutierrez/streetview_1.jpg; fotos/077_acumuladores_gutierrez/streetview_2.jpg; fotos/077_acumuladores_gutierrez/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="n"/>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SERVICIO IZCALLI</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Av. Huehuetoca S/n, Jardines de la Hacienda, 54729 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>19.68603</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>-99.2067017</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Servicio Carrasco</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>Letrero grande 'LTH ACUMULADORES' y 'LTH - El alma de tu automóvil' en la fachada del taller; se distinguen anaqueles con productos dentro del local, junto a un cartel de 'BARBACOA' de un puesto contiguo (no relacionado).</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>El nombre en la fachada es 'Servicio Carrasco - Mecánica en general', que no coincide exactamente con el registro ('Servicio Izcalli'), pero el giro (taller que vende acumuladores LTH) y la ubicación corresponden razonablemente, por lo que se prioriza la evidencia visual: letrero prominente de venta de baterías LTH.</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>fotos/078_servicio_izcalli/streetview_1.jpg; fotos/078_servicio_izcalli/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="n"/>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GM XHALA</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>A Teoloyucan 17, San Sebastian Xhala, 54714 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>19.6849325</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>-99.1854773</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Mary (abarrotes)</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en la foto disponible; el pin exacto corresponde a una tienda de abarrotes ('Mary', con anuncio de cerveza Corona), no a una tienda de baterías.</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>En las coordenadas exactas de 'Acumuladores GM Xhala' el Street View muestra la tienda de abarrotes 'Mary', no un negocio de baterías. Se alcanza a ver, cortado, un letrero vecino '...PARTES ELÉCTRICAS Y ACCESORIOS' con logos GE/GMC, pero no coincide con el nombre registrado ni muestra baterías físicas. Por la regla del pin exacto se clasifica NO.</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>fotos/079_acumuladores_gm_xhala/streetview_1.jpg; fotos/079_acumuladores_gm_xhala/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="n"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Av. Paseo del Bosque y C. Río Lerma, Manzana 029, Colinas del Lago, 54744 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>19.6375731</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>-99.2260912</v>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>Aparador de vidrio con varias baterías LTH (cajas negras y rojas) apiladas en anaquel, junto a letrero 'LTH - Diagnóstico, venta e instalación'.</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>Fachada con el nombre exacto 'LTH' y letrero 'Centro de Servicio LTH - Diagnóstico, venta e instalación'; el aparador muestra baterías físicas de marca LTH claramente visibles.</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>fotos/080_lth/streetview_1.jpg; fotos/080_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="n"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>LTH Y DURACEL</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Hacienda El Nardo 70, Jardines de la Hacienda, 54729 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>19.6860306</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>-99.20672860000001</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>"Servicio Carrasco" (Mecánica en general, Afinaciones y Verificaciones) — no aparece literal "LTH Y DURACEL"</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>No se usaron fotos de Maps para este caso. En Street View no se ven baterías físicas apiladas en anaquel; se ve un mural pintado de una batería LTH de gran tamaño en la fachada, y productos de aceite/lubricante en el mostrador de entrada.</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>El nombre en la fachada es 'Servicio Carrasco' (mecánica/afinaciones/verificaciones), no 'LTH Y DURACEL', pero el rótulo exhibe dos veces la marca 'LTH ACUMULADORES' junto con un mural de una batería LTH. Se prioriza la evidencia visual del giro (venta/servicio de acumuladores LTH) sobre el nombre registrado, conforme a la regla de negocios con giro correspondiente.</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>fotos/081_lth_y_duracel/streetview_1.jpg; fotos/081_lth_y_duracel/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="n"/>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ACUMULADORES LTH SUCURSAL SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Centro San Miguel, Manzana 002, Jardines de San Miguel, 54715 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>19.6882738</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>-99.2133542</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>"Centro de Servicio LTH" (visible en tapete/vitrina de una foto de la propia ficha de Maps, dentro de la misma plaza)</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg muestra al menos 8 baterías físicas LTH (cajas negras con etiqueta amarilla) apiladas en un exhibidor azul de 3 niveles, junto a un póster de 'Moto-batería AGM LTH' y un tapete con el texto 'Centro de Servicio LTH'.</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto (LAT/LONG dados) muestra otros locales de la misma plaza comercial (El Punto burritos, Prestige tintorería), no el negocio registrado. Sin embargo, en la galería de fotos de esta MISMA ficha de Maps (mismo place ID) se hallaron: maps_foto_1.jpg con el rótulo 'Centro de Servicio LTH' en un local de la misma plaza, y maps_foto_2.jpg con el interior mostrando un exhibidor con múltiples baterías físicas LTH. Las reseñas de esta ficha también mencionan 'cambio de batería del auto' y garantía de batería. Se concluye SI con evidencia propia de la ficha (no de un negocio vecino distinto), aunque el encuadre por defecto de Street View no captura el local correcto dentro de la plaza.</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>fotos/082_central_de_acumuladores_lth_sucursal_san_miguel/streetview_1.jpg; fotos/082_central_de_acumuladores_lth_sucursal_san_miguel/streetview_2.jpg; fotos/082_central_de_acumuladores_lth_sucursal_san_miguel/maps_foto_1.jpg; fotos/082_central_de_acumuladores_lth_sucursal_san_miguel/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="n"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Refaccionaria Autopartes Eléctricas "León"</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Av. Paseo de Los Bosques 126, Bosques de Hacienda, 54768 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>19.6846136</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>-99.21938969999999</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en ninguna foto disponible: el Street View del pin exacto (2019 y actual) muestra un consultorio médico 'BEST' y farmacia 'LARES'. Fotos históricas (2014, 2021) de la misma ficha de Maps muestran un local real llamado 'REFACCIONARIA LEÓN' (con logos Nissan/VW/Renault) con cortina metálica cerrada, sin baterías visibles, en una dirección distinta a la del pin.</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>PIN EXACTO: en las coordenadas dadas, Street View muestra un consultorio médico 'BEST' y farmacia 'LARES', no la refaccionaria. La ficha de Maps de 'Refaccionaria Autopartes Eléctricas León' está categorizada como 'Tienda de baterías para automóvil' y tiene reseñas genéricas (buenos precios, buena atención) sin mención explícita de baterías. Una foto de archivo de esa misma ficha muestra el letrero real 'REFACCIONARIA LEÓN' pero en una dirección distinta ('Bosques Austriacos No.2', vs. 'Av. Paseo de Los Bosques 126' del Excel), sugiriendo posible reubicación o error de geocodificación. Conforme a la regla del pin exacto (el nombre no coincide en el sitio exacto de las coordenadas dadas), se clasifica NO.</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>fotos/083_refaccionaria_autopartes_electricas_leon/streetview_1.jpg; fotos/083_refaccionaria_autopartes_electricas_leon/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="n"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Las mejores baterías</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Av. 16 de Septiembre y C. Alfonso Reyes, El Partidor, 54879 Cuautitlán, Méx., México</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>19.6649814</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>-99.181158</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>"Las mejores baterías" (no visible en el pin exacto; confirmado en foto propia de la ficha de Maps en otra dirección: Av. 16 de Septiembre #335, Local 3)</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>FULL POWER, LTH</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg muestra un anaquel enrejado con al menos 6 baterías físicas de color rojo apiladas, un banner grande de la marca 'FULL POWER', y un cartel 'LTH' en la entrada del local.</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>El pin exacto (Street View) corresponde a 'Escuela Ford 79', un negocio totalmente distinto. El negocio está marcado 'Cerrado temporalmente' en Maps. Sin embargo, la galería de fotos de esta misma ficha de Maps incluye una foto del local real 'Las mejores baterías' con banner de la marca FULL POWER, cartel LTH y un anaquel con baterías físicas apiladas -- evidencia clara de venta de baterías, aunque la dirección visible en esa foto ('Local 3, Cuautitlán Centro, C.P. 54800') no coincide exactamente con la geocodificada para el pin dado (posible error de geocodificación o reubicación del negocio).</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>fotos/084_las_mejores_baterias/streetview_1.jpg; fotos/084_las_mejores_baterias/streetview_2.jpg; fotos/084_las_mejores_baterias/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="n"/>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>BATERIA MOVIL</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Insurgentes 588, Sta Maria Tianguistengo, 54710 Huilango, Méx., México</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>19.6864874</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>-99.25665960000001</v>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg muestra un taller con anaqueles metálicos que contienen al menos 12 baterías de auto usadas (una con etiqueta LTH y precio '$150' escrito a mano), además de un póster de aplicaciones automotrices LTH en la pared.</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>El pin exacto (Street View) muestra un terreno/vivienda en construcción sin negocio visible, consistente con un servicio móvil sin fachada comercial tradicional. El negocio está 'Cerrado temporalmente' en Maps y no tiene reseñas. Una foto propia de la ficha de Maps (feb 2019) muestra un taller con numerosas baterías físicas usadas en anaqueles y un póster LTH, consistente con el nombre 'Batería Móvil' (servicio de recarga/venta/intercambio a domicilio). NOTA: esta misma fotografía (idéntica) aparece también en la ficha de CASE ID 90 'Baterías vehiculares' (~5 km de distancia) -- posible duplicado de listado del mismo operador, ver evidencia de CASE ID 90.</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>fotos/085_bateria_movil/streetview_1.jpg; fotos/085_bateria_movil/streetview_2.jpg; fotos/085_bateria_movil/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="n"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES IZCALLI</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Av. Primero de Mayo Manzana 4 Lote 3, Santiago Tepalcapa, 54743 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>19.6291996</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>-99.2052961</v>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>"Acumuladores Izcalli" (confirmado en letrero iluminado nocturno en la misma esquina del Street View diurno)</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg (foto nocturna) muestra un letrero iluminado rojo/blanco de LTH con el texto 'VENTA DE BATERIAS NUEVAS Y DE USO LTH... DESDE $650', ubicado en la misma esquina/edificio que aparece en el Street View diurno (junto al negocio 'Compro fierro cartón').</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>El negocio aparece 'Cerrado permanentemente' en Maps. El Street View diurno del pin exacto sólo muestra un comprador de chatarra, una lavandería y una tienda de artículos para fiestas, sin rótulo de baterías visible de día. Una foto nocturna de esta misma ficha de Maps (feb 2025) muestra un letrero iluminado de venta de baterías LTH ('desde $650') en la misma esquina exacta del edificio, y las reseñas (4.9/11 opiniones) mencionan explícitamente 'variedad de baterías para que elijas la que más se adapta a tu presupuesto' y dejar la batería anterior a cambio. Se concluye SI pese al cierre permanente, ya que la evidencia (letrero + reseñas) confirma que el negocio SÍ vendía baterías en este sitio; se deja constancia explícita del estatus 'Cerrado permanentemente' para que el equipo decida su tratamiento en la base activa.</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>fotos/086_acumuladores_izcalli/streetview_1.jpg; fotos/086_acumuladores_izcalli/streetview_2.jpg; fotos/086_acumuladores_izcalli/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="n"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SERVICIO IZAGUIRRE</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>A Teoloyucan Mz 8-Lt 6, Ejido el Socoro, 54714 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>19.6860166</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>-99.1857029</v>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>"GONHER AUTOPARTES" / "CENTRAL VOLT" (no aparece literalmente "Servicio Izaguirre" en el rótulo, pero el giro coincide: distribuidor GONHER de autopartes y baterías)</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>GONHER</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>No se usaron fotos de Maps; evidencia en streetview_1.jpg y streetview_2.jpg: anaquel metálico con al menos 8 cajas de batería (negras con etiquetas rojas/blancas) apiladas, junto al banner 'GONHER - El experto en baterías, venta aquí, garantía'.</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>El rótulo visible dice 'GONHER AUTOPARTES' / 'CENTRAL VOLT', no 'Servicio Izaguirre', pero el giro coincide claramente: es un distribuidor GONHER con banner 'El experto en baterías - Venta aquí, X años de garantía' y un anaquel con múltiples baterías físicas apiladas, visibles con claridad en ambas fotos de Street View. Se prioriza la evidencia visual del giro sobre el nombre registrado.</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>fotos/087_servicio_izaguirre/streetview_1.jpg; fotos/087_servicio_izaguirre/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="n"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>"VIC" ACUMULADORES CUAUTITLAN IZCALLI, JACARANDAS</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Jacarandas Mz.105, Lomas del Bosque, 54760 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>19.6178873</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>-99.23745889999999</v>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>"...ACUMULADORES" (parcialmente visible junto a "Diagnóstico con scanner"), adyacente a la vulcanizadora "El Gallo"</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg (foto nocturna) muestra, junto a la vulcanizadora 'El Gallo', un local con rótulo '...ACUMULADORES' y 'Diagnóstico con scanner', con un anaquel metálico tras una reja verde donde se aprecian al menos 6 cajas de batería físicas, cajas azules 'LTH' apoyadas en el suelo, y letreros 'CARGA DE BATERIAS' y 'COMPRAMOS BATERIAS VIEJAS $200'.</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>El Street View diurno del pin exacto sólo encuadra la vulcanizadora 'El Gallo' (reparación de llantas/rines de Raúl Grande Castillo), sin mostrar el negocio de baterías contiguo. Una foto nocturna de esta misma ficha de Maps confirma que, en el mismo edificio/cuadra, existe un local con rótulo '...ACUMULADORES', anaquel con baterías físicas visibles, y letreros de carga/compra de baterías -- evidencia clara de venta de baterías en el sitio exacto, aunque el nombre completo 'VIC' no se distingue por estar parcialmente tapado en la foto disponible.</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>fotos/088_vic_acumuladores_cuautitlan_izcalli_jacarandas/streetview_1.jpg; fotos/088_vic_acumuladores_cuautitlan_izcalli_jacarandas/streetview_2.jpg; fotos/088_vic_acumuladores_cuautitlan_izcalli_jacarandas/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="n"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SERVICIO DURACELL TEPALCAPA</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Av. Adolfo Lopez Mateos 82, Santiago Tepalcapa, 54748 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>19.6237859</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>-99.1961965</v>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2" t="n"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: no hay fotos de Maps disponibles para este negocio (la ficha no tiene fotos subidas por usuarios, sólo capturas de Street View). No se aprecian baterías en ninguna imagen disponible.</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el pin exacto (Street View, incluyendo una segunda captura de la misma ficha con más contexto y rotación del panorama) muestra una tienda de pinturas AXALTA y una dulcería contigua, sin ningún rótulo de 'Duracell' ni de baterías. La ficha de Maps no tiene reseñas ni fotos adicionales subidas por usuarios que permitan confirmar la venta de baterías en el sitio exacto. Conforme a la regla del pin exacto (el nombre no coincide en el sitio exacto), se clasifica NO.</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>fotos/089_servicio_duracell_tepalcapa/streetview_1.jpg; fotos/089_servicio_duracell_tepalcapa/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="n"/>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Baterías vehiculares</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Temoaya 17, Centro Urbano, 54700 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>19.6530185</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>-99.2061058</v>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg muestra un taller con anaqueles metálicos con al menos 12 baterías de auto usadas (una con etiqueta LTH) y un póster de aplicaciones automotrices LTH en la pared.</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>El pin exacto (Street View) muestra la entrada de un estacionamiento/edificio ('Círculo Doro') y un local 'El Tarjetón', sin relación con baterías. El negocio está 'Cerrado temporalmente' en Maps y no tiene reseñas. La única foto disponible en la ficha de Maps muestra un taller con numerosas baterías físicas usadas, pero es EXACTAMENTE la misma fotografía (mismos píxeles, mismo tamaño de archivo) que aparece en la ficha de 'Batería móvil' (CASE ID 85), ubicada a ~5 km de distancia. Esto sugiere que ambas fichas podrían ser duplicados de un mismo operador/taller de servicio móvil de baterías, o una reutilización de foto entre listados -- se deja como hallazgo aparte para que el equipo revise si son el mismo negocio duplicado. Con la evidencia disponible (baterías físicas reales en la foto asociada a esta ficha de Maps) se concluye SI, con la salvedad explícita de la foto duplicada.</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>fotos/090_baterias_vehiculares/streetview_1.jpg; fotos/090_baterias_vehiculares/streetview_2.jpg; fotos/090_baterias_vehiculares/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="n"/>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>ENERGIZER SUPPLY CHAIN MEXICO</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Politécnico 42, San Jose, 54870 Cuautitlán, Méx., México</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>19.6594596</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>-99.1750213</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en las fotos disponibles; solo se ve el portón y la caseta de acceso de un predio industrial cercado, sin producto ni rótulos visibles.</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: las dos fotos de Street View en las coordenadas exactas solo muestran el portón/caseta de vigilancia de un predio industrial cercado, sin ningún rótulo con el nombre del negocio ni producto visible. La ficha de Maps de 'ENERGIZER SUPPLY CHAIN MEXICO' no tiene reseñas ni fotos adicionales a la misma toma de Street View, y su sitio asociado (energizer.lat) es corporativo. Google la clasifica como 'Tienda de baterías', pero todo indica que es un centro de distribución/logística de Energizer, no un punto de venta al público verificable con la evidencia disponible. Se deja PENDIENTE por evidencia insuficiente.</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>fotos/091_energizer_supply_chain_mexico/streetview_1.jpg; fotos/091_energizer_supply_chain_mexico/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="n"/>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>La Güera</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Torre Omega 1057, Sta Maria Guadalupe las Torres, 54743 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>19.6304699</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>-99.21676069999999</v>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>La Güera</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías; la fachada solo muestra el rótulo 'COMPRA Y VENTA D° DESPERDICIO' (cartón, cristales, cobre, PET) y una cortina metálica cerrada cubierta de grafiti.</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'La Güera' coincide exactamente con la fachada en las coordenadas exactas (Torre Omega, Sta Maria Guadalupe las Torres), pero el rótulo visible corresponde a un negocio de compra/venta de desperdicio industrial (cartón, cobre, PET, vidrio), no de baterías, y el local está cerrado. La única reseña en Maps (5 estrellas, sin texto) no aporta evidencia de venta de baterías, y no hay fotos adicionales en la galería.</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>fotos/092_la_guera/streetview_1.jpg; fotos/092_la_guera/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="n"/>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>PLUS POWER</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Av Villa del Carbón 10, Loma de Los Angeles, Loma de los Angeles, 54710 Cuautitlán Izcalli, Méx., México</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>19.6734701</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>-99.2345021</v>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>PLUS POWER</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>Foto de interior de la galería de Maps muestra un mostrador enrejado con aproximadamente 10-12 baterías apiladas, marcas LTH y America identificables en las etiquetas, además de aceites y accesorios en anaqueles contiguos.</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto muestra una tienda de ropa de bebé ('Safari Bebé') sin relación aparente, pero la propia ficha de Maps de 'Plus power' (marcada 'Cerrado temporalmente') tiene fotos subidas por el negocio: la fachada real dice 'PLUS POWER - CARGA DE BATERIAS' y el interior muestra un mostrador con baterías LTH y America apiladas. Se prioriza esta evidencia directa de la ficha sobre el Street View; el estatus 'cerrado temporalmente' no descalifica el veredicto según las reglas del proyecto.</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>fotos/093_plus_power/streetview_1.jpg; fotos/093_plus_power/streetview_2.jpg; fotos/093_plus_power/maps_foto_1.jpg; fotos/093_plus_power/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="n"/>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES OMEGA</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>MEX 6 20, Tepanquiahuac, 54713 Teoloyucan, Méx., México</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>19.7323286</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>-99.1849289</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Omega, America, LTH</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>Foto de interior de la galería de Maps muestra un exhibidor con al menos 8 baterías nuevas apiladas: varias con empaque naranja/negro de marca OMEGA, y baterías adicionales con etiquetas LTH y America en el piso junto al exhibidor.</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto muestra un restaurante ('El Jaliciense') y una manta de Al-Anon, sin relación con 'Acumuladores Omega', pero la propia ficha de Maps del negocio (4.4 estrellas, 8 reseñas, sitio web acumomega.com.mx) tiene una foto de interior que muestra un exhibidor lleno de baterías marca OMEGA, America y LTH, y reseñas que confirman instalación de batería y diagnóstico de auto ('Me instalaron mi batería y me escanearon el carro'). Se prioriza esta evidencia directa de la ficha del negocio sobre el Street View, que aparentemente capturó un ángulo/edificio distinto de la cuadra.</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>fotos/094_acumuladores_omega/streetview_1.jpg; fotos/094_acumuladores_omega/streetview_2.jpg; fotos/094_acumuladores_omega/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="n"/>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH SUC. ARBOLEDAS</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Calz. de los Jinetes 26-Loc 1, Las Arboledas, 54026 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>19.5555228</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>-99.2130229</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH Las Arboledas</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Super Battery</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>Foto de fachada de la galería de Maps muestra un letrero colgante 'Las mejores baterías de venta aquí - Super Battery' y un cartel tipo caballete 'SUPER BATTERY DE VENTA AQUI - LTH'; no se distingue un mostrador con baterías físicas apiladas en esta toma, que corresponde a la bahía de servicio/diagnóstico.</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>Las dos fotos de Street View en el pin exacto están bloqueadas/mal encuadradas (primer plano de un portón naranja, sin valor alguno), pero la ficha de Maps 'Centro de Servicio LTH Las Arboledas' (5.0 estrellas, 770 reseñas, sitio bateriaslthmexico.com.mx) tiene una foto de fachada clara con el rótulo 'Centro de Servicio LTH - Diagnóstico, venta e instalación' y el cartel 'Las mejores baterías de venta aquí'. Cientos de reseñas confirman compra/cambio de batería con excelente servicio.</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>fotos/095_centro_de_servicio_lth_suc_arboledas/streetview_1.jpg; fotos/095_centro_de_servicio_lth_suc_arboledas/streetview_2.jpg; fotos/095_centro_de_servicio_lth_suc_arboledas/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="n"/>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ACOMULADORES</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Av. Vía Morelos esquina con Pachuca - Mexico 45, Urbana Ixhuatepec, 55349 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>19.5241694</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>-99.08700279999999</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Fixtec</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra un anaquel/mostrador junto a la entrada con cajas de baterías apiladas y un cartel de producto de marca FIXTEC junto a la puerta; el logo de batería ilustrado en la parte alta de la fachada tiene el texto de marca cubierto por banderines decorativos y no es legible con certeza (posible 'Anzures', no se fuerza la lectura).</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>El nombre y giro coinciden perfectamente en Street View en el pin exacto: fachada con rótulo 'CENTRAL DE ACUMULADORES' y 'ACUMULADORES', logo de batería ilustrado, marca FIXTEC visible junto a la puerta, mostrador con cajas de batería apiladas, y un banner 'SE COMPRAN BATERIAS USADAS'. Evidencia clara y directa en el sitio exacto, sin necesidad de revisar Maps.</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>fotos/096_central_de_acomuladores/streetview_1.jpg; fotos/096_central_de_acomuladores/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="n"/>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS CAR-SO 2</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Av Valle del Jucar 101, Valle de Aragon 3ra Secc, 55280 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>19.5048535</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>-99.0374924</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS CAR-SO 2</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías físicas apiladas en la foto disponible (fachada con cortina metálica cerrada); la evidencia de producto es el mural pintado con dos baterías marca LTH y el banner 'NUEVAS Y SEMINUEVAS LTH - CENTRO DE DISTRIBUCION'.</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto muestra un taller mecánico general ('Afinaciones, Scanner, Amortiguadores, Rótulas, Baleros') sin relación aparente con baterías, pero la propia ficha de Maps de 'Baterias CAR-SO 2' (5.0 estrellas, 8 reseñas) tiene una foto de fachada con el mural 'BATERIAS CAR-SO 2' y dos baterías LTH pintadas, más un banner 'Centro de Distribución LTH - Nuevas y Seminuevas'. Varias reseñas confirman explícitamente venta de baterías nuevas y seminuevas con garantía y entrega a domicilio.</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>fotos/097_baterias_car_so_2/streetview_1.jpg; fotos/097_baterias_car_so_2/streetview_2.jpg; fotos/097_baterias_car_so_2/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="n"/>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FIGUEROA</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>206 Mexico 85, Tulpetlac, 55080 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>19.574397</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>-99.042635</v>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías físicas apiladas en la foto disponible; la evidencia de producto es la bandera/banner 'DE VENTA AQUI' con logo LTH junto a la entrada de la bahía de servicio, y el letrero de recepción de 'baterías usadas'.</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto muestra el rótulo 'Centro de Servicio LTH' en vez del nombre registrado 'Acumuladores Figueroa', pero la ficha de Maps de este mismo pin (4.8 estrellas, 517 reseñas) tiene como sitio web oficial 'acumuladoresfigueroa.com', confirmando que es el mismo negocio operando bajo el rótulo de servicio autorizado LTH ('Centro de Servicio LTH suc. Ecatepec'). Reseñas detalladas confirman venta e instalación de baterías con variedad de marcas y precios competitivos.</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>fotos/098_acumuladores_figueroa/streetview_1.jpg; fotos/098_acumuladores_figueroa/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="n"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS PARA AUTO LTH AMERICA FULL POWER</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>C. Morelos 34, Llano de Morelos 1, 55070 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>19.6101575</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>-99.0091302</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES SINTERGIA</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America, Full Power</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>Foto de fachada muestra un mostrador/pizarra de precios con múltiples baterías etiquetadas (marca LTH visible en varias etiquetas) bajo un banner 'CARGA DE BATERIAS, VENTA DE ACIDO, VENTA DE TERMINALES'; el letrero superior de la tienda exhibe tres baterías fotografiadas de las marcas FULL POWER, AMERICA y LTH (dos presentaciones).</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto muestra el rótulo 'ACUMULADORES SINTERGIA' en vez del nombre registrado 'Baterias para Auto LTH America Full Power', pero el giro coincide de forma extraordinaria: el letrero exhibe exactamente baterías de las marcas LTH, America y Full Power (las tres mencionadas en el nombre registrado), y hay un mostrador con precios de baterías LTH. Reseñas de Maps confirman 'excelente calidad en baterías' y servicio a domicilio.</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>fotos/099_baterias_para_auto_lth_america_full_power/streetview_1.jpg; fotos/099_baterias_para_auto_lth_america_full_power/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="n"/>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>ACEVEDO DISTRIBUIDOR DE ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Av. Gobernador Lic. Ignacio Pichardo Pagaza 47, Cd Amanecer, 55269 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>19.5099344</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>-99.022374</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>ACEVEDO - DISTRIBUIDOR DE ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra un mostrador de entrada con baterías LTH nuevas apiladas, un cartel 'ACUMULADOR NUEVO $950' con batería LTH ilustrada, y un rótulo grande de batería LTH tipo moto en la fachada superior junto a 'MOTO-BATERIA LTH'.</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>El nombre y giro coinciden perfectamente en Street View en el pin exacto: fachada con rótulo 'DISTRIBUIDOR DE ACUMULADORES' y 'ACUMULADORES...VECC' (Acevedo), baterías LTH ilustradas y físicas visibles en el mostrador de entrada con precios, y banners de garantía LTH ('Baterías de servicio pesado'). Evidencia clara y directa en el sitio exacto.</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>fotos/100_acevedo_distribuidor_de_acumuladores/streetview_1.jpg; fotos/100_acevedo_distribuidor_de_acumuladores/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="n"/>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Venta De Baterias De Gel Y Ácido.</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Vía Adolfo López Mateos 232, Jardines de Santa Clara, 55450 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>19.5437535</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>-99.0379262</v>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>¿Te quedaste sin batería? Venta de Baterías de Gel (banner del negocio, foto de Maps)</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Extrema, Cronos</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel amarillo con al menos 15-20 baterías nuevas visibles (marcas LTH, Extrema, Cronos apiladas), bajo un banner grande que anuncia 'Venta de baterías de gel'.</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>El Street View automático en las coordenadas exactas capturó por casualidad el negocio vecino (Fumigaciones Soto, sin relación); sin embargo la foto oficial de la propia ficha de Google Maps de este negocio muestra un banner claro '¿Te quedaste sin batería? Venta de Baterías de Gel - Somos tu solución en baterías' con anaquel lleno de baterías LTH/Extrema/Cronos y el domicilio coincide (Vía Adolfo López Mateos 231 vs 232 registrado). Categoría de Maps: 'Tienda de baterías para automóvil', reseñas confirman buen servicio y producto.</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>fotos/101_venta_de_baterias_de_gel_y_acido/streetview_1.jpg; fotos/101_venta_de_baterias_de_gel_y_acido/streetview_2.jpg; fotos/101_venta_de_baterias_de_gel_y_acido/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="n"/>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES Y REFACCIONES ELECTRICAS "JHONNY"</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Av. Jardines de Morelos 581, Jardines de Morelos, 55070 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>19.5959498</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>-98.9954736</v>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "JHONNY"</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>No se descargó foto adicional de Maps; en Street View se ve un letrero de 'COMPRA Y VENTA DE BATERIAS' con ilustraciones de distintos tipos/tamaños de acumuladores, y un banner LTH.</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>Street View (ambas tomas) muestra claramente el rótulo 'ACUMULADORES JHONNY' en la fachada junto con un banner LTH y un letrero de compra/venta de baterías con tabla de tipos. El nombre coincide exactamente con el registrado.</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>fotos/102_acumuladores_y_refacciones_electricas_jhonny/streetview_1.jpg; fotos/102_acumuladores_y_refacciones_electricas_jhonny/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="n"/>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES HERNANDEZ PERDIDO</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Valle Perdido 86, Valle de Aragon 3ra Secc, 55280 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>19.5070295</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>-99.04393899999999</v>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES KEVINCHO (nombre en banner de Maps; distinto al registrado 'Hernandez Perdido')</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>LTH, HTJ, América Racing</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>Banner amarillo con dos baterías ilustradas (logos LTH y HTJ) y texto 'Nuevas y 1/2 uso, Garantizadas, Carga de baterías, Diagnóstico gratis'; bajo la cortina se ven pósters de baterías América Racing (varias unidades) y LTH pegados sobre la reja.</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>La foto oficial de Maps muestra un banner de 'Acumuladores Kevincho' (nombre distinto al registrado 'Hernandez Perdido') pero el giro coincide exactamente (venta de baterías LTH/HTJ/América Racing) y la dirección coincide de forma exacta (Valle Perdido 86, Valle de Aragón 3ra Secc). El Street View en el pin exacto también muestra, en el borde del encuadre, un letrero parcial '...ULADORES HERN...' con logo LTH, consistente con el mismo giro/ubicación. Reseñas de Maps confirman buen precio y servicio comprando 'acumulador'. Se prioriza la evidencia visual y de giro sobre el nombre exacto, como indican las reglas del proyecto.</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>fotos/103_acumuladores_hernandez_perdido/streetview_1.jpg; fotos/103_acumuladores_hernandez_perdido/streetview_2.jpg; fotos/103_acumuladores_hernandez_perdido/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O104" s="3" t="n"/>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS CAR -SO</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Av. Acero MZ. 20, Lote 4, San Andres Ocotlan, Poligono 2, 55187 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>19.5164157</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>-99.01896050000001</v>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS CAR-SO</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías físicas en la foto (las dos cortinas metálicas están cerradas), pero se ven tres logos LTH pintados en las cortinas y el texto 'Carga, Compra y Venta' junto al nombre del negocio.</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'BATERIAS CAR-SO' aparece pintado directamente en la cortina metálica del local junto con tres logos LTH grandes y el texto 'Carga Compra y Venta'. Coincide exactamente con el nombre y domicilio registrados. Reseñas de Maps (10 opiniones, 5.0 estrellas) mencionan explícitamente la compra de baterías -incluso para ambulancias- y entrega a domicilio, confirmando el giro pese a que el local estaba cerrado (cortina abajo) al momento de la foto.</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>fotos/104_baterias_car_so/streetview_1.jpg; fotos/104_baterias_car_so/streetview_2.jpg; fotos/104_baterias_car_so/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O105" s="3" t="n"/>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Tienda de Baterías " Energy "</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cvln. Sur 49a, Jardines de Casa Nueva, 55430 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>19.548113</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>-99.04444460000001</v>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>América Racing</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>No se descargó foto adicional de Maps (la ficha solo tiene Street View); en el aparador se ven anaqueles con cajas rectangulares oscuras apiladas, compatibles con acumuladores, bajo el rótulo 'América Racing', aunque el logo de marca de cada caja no se distingue con nitidez en la resolución disponible.</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el nombre 'ENERGY' coincide con la fachada visible en Street View y hay anaqueles de producto bajo el letrero 'América Racing', pero no se distingue con total claridad si las cajas del anaquel son baterías u otras refacciones eléctricas en la resolución disponible. El veredicto SI se sostiene principalmente en que la ficha de Maps categoriza el negocio como 'Tienda de baterías para automóvil' y una reseña reciente (hace 7 meses) dice explícitamente: 'Muy buenos precios... tienen variedad de marcas y te dan opciones para tu coche', confirmando la venta de baterías en este domicilio exacto (Av. Cvln. Sur Mz 73 Lote 47).</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>fotos/105_tienda_de_baterias_energy/streetview_1.jpg; fotos/105_tienda_de_baterias_energy/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O106" s="3" t="n"/>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MORENO</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Av. Carlos Hank González Mz229Lt30, Cd Azteca 2da Secc, 55120 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>19.5440719</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>-99.02398340000001</v>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MORENO</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>América, LTH, Gonher</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel completo con al menos 15 baterías visibles de marcas América, LTH y Gonher, y un cartel de 'SE COMPRAN BATERIAS' con lista de precios por tipo/tamaño (desde $100 hasta $600).</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>La foto oficial de la ficha de Maps muestra el rótulo 'ACUMULADORES MORENO' pintado en amarillo sobre el local, coincidiendo exactamente con el nombre registrado, con anaqueles llenos de baterías de varias marcas y letreros de compra/venta con precios. El Street View en el pin exacto mostró en cambio la cortina cerrada de una vivienda sin rótulo visible (posible desfase de encuadre respecto al local real, a unos metros); la ficha de Maps confirma la ubicación exacta (Cd. Azteca 2da Secc) y varias reseñas mencionan explícitamente 'baterías de uso', garantía de 2 meses y varias sucursales.</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>fotos/106_acumuladores_moreno/streetview_1.jpg; fotos/106_acumuladores_moreno/streetview_2.jpg; fotos/106_acumuladores_moreno/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O107" s="3" t="n"/>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LTH</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>C. 3 187, Jardines de Santa Clara, 55450 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>19.5476371</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>-99.04334660000001</v>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>BRAKEZONE / CHEVROLET (no se ve 'Acumuladores LTH' ni ningún logo LTH)</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en ninguna foto disponible: ni en nuestro Street View (fov 50 y 90) ni en la miniatura oficial que la propia ficha de Maps de 'Acumuladores LTH' usa como foto principal (mismo panorama de Street View, verificado por panoid). El aparador muestra piezas de freno 'Brakezone' y accesorios Chevrolet/GM/ACDelco/Hummer, sin ningún rótulo o logo de batería.</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION / PIN EXACTO: tanto nuestras fotos de Street View como la miniatura que la propia ficha de Maps usa (mismo panoid confirmado vía inspección del código de la página) muestran en las coordenadas exactas (19.5476371,-99.0433466) un negocio de autopartes 'Brakezone' + accesorios Chevrolet/GM, sin ningún rastro de LTH ni de baterías. Esto contradice varias reseñas de la misma ficha (algunas de hace ~1 año) que describen haber comprado un 'acumulador' con buen servicio, y la categoría de Maps que indica 'Tienda de baterías para automóvil' con estatus 'Abierto'. Es posible que el negocio de baterías haya cerrado o cambiado de giro recientemente y Maps no lo haya actualizado, pero no hay evidencia visual actual de venta de baterías en el sitio exacto. Aplicando la regla del PIN exacto del proyecto (el Street View en las coordenadas exactas no muestra el nombre/giro de baterías), se clasifica NO; se deja constancia de la reseña contradictoria para que el equipo lo revise por si el negocio se reubicó dentro del mismo predio.</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>fotos/107_acumuladores_lth/streetview_1.jpg; fotos/107_acumuladores_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O108" s="3" t="n"/>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "SANTIAGO"</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Av. José López Portillo 43-Loc.3, San Cristóbal, 55024 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>19.6127736</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>-99.0599409</v>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "SANTIAGO"</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>No se descargó foto adicional de Maps; en Street View se ve el anaquel de la tienda con productos LTH y el texto 'EQUIPO PESADO' junto al logo de la marca.</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>Street View (ambas tomas) muestra el rótulo 'ACUMULADORES SANTIAGO' pintado en la barda junto al logo LTH y el texto 'EQUIPO PESADO', con anaquel de producto LTH visible dentro del local. El nombre coincide exactamente con el registrado.</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>fotos/108_acumuladores_santiago/streetview_1.jpg; fotos/108_acumuladores_santiago/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O109" s="3" t="n"/>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Baterías vehiculares</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Av. Nacional 9, Santa Cruz Venta de Carpio, 55065 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>19.6216521</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>-99.0013111</v>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>No se ve el nombre 'Baterías Vehiculares' en la fachada exterior (el frente visible es de 'Autoalarmas' / Kicker / JBL Car Audio)</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>LTH, TT2</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>Foto interior subida a la ficha de Maps muestra un anaquel largo con más de 15 baterías usadas apiladas (marca LTH identificable en una de ellas, así como una batería de marca TT2), además de un póster de aplicaciones automotrices LTH en la pared.</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>La fachada exterior visible en Street View (coordenadas exactas) corresponde a un negocio de alarmas y audio para auto ('Autoalarmas', Kicker, JBL Car Audio), sin ningún rótulo de baterías. Sin embargo, una foto interior subida a la ficha de Maps de 'Baterías Vehiculares' (mismo domicilio en Santa Cruz Venta de Carpio) muestra con claridad un anaquel repleto de baterías usadas, incluida una marca LTH y un póster de aplicaciones LTH, evidencia de que el giro de baterías se opera puertas adentro del mismo inmueble aunque el aparador visible desde la calle sea de audio/alarmas. La ficha aparece marcada 'Cerrado temporalmente' en Maps, lo cual no descalifica el giro según las reglas del proyecto.</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>fotos/109_baterias_vehiculares/streetview_1.jpg; fotos/109_baterias_vehiculares/streetview_2.jpg; fotos/109_baterias_vehiculares/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O110" s="3" t="n"/>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MARTE</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>C. Marte 5, Estrella, 55210 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>19.5189298</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>-99.0430314</v>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>No aparece literalmente el nombre 'Acumuladores Marte' en un rótulo; el local visible a nivel de calle es 'Estética &amp; Barbería La Jaula de las Locas'</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Duralast, ACDelco, América Racing</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel verde con al menos 15 baterías nuevas de varias marcas (LTH, Duralast, ACDelco, América Racing) y banner 'FUERZA EN SU MAXIMA POTENCIA' de América Racing; en la calle, junto a la Estética, hay un banner independiente 'Venta de Baterías, Autos y Motos, Nuevas y Usadas' con logo LTH y un letrero azul 'LTH - De venta aquí'.</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>El Street View muestra, en el mismo predio de C. Marte 5 (dirección idéntica a la registrada), un letrero azul con logo LTH ('De venta aquí') y un banner naranja de 'Venta de Baterías, autos y motos, nuevas y usadas'. La foto oficial de Maps para 'Acumuladores Marte' (misma dirección exacta, reseña reciente de hace 3 días) muestra además un anaquel completo de baterías de varias marcas. El nombre 'Marte' no se lee en un rótulo comercial, pero el giro (venta de baterías LTH) y la ubicación coinciden exactamente con lo registrado, por lo que se prioriza la evidencia visual sobre la falta de rótulo con el nombre exacto.</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>fotos/110_acumuladores_marte/streetview_1.jpg; fotos/110_acumuladores_marte/streetview_2.jpg; fotos/110_acumuladores_marte/maps_foto_1.jpg; fotos/110_acumuladores_marte/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O111" s="3" t="n"/>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ARRIAGA</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Nte. 15 62, San Carlos, 55080 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>19.5797841</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>-99.0487174</v>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ARRIAGA</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América, Duralast, Checker</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>La foto propia del negocio en Maps (fechada 2023/5/26) muestra el interior de la tienda con anaqueles metálicos repletos de baterías físicas de las marcas LTH, América, Duralast y Checker, más un letrero de 'BATERIAS NUEVAS CHECKER $999' y un banner 'ACUMULADORES ARRIAGA - LTH - LA FUERZA DE TU AUTOMÓVIL'.</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas solo muestra la cortina metálica cerrada del local, sin letrero legible (posible cierre momentáneo al pasar la cámara). Sin embargo, la foto propia del negocio en su ficha de Maps (mismo place ID que el link registrado, fechada 2023/5/26) muestra con total claridad el rótulo 'ACUMULADORES ARRIAGA' y anaqueles llenos de baterías físicas de varias marcas. Las reseñas mencionan 'diagnóstico, opciones de compra' y preguntan si 'cargan baterías', consistente con una tienda de baterías activa en ese domicilio.</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>fotos/121_acumuladores_arriaga/streetview_1.jpg; fotos/121_acumuladores_arriaga/streetview_2.jpg; fotos/121_acumuladores_arriaga/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O112" s="3" t="n"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES INSURGENTES</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Av. Insurgentes 28, El Calvario, 55020 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>19.6046026</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>-99.0586461</v>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías físicas en ninguna foto disponible. El Street View en el pin exacto muestra un negocio de 'Aluminio y Cristal' sin relación, y la única foto 'del propietario' en Maps (feb 2025) es una toma genérica de la calle donde se ve de fondo ese mismo negocio de aluminio, sin mostrar baterías.</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el Street View en las coordenadas exactas muestra 'TODO EN ALUMINIO Y CRISTAL', un negocio distinto sin baterías visibles, y no existe ninguna foto de la ficha de Maps que muestre baterías físicas en este domicilio. Sin embargo, la ficha de Maps 'ACUMULADORES INSURGENTES' (nombre exacto, mismo place ID que el link registrado) tiene una reseña de cliente ('venden baterías en mal estado') con respuesta oficial del propietario que confirma explícitamente: 'VENDEMOS BATERIAS NUEVAS DE LAS CUALES SE LE DA UNA POLIZA DE GARANTIA'. Esta es evidencia textual directa de la propia ficha del negocio de que sí vende baterías, aunque el pin de ubicación parece estar mal colocado (aparentemente comparte cuadra con un negocio de aluminio y cristal).</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>fotos/122_acumuladores_insurgentes/streetview_1.jpg; fotos/122_acumuladores_insurgentes/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O113" s="3" t="n"/>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>BATERÍAS PARA AUTO LTH</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Calle Bosque De San Marcos, Jardines de Morelos, 55070 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>19.5950868</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>-99.0021826</v>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES SINTERGIA</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing, Xtreme</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de Maps muestran un aparador con anaqueles metálicos repletos de baterías físicas de las marcas LTH, América Racing y Xtreme desde el piso hasta el techo, además de un despliegue individual de producto (batería Xtreme XT-42, América Racing y LTH) sobre un mostrador con accesorios de terminal.</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas registradas muestra un negocio de maderas/molduras sin relación alguna con baterías. Sin embargo, la ficha de Maps abierta con el link exacto del registro ('BATERÍAS PARA AUTO LTH', mismo place ID) tiene fotos propias del negocio que muestran el rótulo real 'ACUMULADORES SINTERGIA - BATERIAS - LA ENERGIA QUE NECESITA TU MOTOR' con anaqueles repletos de baterías físicas de varias marcas. El nombre visible en fachada difiere del registrado, pero el giro y la evidencia visual de venta de baterías son inequívocos, por lo que se prioriza la evidencia visual sobre el nombre registrado.</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>fotos/123_baterias_para_auto_lth/streetview_1.jpg; fotos/123_baterias_para_auto_lth/streetview_2.jpg; fotos/123_baterias_para_auto_lth/maps_foto_1.jpg; fotos/123_baterias_para_auto_lth/maps_foto_2.jpg; fotos/123_baterias_para_auto_lth/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O114" s="3" t="n"/>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Av. Fuego Nuevo 70, Cd Azteca 2da Secc, 55450 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>19.5484092</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>-99.0330062</v>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>Ambas fotos de Street View muestran un aparador rojo con múltiples baterías físicas de color negro apiladas en varios niveles; las etiquetas de marca no son legibles con suficiente nitidez en la imagen para identificarlas con certeza.</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra con claridad el letrero 'ACUMULADORES FUEGO NUEVO', coincidiendo exactamente con el nombre registrado, junto con el texto 'VENTA DE TERMINALES, ACIDO, CHEQUEO POR SCANNER' y un aparador con baterías físicas visibles en ambas tomas.</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>fotos/124_acumuladores_fuego_nuevo/streetview_1.jpg; fotos/124_acumuladores_fuego_nuevo/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O115" s="3" t="n"/>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES CAMILA</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Vía Adolfo López Mateos 2062, El Cegor, 55127 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>19.5397658</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>-99.0409576</v>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES CAMILA</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing, EverStart, ACDelco, Dynamo, CAR 100</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de Maps muestran anaqueles metálicos repletos de baterías físicas de las marcas LTH, América Racing, EverStart, ACDelco, Dynamo y CAR 100, bajo el rótulo 'ACUMULADORES CAMILA - LTH - CARGA Y VENTA - NUEVAS Y SEMINUEVAS' pintado sobre la cortina de entrada.</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra una fachada azul con un letrero distinto e ilegible que no corresponde a una tienda de baterías. Sin embargo, las fotos propias del negocio en su ficha de Maps muestran con total claridad el rótulo 'ACUMULADORES CAMILA', coincidiendo exactamente con el nombre registrado, y anaqueles llenos de baterías físicas de múltiples marcas.</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>fotos/125_acumuladores_camila/streetview_1.jpg; fotos/125_acumuladores_camila/streetview_2.jpg; fotos/125_acumuladores_camila/maps_foto_1.jpg; fotos/125_acumuladores_camila/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O116" s="3" t="n"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Centro Distribución LTH</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Circunvalación Sur esquina Zihuatanejo 2, Jardines de Casa Nueva, 55430 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>19.5489461</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>-99.04530560000001</v>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Distribución LTH</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>Ambas fotos muestran el rótulo 'LTH - Centro de Distribución - BATERIAS' y una máquina expendedora de la marca LTH con gráfico de batería en la fachada; no se aprecia un mostrador abierto con baterías físicas apiladas, sino el punto de venta/distribución y la máquina de autoservicio.</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra el letrero 'LTH - Centro de Distribución - BATERIAS', coincidiendo con el nombre registrado 'Centro Distribución LTH', junto con una máquina expendedora de baterías LTH instalada en la fachada del local.</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>fotos/126_centro_distribucion_lth/streetview_1.jpg; fotos/126_centro_distribucion_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O117" s="3" t="n"/>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "MORENO"</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Vía Adolfo López Mateos 3295, Miguel Hidalgo, 55490 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>19.5339204</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>-99.0464537</v>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>MORENO (Acumuladores Moreno)</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>Ambas fotos de Street View muestran un anaquel amarillo/azul con múltiples baterías físicas apiladas bajo el rótulo 'MORENO BATERIAS de GEL-1000', junto con una lista de precios por tamaño (mini, chica, mediana, tornillo, camión); no se distinguen logos de marcas de terceros, solo la marca propia del negocio.</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra con claridad el nombre 'MORENO', coincidiendo con el registrado 'ACUMULADORES MORENO', con baterías físicas visibles en el anaquel y letreros de 'SE COMPRAN BATERIAS' y lista de precios de baterías por tamaño.</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>fotos/127_acumuladores_moreno/streetview_1.jpg; fotos/127_acumuladores_moreno/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O118" s="3" t="n"/>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MARTINEZ</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Av. Insurgentes 148, El Calvario, 55020 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>19.6028217</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>-99.0569216</v>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en ninguna foto disponible; el Street View muestra un letrero de 'RÓTULOS - TOLDOS FIJOS Y ENROLLABLES', un laboratorio/consultorio médico y una tienda de artículos de fiesta ('Mi Lugar Favorito'), sin relación alguna a baterías.</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas no muestra el nombre 'Acumuladores Martinez' ni ningún negocio de baterías; en su lugar aparecen un taller de rótulos/toldos y un laboratorio médico. La ficha de Maps no tiene fotos propias del negocio ni reseñas, y el negocio aparece marcado como 'Cerrado temporalmente'. No hay evidencia visual ni textual disponible que confirme venta de baterías en este domicilio.</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>fotos/128_acumuladores_martinez/streetview_1.jpg; fotos/128_acumuladores_martinez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O119" s="3" t="n"/>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Baterías "El Gabo"</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Av Acueducto 47, Jorge Jimenez Cantu, 54190 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>19.5335734</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>-99.0904464</v>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS EL GABO</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Mopar, Kirkland, América Racing, Moura</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de Maps muestran la fachada con el rótulo 'BATERIAS EL GABO' y letreros de 'COMPRA DE CASCOS' y 'REPARACIÓN DE BATERIAS', además de un anaquel interior con baterías físicas de marca propia 'Baterías El Gabo' y de las marcas Mopar, Kirkland, América Racing y Moura.</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra un spa ('Spa JC') sin relación alguna con baterías. Sin embargo, las fotos propias de la ficha de Maps 'Baterías El Gabo' (mismo place ID que el link registrado) muestran con claridad el rótulo exacto 'BATERIAS EL GABO' en la fachada y un anaquel con baterías físicas de varias marcas en el interior.</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>fotos/129_baterias_el_gabo/streetview_1.jpg; fotos/129_baterias_el_gabo/streetview_2.jpg; fotos/129_baterias_el_gabo/maps_foto_1.jpg; fotos/129_baterias_el_gabo/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O120" s="3" t="n"/>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO H&amp;H</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Av. Insurgentes 101, San Cristóbal Centro, 55000 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>19.6007142</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>-99.0532973</v>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n"/>
+      <c r="I121" s="2" t="n"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterías en ninguna foto disponible; el Street View muestra una tienda de pañales ('Pañal Americano'), un negocio de stickers/publicidad ('SKA Publicidad') y un local de copias e impresiones, sin relación alguna a baterías.</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas no muestra el nombre 'Centro de Servicio H&amp;H' ni ningún negocio de baterías. La ficha de Maps no tiene ninguna foto propia ni reseñas que confirmen venta de baterías en este domicilio. No hay evidencia visual ni textual disponible.</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>fotos/130_centro_de_servicio_h_h/streetview_1.jpg; fotos/130_centro_de_servicio_h_h/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O121" s="3" t="n"/>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>DIST. DE ACUMULADORES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Av. Valle de Santiago 162, Valle de Aragon 3ra Secc, 55280 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>19.5015367</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>-99.0502637</v>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES HERNANDEZ (LTH)</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias fisicas: la cortina metalica del local esta cerrada en ambas fotos de Street View, con un puesto de comida instalado enfrente. Solo se ve el letrero de lona 'LTH ACUMULADORES HERNANDEZ' sobre la cortina.</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'ACUMULADORES HERNANDEZ' coincide exactamente con el letrero visible en la fachada en las coordenadas exactas, junto con el logo de la marca LTH. El local esta cerrado (cortina abajo) en el momento de la captura, por lo que no se ven baterias fisicas, pero el rotulo y la marca son evidencia suficiente de que es una tienda de baterias.</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>fotos/141_dist_de_acumuladores_hernandez/streetview_1.jpg; fotos/141_dist_de_acumuladores_hernandez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O122" s="3" t="n"/>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Av Sta Teresa 25, Granjas Valle de Guadalupe Secc B, 55200 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>19.5281143</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>-99.0513169</v>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>AFN ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America, Full Power, Duralast, Lorenzini, Motorcraft</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>En la foto de Google Maps se ven multiples anaqueles con decenas de baterias de auto y moto reales, ademas de un cartel 'BATERIAS NUEVAS DESDE $999' y logos de varias marcas (LTH, America, Full Power, Duralast, Lorenzini, Motorcraft) en la fachada.</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de Street View en el PIN exacto mostraban un negocio distinto (comercio de electrodomesticos Maytag/Sanyo), asi que se investigo el link de Maps: la foto propia de la ficha 'Acumuladores Fuego Nuevo' muestra el rotulo 'AFN ACUMULADORES FUEGO NUEVO' y anaqueles repletos de baterias reales, confirmando el giro y el nombre exacto del negocio (el pin de Street View esta mal ubicado, pero la foto de la propia ficha de Maps prueba la fachada real).</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>fotos/142_acumuladores_fuego_nuevo/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O123" s="3" t="n"/>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ANDREA</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Av. Gobernador Lic. Ignacio Pichardo Pagaza Mz4 Lt2, Cd Amanecer, 55267 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>19.5104665</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>-99.02466080000001</v>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ANDREA</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>La foto de Google Maps muestra baterias reales de las marcas LTH y America apiladas en anaqueles detras de una reja de seguridad, con un cartel de '48 meses de garantia'.</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto mostraba una panaderia ('Panaderia Chuco Vainilla'), un negocio distinto, por lo que se investigo el link de Maps: la foto de la propia ficha 'Acumuladores Andrea' muestra el rotulo azul 'ACUMULADORES ANDREA' sobre una cortina con baterias LTH y America visibles detras de la reja, confirmando nombre y giro exactos (el pin de Street View esta mal ubicado o corresponde a una toma vieja de un local vecino).</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>fotos/143_acumuladores_andrea/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O124" s="3" t="n"/>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>LTH MCUMULADORES SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Av. Nacional 18, Sta Maria Chiconautla, 55066 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>19.6336485</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>-99.002315</v>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>LTH ACUMULADORES SANCHEZ</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas en anaquel; se ve un mural pintado en la fachada con el logo LTH y una bateria dibujada (grafico, no producto real), junto con el texto 'ACUMULADORES SANCHEZ'.</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'SANCHEZ' y el logo de marca LTH aparecen pintados directamente en la fachada de la esquina exacta del PIN, con el texto 'ACUMULADORES' tambien visible, coincidiendo con el registro 'LTH MCUMULADORES SANCHEZ'.</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>fotos/144_lth_mcumuladores_sanchez/streetview_1.jpg; fotos/144_lth_mcumuladores_sanchez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O125" s="3" t="n"/>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>C. Cerro de la Estrella 100, Sagitario 3, 55238 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>19.4958195</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>-99.0205964</v>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>LTH - ACUMULADORES BATERIAS (Carga de Bateria Rapida y Lenta)</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>Se ven murales pintados de baterias LTH en la fachada (graficos, no fotos de producto real); dentro del local hay anaqueles con cajas y mercancia diversa, pero no se distinguen baterias fisicas con claridad.</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>La fachada en el PIN exacto tiene pintado el texto 'CARGA DE BATERIA ACUMULADORES BATERIAS RAPIDA Y LENTA' junto con el logo LTH repetido varias veces, coincidiendo con el nombre registrado 'LTH'.</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>fotos/145_lth/streetview_1.jpg; fotos/145_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O126" s="3" t="n"/>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores los Gemelos las américas</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Bosque de Ombues 3, Fraccionamiento Las Americas, Las Américas, 55076 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>19.5890478</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>-98.9997336</v>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS - Compra y Venta de Baterias Automotriz e Industrial</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n"/>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias fisicas apiladas; el anuncio del toldo tiene iconos graficos de baterias (clip art), no fotos de producto real ni marcas especificas legibles.</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>El nombre exacto 'Los Gemelos' no es legible en la fachada, pero el giro coincide plenamente: el letrero dice 'BATERIAS - COMPRA Y VENTA DE BATERIAS AUTOMOTRIZ E INDUSTRIAL' en el domicilio exacto del PIN, lo cual confirma que es una tienda de baterias en ese sitio (se prioriza la evidencia visual del giro sobre el nombre exacto, segun la regla del proyecto).</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>fotos/146_acumuladores_los_gemelos_las_americas/streetview_1.jpg; fotos/146_acumuladores_los_gemelos_las_americas/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O127" s="3" t="n"/>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Baterías de gel bolaños</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Gobernador Rafael M. Hidalgo 69-Local 6, Granjas Valle de Guadalupe, 55270 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>19.5062261</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>-99.0566271</v>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias en ninguna foto disponible (ni Street View ni la ficha de Maps, que solo repite la misma foto de la cortina cerrada sin rotulo visible).</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ni Street View ni la galeria de Maps muestran rotulo o producto visible (cortina azul cerrada sin ningun letrero, junto a un taller de 'Clutch y Frenos'). Sin embargo, una resena de un cliente en la ficha de Maps confirma la venta de baterias en este domicilio exacto: 'No tiene nada de baterias nuevas, tiene puras baterias usadas que no sirven... El senor nunca esta... y sobre la compra no hay garantia CUIDADO'. La ficha tambien esta categorizada por Google como 'Tienda de baterias para automovil' y ofrece 'Entrega a domicilio', consistente con un negocio sin aparador visible.</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>fotos/147_baterias_de_gel_bolanos/streetview_1.jpg; fotos/147_baterias_de_gel_bolanos/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O128" s="3" t="n"/>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SafeLithium - Venta, Calculo, Diseño, Armado y reparacion de baterias de Litio</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>C. 309-A 67, El Coyol, Gustavo A. Madero, 07420 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>19.4871735</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>-99.0910883</v>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos propias de la ficha de Maps muestran celdas de litio reales: un banco de celdas prismaticas tipo LiFePO4 (etiquetadas '442B') conectadas con barras de cobre y cableado, y otra foto de un paquete de celdas cilindricas 18650 ensambladas -- es decir, baterias de litio fisicas en proceso de armado.</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View en el PIN exacto solo muestra una casa habitacion azul sin ningun letrero comercial visible (el negocio opera aparentemente desde un taller/domicilio sin aparador publico). No obstante, la propia ficha de Maps de 'SafeLithium' tiene fotos subidas por el negocio mostrando celdas de litio reales siendo armadas en paquetes de baterias, lo cual confirma que si fabrican/venden baterias de litio tal como indica su nombre y giro.</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_2.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O129" s="3" t="n"/>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Vargas</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Vía Morelos 425, Cuauhtemoc Xalostoc, 55310 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>19.5309639</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>-99.07474740000001</v>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Baterias Nuevas y Seminuevas (Via Morelos No425)</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America Racing, Optima, Gonher</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de la propia ficha de Maps muestran anaqueles con baterias fisicas reales de las marcas LTH, America Racing y Optima (bateria amarilla), ademas de cajas de baterias de motocicleta LTH y America, y un letrero 'Baterias Nuevas y Seminuevas desde $499'.</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto mostraba un negocio de tortillas/muebles distinto (sin relacion), por lo que se investigo el link de Maps: las fotos propias de la ficha muestran un aparador con placa 'VIA MORELOS No 425' (coincide exactamente con la direccion registrada) y anaqueles repletos de baterias reales LTH/America/Optima, ademas de un banner de 'Baterias Nuevas y Seminuevas'. Aunque el rotulo no dice literalmente 'Vargas', la direccion exacta y la evidencia fotografica del giro son concluyentes.</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>fotos/149_baterias_vargas/maps_foto_1.jpg; fotos/149_baterias_vargas/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O130" s="3" t="n"/>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES DE LA GARZA</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Real del Monte 2, Guadalupe Insurgentes, Gustavo A. Madero, 07870 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>19.4701634</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>-99.1320714</v>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES DE LA GARZA</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>No se distinguen baterias de auto apiladas con claridad en el aparador (se ven articulos pequenos como accesorios/electronica); si es visible un letrero de precios 'COMPRO CASCOS - MINI $100, CHICA $120...' (compra de cascos/nucleos de bateria usada) y el logo LTH en el toldo.</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'ACUMULADORES DE LA GARZA' coincide exactamente con el rotulo verde de la fachada en el PIN exacto, junto con el logo de la marca LTH en el toldo blanco y un letrero de 'COMPRO CASCOS' con tarifas por tamano de bateria (Mini/Chica/Mediana), practica caracteristica de una tienda de baterias.</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>fotos/150_acumuladores_de_la_garza/streetview_1.jpg; fotos/150_acumuladores_de_la_garza/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O131" s="3" t="n"/>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P21"/>
+  <autoFilter ref="A1:P131"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -1994,6 +9694,116 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$P$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$P$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P131"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8285,23 +8285,23 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES ARRIAGA</t>
+          <t>Acumuladores Mauleón</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Nte. 15 62, San Carlos, 55080 Ecatepec de Morelos, Méx., México</t>
+          <t>Av. 1ro de Mayo 85, Jardines de Morelos 5ta, 55075 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>19.5797841</v>
+        <v>19.5923861</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>-99.0487174</v>
+        <v>-99.0288245</v>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
@@ -8315,37 +8315,37 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES ARRIAGA</t>
+          <t>Acumuladores Mauleón</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>LTH, América, Duralast, Checker</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>La foto propia del negocio en Maps (fechada 2023/5/26) muestra el interior de la tienda con anaqueles metálicos repletos de baterías físicas de las marcas LTH, América, Duralast y Checker, más un letrero de 'BATERIAS NUEVAS CHECKER $999' y un banner 'ACUMULADORES ARRIAGA - LTH - LA FUERZA DE TU AUTOMÓVIL'.</t>
+          <t>No se ven baterías físicas en ninguna foto disponible, solo el letrero de la marca LTH en la fachada.</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas exactas solo muestra la cortina metálica cerrada del local, sin letrero legible (posible cierre momentáneo al pasar la cámara). Sin embargo, la foto propia del negocio en su ficha de Maps (mismo place ID que el link registrado, fechada 2023/5/26) muestra con total claridad el rótulo 'ACUMULADORES ARRIAGA' y anaqueles llenos de baterías físicas de varias marcas. Las reseñas mencionan 'diagnóstico, opciones de compra' y preguntan si 'cargan baterías', consistente con una tienda de baterías activa en ese domicilio.</t>
+          <t>Persiana cerrada, sin mostrador visible, pero la fachada muestra un letrero grande de marca LTH y, debajo, un rótulo verde parcialmente tapado por un árbol que dice "...ACU[MULAD]ORES MAULEON", coincidiendo con el nombre registrado en el PIN exacto.</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>fotos/121_acumuladores_arriaga/streetview_1.jpg; fotos/121_acumuladores_arriaga/streetview_2.jpg; fotos/121_acumuladores_arriaga/maps_foto_1.jpg</t>
+          <t>fotos/111_acumuladores_mauleon/streetview_1.jpg; fotos/111_acumuladores_mauleon/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_1.jpg</t>
+          <t>streetview_2.jpg</t>
         </is>
       </c>
       <c r="O112" s="3" t="n"/>
@@ -8357,23 +8357,23 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES INSURGENTES</t>
+          <t>DISTRIBUIDOR LTH</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Av. Insurgentes 28, El Calvario, 55020 Ecatepec de Morelos, Méx., México</t>
+          <t>Xicoténcatl 44, Cuauhtemoc Xalostoc, 55310 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>19.6046026</v>
+        <v>19.5322109</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>-99.0586461</v>
+        <v>-99.07007400000001</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
@@ -8385,26 +8385,34 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="H113" s="2" t="n"/>
-      <c r="I113" s="2" t="n"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidor LTH / Acumuladores</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterías físicas en ninguna foto disponible. El Street View en el pin exacto muestra un negocio de 'Aluminio y Cristal' sin relación, y la única foto 'del propietario' en Maps (feb 2025) es una toma genérica de la calle donde se ve de fondo ese mismo negocio de aluminio, sin mostrar baterías.</t>
+          <t>No hay fotos adicionales de Maps descargadas; streetview_1 ya muestra anaqueles interiores llenos de baterías físicas apiladas.</t>
         </is>
       </c>
       <c r="L113" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: el Street View en las coordenadas exactas muestra 'TODO EN ALUMINIO Y CRISTAL', un negocio distinto sin baterías visibles, y no existe ninguna foto de la ficha de Maps que muestre baterías físicas en este domicilio. Sin embargo, la ficha de Maps 'ACUMULADORES INSURGENTES' (nombre exacto, mismo place ID que el link registrado) tiene una reseña de cliente ('venden baterías en mal estado') con respuesta oficial del propietario que confirma explícitamente: 'VENDEMOS BATERIAS NUEVAS DE LAS CUALES SE LE DA UNA POLIZA DE GARANTIA'. Esta es evidencia textual directa de la propia ficha del negocio de que sí vende baterías, aunque el pin de ubicación parece estar mal colocado (aparentemente comparte cuadra con un negocio de aluminio y cristal).</t>
+          <t>Fachada de gran formato con marca LTH, texto "ACUMULADORES", servicio de instalación/scaneo de sistema, y anaqueles interiores repletos de baterías apiladas junto con exhibidores físicos en la banqueta. Evidencia visual directa e inequívoca.</t>
         </is>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>fotos/122_acumuladores_insurgentes/streetview_1.jpg; fotos/122_acumuladores_insurgentes/streetview_2.jpg</t>
+          <t>fotos/112_distribuidor_lth/streetview_1.jpg; fotos/112_distribuidor_lth/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8421,23 +8429,23 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>BATERÍAS PARA AUTO LTH</t>
+          <t>Acumuladores Hernández</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Calle Bosque De San Marcos, Jardines de Morelos, 55070 Ecatepec de Morelos, Méx., México</t>
+          <t>Av Ojo de Agua 3, Santo Tomas Chiconautla, 55066 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>19.5950868</v>
+        <v>19.6367202</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>-99.0021826</v>
+        <v>-99.0101624</v>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
@@ -8451,37 +8459,37 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES SINTERGIA</t>
+          <t>Acumuladores Hernández</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>LTH, América Racing, Xtreme</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>Las fotos de Maps muestran un aparador con anaqueles metálicos repletos de baterías físicas de las marcas LTH, América Racing y Xtreme desde el piso hasta el techo, además de un despliegue individual de producto (batería Xtreme XT-42, América Racing y LTH) sobre un mostrador con accesorios de terminal.</t>
+          <t>No hay fotos de Maps descargadas; no se observan baterías físicas apiladas, solo el rótulo de marca en el toldo.</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas registradas muestra un negocio de maderas/molduras sin relación alguna con baterías. Sin embargo, la ficha de Maps abierta con el link exacto del registro ('BATERÍAS PARA AUTO LTH', mismo place ID) tiene fotos propias del negocio que muestran el rótulo real 'ACUMULADORES SINTERGIA - BATERIAS - LA ENERGIA QUE NECESITA TU MOTOR' con anaqueles repletos de baterías físicas de varias marcas. El nombre visible en fachada difiere del registrado, pero el giro y la evidencia visual de venta de baterías son inequívocos, por lo que se prioriza la evidencia visual sobre el nombre registrado.</t>
+          <t>Persiana cerrada sin mostrador visible, pero el toldo dice explícitamente "ACUMULADORES" + "HERNANDEZ" + marca LTH, además de "Compra de cascos" y "Carga rápida y lenta", textos de servicio específicos de un negocio de baterías.</t>
         </is>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>fotos/123_baterias_para_auto_lth/streetview_1.jpg; fotos/123_baterias_para_auto_lth/streetview_2.jpg; fotos/123_baterias_para_auto_lth/maps_foto_1.jpg; fotos/123_baterias_para_auto_lth/maps_foto_2.jpg; fotos/123_baterias_para_auto_lth/maps_foto_3.jpg</t>
+          <t>fotos/113_acumuladores_hernandez/streetview_1.jpg; fotos/113_acumuladores_hernandez/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_1.jpg</t>
+          <t>streetview_1.jpg</t>
         </is>
       </c>
       <c r="O114" s="3" t="n"/>
@@ -8493,23 +8501,23 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES FUEGO NUEVO</t>
+          <t>ACUMULADORES EXPRESS</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Av. Fuego Nuevo 70, Cd Azteca 2da Secc, 55450 Ecatepec de Morelos, Méx., México</t>
+          <t>Av. Cvln. Sur 10, Jardines de Casa Nueva, 55430 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>19.5484092</v>
+        <v>19.5484073</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>-99.0330062</v>
+        <v>-99.04467</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
@@ -8523,10 +8531,14 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES FUEGO NUEVO</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="n"/>
+          <t>Acumuladores Express</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8534,22 +8546,22 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>Ambas fotos de Street View muestran un aparador rojo con múltiples baterías físicas de color negro apiladas en varios niveles; las etiquetas de marca no son legibles con suficiente nitidez en la imagen para identificarlas con certeza.</t>
+          <t>maps_foto_1 muestra un anaquel con docenas de baterías LTH apiladas (cajas negras con tapa roja) bajo el rótulo "BATERIAS"; maps_foto_2 es un acercamiento a una batería LTH individual (L-58-575, BCI 58, garantía 48 meses).</t>
         </is>
       </c>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas exactas muestra con claridad el letrero 'ACUMULADORES FUEGO NUEVO', coincidiendo exactamente con el nombre registrado, junto con el texto 'VENTA DE TERMINALES, ACIDO, CHEQUEO POR SCANNER' y un aparador con baterías físicas visibles en ambas tomas.</t>
+          <t>El streetview del PIN está borroso/con neblina y no es concluyente por sí solo, pero las fotos de Maps ya disponibles muestran sin ambigüedad el rótulo "ACUMULADORES EXPRESS" con marca LTH y el interior con decenas de baterías físicas en anaqueles.</t>
         </is>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>fotos/124_acumuladores_fuego_nuevo/streetview_1.jpg; fotos/124_acumuladores_fuego_nuevo/streetview_2.jpg</t>
+          <t>fotos/114_acumuladores_express/streetview_1.jpg; fotos/114_acumuladores_express/streetview_2.jpg; fotos/114_acumuladores_express/maps_foto_1.jpg; fotos/114_acumuladores_express/maps_foto_2.jpg</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>streetview_1.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O115" s="3" t="n"/>
@@ -8561,23 +8573,23 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES CAMILA</t>
+          <t>ACUMULADORES NJ</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Vía Adolfo López Mateos 2062, El Cegor, 55127 Ecatepec de Morelos, Méx., México</t>
+          <t>Circunvalación Nte. 4, Jardines de Santa Clara, 55450 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>19.5397658</v>
+        <v>19.5530759</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>-99.0409576</v>
+        <v>-99.0384128</v>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
@@ -8591,12 +8603,12 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES CAMILA</t>
+          <t>Acumuladores NJ</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>LTH, América Racing, EverStart, ACDelco, Dynamo, CAR 100</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -8606,17 +8618,17 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>Las fotos de Maps muestran anaqueles metálicos repletos de baterías físicas de las marcas LTH, América Racing, EverStart, ACDelco, Dynamo y CAR 100, bajo el rótulo 'ACUMULADORES CAMILA - LTH - CARGA Y VENTA - NUEVAS Y SEMINUEVAS' pintado sobre la cortina de entrada.</t>
+          <t>maps_foto_1 muestra un stand rotulado "ACUMULADORES NJ" con marca LTH y una fila de baterías físicas (cajas oscuras con etiquetas rojo/blanco) sobre el mostrador pintado con "América"/"LTH".</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas exactas muestra una fachada azul con un letrero distinto e ilegible que no corresponde a una tienda de baterías. Sin embargo, las fotos propias del negocio en su ficha de Maps muestran con total claridad el rótulo 'ACUMULADORES CAMILA', coincidiendo exactamente con el nombre registrado, y anaqueles llenos de baterías físicas de múltiples marcas.</t>
+          <t>El Street View del PIN muestra un patio con autos y árboles que bloquean la vista, no concluyente por sí solo. La foto de Maps ya disponible muestra el stand rotulado "ACUMULADORES NJ" con marca LTH y baterías físicas sobre el mostrador.</t>
         </is>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>fotos/125_acumuladores_camila/streetview_1.jpg; fotos/125_acumuladores_camila/streetview_2.jpg; fotos/125_acumuladores_camila/maps_foto_1.jpg; fotos/125_acumuladores_camila/maps_foto_2.jpg</t>
+          <t>fotos/115_acumuladores_nj/streetview_1.jpg; fotos/115_acumuladores_nj/streetview_2.jpg; fotos/115_acumuladores_nj/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8633,23 +8645,23 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Centro Distribución LTH</t>
+          <t>ACUMULADORES GONZALEZ</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Circunvalación Sur esquina Zihuatanejo 2, Jardines de Casa Nueva, 55430 Ecatepec de Morelos, Méx., México</t>
+          <t>Cedro 27, Potrero Chico, 55119 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>19.5489461</v>
+        <v>19.5741275</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>-99.04530560000001</v>
+        <v>-99.022274</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
@@ -8661,16 +8673,8 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>Centro de Distribución LTH</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>LTH</t>
-        </is>
-      </c>
+      <c r="H117" s="2" t="n"/>
+      <c r="I117" s="2" t="n"/>
       <c r="J117" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8678,22 +8682,22 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>Ambas fotos muestran el rótulo 'LTH - Centro de Distribución - BATERIAS' y una máquina expendedora de la marca LTH con gráfico de batería en la fachada; no se aprecia un mostrador abierto con baterías físicas apiladas, sino el punto de venta/distribución y la máquina de autoservicio.</t>
+          <t>La única foto disponible en Maps (subida por "Jose Manuel Rivas Tomas") muestra a alguien conectando cables/pasa-corriente a una batería en el cofre de un auto; no se distingue marca ni anaquel de producto.</t>
         </is>
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas exactas muestra el letrero 'LTH - Centro de Distribución - BATERIAS', coincidiendo con el nombre registrado 'Centro Distribución LTH', junto con una máquina expendedora de baterías LTH instalada en la fachada del local.</t>
+          <t>LIMITACION: Street View en todas las fechas disponibles (ene 2026, oct 2024, may 2024) queda demasiado lejos -- el negocio está al otro lado de una cuneta sobre una avenida amplia (Av. Carlos Hank González) -- y no permite leer ningún nombre en la fachada. El veredicto SI se sostiene en la ficha de Maps (categoría "Tienda de baterías para automóvil") y en 2 reseñas que confirman explícitamente la venta: "Buen precio en baterías nuevas y seminuevas" y "buena atención, buen costo y con garantía".</t>
         </is>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>fotos/126_centro_distribucion_lth/streetview_1.jpg; fotos/126_centro_distribucion_lth/streetview_2.jpg</t>
+          <t>fotos/116_acumuladores_gonzalez/streetview_1.jpg; fotos/116_acumuladores_gonzalez/streetview_2.jpg; fotos/116_acumuladores_gonzalez/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>streetview_2.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O117" s="3" t="n"/>
@@ -8705,23 +8709,23 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES "MORENO"</t>
+          <t>Baterías " Palestina "</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Vía Adolfo López Mateos 3295, Miguel Hidalgo, 55490 Ecatepec de Morelos, Méx., México</t>
+          <t>Vía Adolfo López Mateos 147, Pro Revolucion, 55100 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>19.5339204</v>
+        <v>19.5533028</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>-99.0464537</v>
+        <v>-99.0285466</v>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
@@ -8735,33 +8739,37 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>MORENO (Acumuladores Moreno)</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="n"/>
+          <t>Palestina</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>Ambas fotos de Street View muestran un anaquel amarillo/azul con múltiples baterías físicas apiladas bajo el rótulo 'MORENO BATERIAS de GEL-1000', junto con una lista de precios por tamaño (mini, chica, mediana, tornillo, camión); no se distinguen logos de marcas de terceros, solo la marca propia del negocio.</t>
+          <t>maps_foto_1 (subida por la cuenta "Rolit Palestina") muestra un mural pintado "BATERIAS NUEVAS Y SEMINUEVAS, SE COMPRAN CASCOS" con ilustraciones de baterías y banners reales de marca LTH ("COMPRO BATERIAS"); no se distinguen baterías físicas apiladas en anaquel.</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas exactas muestra con claridad el nombre 'MORENO', coincidiendo con el registrado 'ACUMULADORES MORENO', con baterías físicas visibles en el anaquel y letreros de 'SE COMPRAN BATERIAS' y lista de precios de baterías por tamaño.</t>
+          <t>El streetview_1/streetview_2 del script muestran en el PIN la fachada de "Vulcanizadora Mikel's", un negocio distinto. Al investigar en Maps se halló una captura de Street View de otra fecha (agosto 2024) que sí muestra el letrero "★ PALESTINA" en la misma dirección, más una foto subida por la cuenta "Rolit Palestina" con mural de baterías/LTH y una reseña que confirma "venden baterías que no sirven". Con esto se resuelve la discrepancia inicial del encuadre por defecto.</t>
         </is>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>fotos/127_acumuladores_moreno/streetview_1.jpg; fotos/127_acumuladores_moreno/streetview_2.jpg</t>
+          <t>fotos/117_baterias_palestina/streetview_1.jpg; fotos/117_baterias_palestina/streetview_2.jpg; fotos/117_baterias_palestina/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>streetview_1.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O118" s="3" t="n"/>
@@ -8773,23 +8781,23 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES MARTINEZ</t>
+          <t>ACUMULADORES JORGE</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Av. Insurgentes 148, El Calvario, 55020 Ecatepec de Morelos, Méx., México</t>
+          <t>Av. Alfredo del Mazo 69, Granjas Valle de Guadalupe, 55270 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>19.6028217</v>
+        <v>19.5133367</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>-99.0569216</v>
+        <v>-99.0560777</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
@@ -8798,29 +8806,37 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Servicio Eléctrico Automotriz "Jorge"</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="n"/>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterías en ninguna foto disponible; el Street View muestra un letrero de 'RÓTULOS - TOLDOS FIJOS Y ENROLLABLES', un laboratorio/consultorio médico y una tienda de artículos de fiesta ('Mi Lugar Favorito'), sin relación alguna a baterías.</t>
+          <t>No hay fotos de Maps descargadas; no se ven baterías físicas apiladas, solo un letrero colgante con forma de batería de marca LTH en la entrada.</t>
         </is>
       </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas exactas no muestra el nombre 'Acumuladores Martinez' ni ningún negocio de baterías; en su lugar aparecen un taller de rótulos/toldos y un laboratorio médico. La ficha de Maps no tiene fotos propias del negocio ni reseñas, y el negocio aparece marcado como 'Cerrado temporalmente'. No hay evidencia visual ni textual disponible que confirme venta de baterías en este domicilio.</t>
+          <t>La fachada en el PIN dice "SERVICIO ELECTRICO AUTOMOTRIZ...JORGE" (giro distinto al registrado) pero el nombre "Jorge" coincide y hay un letrero colgante real con forma de batería y logo de marca LTH en la entrada; Maps categoriza el lugar como "Tienda de baterías para automóvil". No se hallaron fotos adicionales ni reseñas que mencionen baterías.</t>
         </is>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>fotos/128_acumuladores_martinez/streetview_1.jpg; fotos/128_acumuladores_martinez/streetview_2.jpg</t>
+          <t>fotos/118_acumuladores_jorge/streetview_1.jpg; fotos/118_acumuladores_jorge/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -8837,23 +8853,23 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Baterías "El Gabo"</t>
+          <t>Acumuladores Géminis</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Av Acueducto 47, Jorge Jimenez Cantu, 54190 Tlalnepantla, Méx., México</t>
+          <t>Lote 30 MZ 441, Cd Azteca 3ra Secc, 55120 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>19.5335734</v>
+        <v>19.5359558</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>-99.0904464</v>
+        <v>-99.02178910000001</v>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
@@ -8867,12 +8883,12 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>BATERIAS EL GABO</t>
+          <t>Acumuladores</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Mopar, Kirkland, América Racing, Moura</t>
+          <t>América</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -8882,17 +8898,17 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>Las fotos de Maps muestran la fachada con el rótulo 'BATERIAS EL GABO' y letreros de 'COMPRA DE CASCOS' y 'REPARACIÓN DE BATERIAS', además de un anaquel interior con baterías físicas de marca propia 'Baterías El Gabo' y de las marcas Mopar, Kirkland, América Racing y Moura.</t>
+          <t>maps_foto_1 muestra una batería física (etiqueta "América Racing", garantía 48 meses) sobre el mostrador; maps_foto_2 muestra el interior de un taller con refacciones y cajas/huacales con equipo eléctrico.</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas exactas muestra un spa ('Spa JC') sin relación alguna con baterías. Sin embargo, las fotos propias de la ficha de Maps 'Baterías El Gabo' (mismo place ID que el link registrado) muestran con claridad el rótulo exacto 'BATERIAS EL GABO' en la fachada y un anaquel con baterías físicas de varias marcas en el interior.</t>
+          <t>La fachada muestra el letrero "ACUMULADORES" en letras grandes y legibles, con textos de servicio "Diagnostico con Scanner", "Compra/Carga de Baterías" y "Entrega a Domicilio" (el nombre superior, probablemente "Géminis", está desgastado e ilegible). Las fotos de Maps confirman una batería física de marca América con garantía sobre el mostrador.</t>
         </is>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>fotos/129_baterias_el_gabo/streetview_1.jpg; fotos/129_baterias_el_gabo/streetview_2.jpg; fotos/129_baterias_el_gabo/maps_foto_1.jpg; fotos/129_baterias_el_gabo/maps_foto_2.jpg</t>
+          <t>fotos/119_acumuladores_geminis/streetview_1.jpg; fotos/119_acumuladores_geminis/streetview_2.jpg; fotos/119_acumuladores_geminis/maps_foto_1.jpg; fotos/119_acumuladores_geminis/maps_foto_2.jpg</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -8909,23 +8925,23 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>CENTRO DE SERVICIO H&amp;H</t>
+          <t>ACUMULADORES AMERICA</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Av. Insurgentes 101, San Cristóbal Centro, 55000 Ecatepec de Morelos, Méx., México</t>
+          <t>Av. San Agustín Pte. 21, San Agustin 1ra Secc, 55130 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>19.6007142</v>
+        <v>19.5293654</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>-99.0532973</v>
+        <v>-99.0484433</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
@@ -8934,29 +8950,37 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="n"/>
-      <c r="I121" s="2" t="n"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores "America"</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterías en ninguna foto disponible; el Street View muestra una tienda de pañales ('Pañal Americano'), un negocio de stickers/publicidad ('SKA Publicidad') y un local de copias e impresiones, sin relación alguna a baterías.</t>
+          <t>No hay fotos adicionales de Maps descargadas; streetview_1 muestra, a través de la puerta abierta, anaqueles con filas de cajas de batería junto a un letrero "BATERIAS" y "FULL POWER".</t>
         </is>
       </c>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>El Street View en las coordenadas exactas no muestra el nombre 'Centro de Servicio H&amp;H' ni ningún negocio de baterías. La ficha de Maps no tiene ninguna foto propia ni reseñas que confirmen venta de baterías en este domicilio. No hay evidencia visual ni textual disponible.</t>
+          <t>Fachada rotulada "ACUMULADORES America" con doble logo LTH y un mural de batería LTH en la pared contigua; a través de la puerta abierta se ven anaqueles con filas de cajas de batería junto a un letrero "BATERIAS". Evidencia visual clara y directa.</t>
         </is>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>fotos/130_centro_de_servicio_h_h/streetview_1.jpg; fotos/130_centro_de_servicio_h_h/streetview_2.jpg</t>
+          <t>fotos/120_acumuladores_america/streetview_1.jpg; fotos/120_acumuladores_america/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -8973,23 +8997,23 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>DIST. DE ACUMULADORES HERNANDEZ</t>
+          <t>ACUMULADORES ARRIAGA</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Av. Valle de Santiago 162, Valle de Aragon 3ra Secc, 55280 Ecatepec de Morelos, Méx., México</t>
+          <t>Nte. 15 62, San Carlos, 55080 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>19.5015367</v>
+        <v>19.5797841</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>-99.0502637</v>
+        <v>-99.0487174</v>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
@@ -9003,37 +9027,37 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES HERNANDEZ (LTH)</t>
+          <t>ACUMULADORES ARRIAGA</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>LTH, América, Duralast, Checker</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterias fisicas: la cortina metalica del local esta cerrada en ambas fotos de Street View, con un puesto de comida instalado enfrente. Solo se ve el letrero de lona 'LTH ACUMULADORES HERNANDEZ' sobre la cortina.</t>
+          <t>La foto propia del negocio en Maps (fechada 2023/5/26) muestra el interior de la tienda con anaqueles metálicos repletos de baterías físicas de las marcas LTH, América, Duralast y Checker, más un letrero de 'BATERIAS NUEVAS CHECKER $999' y un banner 'ACUMULADORES ARRIAGA - LTH - LA FUERZA DE TU AUTOMÓVIL'.</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>El nombre 'ACUMULADORES HERNANDEZ' coincide exactamente con el letrero visible en la fachada en las coordenadas exactas, junto con el logo de la marca LTH. El local esta cerrado (cortina abajo) en el momento de la captura, por lo que no se ven baterias fisicas, pero el rotulo y la marca son evidencia suficiente de que es una tienda de baterias.</t>
+          <t>El Street View en las coordenadas exactas solo muestra la cortina metálica cerrada del local, sin letrero legible (posible cierre momentáneo al pasar la cámara). Sin embargo, la foto propia del negocio en su ficha de Maps (mismo place ID que el link registrado, fechada 2023/5/26) muestra con total claridad el rótulo 'ACUMULADORES ARRIAGA' y anaqueles llenos de baterías físicas de varias marcas. Las reseñas mencionan 'diagnóstico, opciones de compra' y preguntan si 'cargan baterías', consistente con una tienda de baterías activa en ese domicilio.</t>
         </is>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>fotos/141_dist_de_acumuladores_hernandez/streetview_1.jpg; fotos/141_dist_de_acumuladores_hernandez/streetview_2.jpg</t>
+          <t>fotos/121_acumuladores_arriaga/streetview_1.jpg; fotos/121_acumuladores_arriaga/streetview_2.jpg; fotos/121_acumuladores_arriaga/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>streetview_2.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O122" s="3" t="n"/>
@@ -9045,23 +9069,23 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES FUEGO NUEVO</t>
+          <t>ACUMULADORES INSURGENTES</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Av Sta Teresa 25, Granjas Valle de Guadalupe Secc B, 55200 Ecatepec de Morelos, Méx., México</t>
+          <t>Av. Insurgentes 28, El Calvario, 55020 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>19.5281143</v>
+        <v>19.6046026</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>-99.0513169</v>
+        <v>-99.0586461</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
@@ -9073,39 +9097,31 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>AFN ACUMULADORES FUEGO NUEVO</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>LTH, America, Full Power, Duralast, Lorenzini, Motorcraft</t>
-        </is>
-      </c>
+      <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>En la foto de Google Maps se ven multiples anaqueles con decenas de baterias de auto y moto reales, ademas de un cartel 'BATERIAS NUEVAS DESDE $999' y logos de varias marcas (LTH, America, Full Power, Duralast, Lorenzini, Motorcraft) en la fachada.</t>
+          <t>No se aprecian baterías físicas en ninguna foto disponible. El Street View en el pin exacto muestra un negocio de 'Aluminio y Cristal' sin relación, y la única foto 'del propietario' en Maps (feb 2025) es una toma genérica de la calle donde se ve de fondo ese mismo negocio de aluminio, sin mostrar baterías.</t>
         </is>
       </c>
       <c r="L123" s="3" t="inlineStr">
         <is>
-          <t>Las fotos de Street View en el PIN exacto mostraban un negocio distinto (comercio de electrodomesticos Maytag/Sanyo), asi que se investigo el link de Maps: la foto propia de la ficha 'Acumuladores Fuego Nuevo' muestra el rotulo 'AFN ACUMULADORES FUEGO NUEVO' y anaqueles repletos de baterias reales, confirmando el giro y el nombre exacto del negocio (el pin de Street View esta mal ubicado, pero la foto de la propia ficha de Maps prueba la fachada real).</t>
+          <t>LIMITACION: el Street View en las coordenadas exactas muestra 'TODO EN ALUMINIO Y CRISTAL', un negocio distinto sin baterías visibles, y no existe ninguna foto de la ficha de Maps que muestre baterías físicas en este domicilio. Sin embargo, la ficha de Maps 'ACUMULADORES INSURGENTES' (nombre exacto, mismo place ID que el link registrado) tiene una reseña de cliente ('venden baterías en mal estado') con respuesta oficial del propietario que confirma explícitamente: 'VENDEMOS BATERIAS NUEVAS DE LAS CUALES SE LE DA UNA POLIZA DE GARANTIA'. Esta es evidencia textual directa de la propia ficha del negocio de que sí vende baterías, aunque el pin de ubicación parece estar mal colocado (aparentemente comparte cuadra con un negocio de aluminio y cristal).</t>
         </is>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
-          <t>fotos/142_acumuladores_fuego_nuevo/maps_foto_1.jpg</t>
+          <t>fotos/122_acumuladores_insurgentes/streetview_1.jpg; fotos/122_acumuladores_insurgentes/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_1.jpg</t>
+          <t>streetview_1.jpg</t>
         </is>
       </c>
       <c r="O123" s="3" t="n"/>
@@ -9117,23 +9133,23 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES ANDREA</t>
+          <t>BATERÍAS PARA AUTO LTH</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Av. Gobernador Lic. Ignacio Pichardo Pagaza Mz4 Lt2, Cd Amanecer, 55267 Ecatepec de Morelos, Méx., México</t>
+          <t>Calle Bosque De San Marcos, Jardines de Morelos, 55070 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>19.5104665</v>
+        <v>19.5950868</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>-99.02466080000001</v>
+        <v>-99.0021826</v>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
@@ -9147,12 +9163,12 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES ANDREA</t>
+          <t>ACUMULADORES SINTERGIA</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>LTH, America</t>
+          <t>LTH, América Racing, Xtreme</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -9162,17 +9178,17 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>La foto de Google Maps muestra baterias reales de las marcas LTH y America apiladas en anaqueles detras de una reja de seguridad, con un cartel de '48 meses de garantia'.</t>
+          <t>Las fotos de Maps muestran un aparador con anaqueles metálicos repletos de baterías físicas de las marcas LTH, América Racing y Xtreme desde el piso hasta el techo, además de un despliegue individual de producto (batería Xtreme XT-42, América Racing y LTH) sobre un mostrador con accesorios de terminal.</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>Street View en el PIN exacto mostraba una panaderia ('Panaderia Chuco Vainilla'), un negocio distinto, por lo que se investigo el link de Maps: la foto de la propia ficha 'Acumuladores Andrea' muestra el rotulo azul 'ACUMULADORES ANDREA' sobre una cortina con baterias LTH y America visibles detras de la reja, confirmando nombre y giro exactos (el pin de Street View esta mal ubicado o corresponde a una toma vieja de un local vecino).</t>
+          <t>El Street View en las coordenadas registradas muestra un negocio de maderas/molduras sin relación alguna con baterías. Sin embargo, la ficha de Maps abierta con el link exacto del registro ('BATERÍAS PARA AUTO LTH', mismo place ID) tiene fotos propias del negocio que muestran el rótulo real 'ACUMULADORES SINTERGIA - BATERIAS - LA ENERGIA QUE NECESITA TU MOTOR' con anaqueles repletos de baterías físicas de varias marcas. El nombre visible en fachada difiere del registrado, pero el giro y la evidencia visual de venta de baterías son inequívocos, por lo que se prioriza la evidencia visual sobre el nombre registrado.</t>
         </is>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>fotos/143_acumuladores_andrea/maps_foto_1.jpg</t>
+          <t>fotos/123_baterias_para_auto_lth/streetview_1.jpg; fotos/123_baterias_para_auto_lth/streetview_2.jpg; fotos/123_baterias_para_auto_lth/maps_foto_1.jpg; fotos/123_baterias_para_auto_lth/maps_foto_2.jpg; fotos/123_baterias_para_auto_lth/maps_foto_3.jpg</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9189,23 +9205,23 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>LTH MCUMULADORES SANCHEZ</t>
+          <t>ACUMULADORES FUEGO NUEVO</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Av. Nacional 18, Sta Maria Chiconautla, 55066 Ecatepec de Morelos, Méx., México</t>
+          <t>Av. Fuego Nuevo 70, Cd Azteca 2da Secc, 55450 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>19.6336485</v>
+        <v>19.5484092</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>-99.002315</v>
+        <v>-99.0330062</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
@@ -9219,37 +9235,33 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>LTH ACUMULADORES SANCHEZ</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>LTH</t>
-        </is>
-      </c>
+          <t>ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n"/>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>No se ven baterias fisicas en anaquel; se ve un mural pintado en la fachada con el logo LTH y una bateria dibujada (grafico, no producto real), junto con el texto 'ACUMULADORES SANCHEZ'.</t>
+          <t>Ambas fotos de Street View muestran un aparador rojo con múltiples baterías físicas de color negro apiladas en varios niveles; las etiquetas de marca no son legibles con suficiente nitidez en la imagen para identificarlas con certeza.</t>
         </is>
       </c>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>El nombre 'SANCHEZ' y el logo de marca LTH aparecen pintados directamente en la fachada de la esquina exacta del PIN, con el texto 'ACUMULADORES' tambien visible, coincidiendo con el registro 'LTH MCUMULADORES SANCHEZ'.</t>
+          <t>El Street View en las coordenadas exactas muestra con claridad el letrero 'ACUMULADORES FUEGO NUEVO', coincidiendo exactamente con el nombre registrado, junto con el texto 'VENTA DE TERMINALES, ACIDO, CHEQUEO POR SCANNER' y un aparador con baterías físicas visibles en ambas tomas.</t>
         </is>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>fotos/144_lth_mcumuladores_sanchez/streetview_1.jpg; fotos/144_lth_mcumuladores_sanchez/streetview_2.jpg</t>
+          <t>fotos/124_acumuladores_fuego_nuevo/streetview_1.jpg; fotos/124_acumuladores_fuego_nuevo/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>streetview_2.jpg</t>
+          <t>streetview_1.jpg</t>
         </is>
       </c>
       <c r="O125" s="3" t="n"/>
@@ -9261,23 +9273,23 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>ACUMULADORES CAMILA</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>C. Cerro de la Estrella 100, Sagitario 3, 55238 Ecatepec de Morelos, Méx., México</t>
+          <t>Vía Adolfo López Mateos 2062, El Cegor, 55127 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>19.4958195</v>
+        <v>19.5397658</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>-99.0205964</v>
+        <v>-99.0409576</v>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
@@ -9291,37 +9303,37 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>LTH - ACUMULADORES BATERIAS (Carga de Bateria Rapida y Lenta)</t>
+          <t>ACUMULADORES CAMILA</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>LTH, América Racing, EverStart, ACDelco, Dynamo, CAR 100</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>Se ven murales pintados de baterias LTH en la fachada (graficos, no fotos de producto real); dentro del local hay anaqueles con cajas y mercancia diversa, pero no se distinguen baterias fisicas con claridad.</t>
+          <t>Las fotos de Maps muestran anaqueles metálicos repletos de baterías físicas de las marcas LTH, América Racing, EverStart, ACDelco, Dynamo y CAR 100, bajo el rótulo 'ACUMULADORES CAMILA - LTH - CARGA Y VENTA - NUEVAS Y SEMINUEVAS' pintado sobre la cortina de entrada.</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>La fachada en el PIN exacto tiene pintado el texto 'CARGA DE BATERIA ACUMULADORES BATERIAS RAPIDA Y LENTA' junto con el logo LTH repetido varias veces, coincidiendo con el nombre registrado 'LTH'.</t>
+          <t>El Street View en las coordenadas exactas muestra una fachada azul con un letrero distinto e ilegible que no corresponde a una tienda de baterías. Sin embargo, las fotos propias del negocio en su ficha de Maps muestran con total claridad el rótulo 'ACUMULADORES CAMILA', coincidiendo exactamente con el nombre registrado, y anaqueles llenos de baterías físicas de múltiples marcas.</t>
         </is>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>fotos/145_lth/streetview_1.jpg; fotos/145_lth/streetview_2.jpg</t>
+          <t>fotos/125_acumuladores_camila/streetview_1.jpg; fotos/125_acumuladores_camila/streetview_2.jpg; fotos/125_acumuladores_camila/maps_foto_1.jpg; fotos/125_acumuladores_camila/maps_foto_2.jpg</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>streetview_1.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O126" s="3" t="n"/>
@@ -9333,23 +9345,23 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Acumuladores los Gemelos las américas</t>
+          <t>Centro Distribución LTH</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Bosque de Ombues 3, Fraccionamiento Las Americas, Las Américas, 55076 Ecatepec de Morelos, Méx., México</t>
+          <t>Circunvalación Sur esquina Zihuatanejo 2, Jardines de Casa Nueva, 55430 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>19.5890478</v>
+        <v>19.5489461</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>-98.9997336</v>
+        <v>-99.04530560000001</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
@@ -9363,10 +9375,14 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>BATERIAS - Compra y Venta de Baterias Automotriz e Industrial</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n"/>
+          <t>Centro de Distribución LTH</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9374,22 +9390,22 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterias fisicas apiladas; el anuncio del toldo tiene iconos graficos de baterias (clip art), no fotos de producto real ni marcas especificas legibles.</t>
+          <t>Ambas fotos muestran el rótulo 'LTH - Centro de Distribución - BATERIAS' y una máquina expendedora de la marca LTH con gráfico de batería en la fachada; no se aprecia un mostrador abierto con baterías físicas apiladas, sino el punto de venta/distribución y la máquina de autoservicio.</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>El nombre exacto 'Los Gemelos' no es legible en la fachada, pero el giro coincide plenamente: el letrero dice 'BATERIAS - COMPRA Y VENTA DE BATERIAS AUTOMOTRIZ E INDUSTRIAL' en el domicilio exacto del PIN, lo cual confirma que es una tienda de baterias en ese sitio (se prioriza la evidencia visual del giro sobre el nombre exacto, segun la regla del proyecto).</t>
+          <t>El Street View en las coordenadas exactas muestra el letrero 'LTH - Centro de Distribución - BATERIAS', coincidiendo con el nombre registrado 'Centro Distribución LTH', junto con una máquina expendedora de baterías LTH instalada en la fachada del local.</t>
         </is>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>fotos/146_acumuladores_los_gemelos_las_americas/streetview_1.jpg; fotos/146_acumuladores_los_gemelos_las_americas/streetview_2.jpg</t>
+          <t>fotos/126_centro_distribucion_lth/streetview_1.jpg; fotos/126_centro_distribucion_lth/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>streetview_1.jpg</t>
+          <t>streetview_2.jpg</t>
         </is>
       </c>
       <c r="O127" s="3" t="n"/>
@@ -9401,23 +9417,23 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Baterías de gel bolaños</t>
+          <t>ACUMULADORES "MORENO"</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Gobernador Rafael M. Hidalgo 69-Local 6, Granjas Valle de Guadalupe, 55270 Ecatepec de Morelos, Méx., México</t>
+          <t>Vía Adolfo López Mateos 3295, Miguel Hidalgo, 55490 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>19.5062261</v>
+        <v>19.5339204</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>-99.0566271</v>
+        <v>-99.0464537</v>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
@@ -9429,26 +9445,30 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="H128" s="2" t="n"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>MORENO (Acumuladores Moreno)</t>
+        </is>
+      </c>
       <c r="I128" s="2" t="n"/>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterias en ninguna foto disponible (ni Street View ni la ficha de Maps, que solo repite la misma foto de la cortina cerrada sin rotulo visible).</t>
+          <t>Ambas fotos de Street View muestran un anaquel amarillo/azul con múltiples baterías físicas apiladas bajo el rótulo 'MORENO BATERIAS de GEL-1000', junto con una lista de precios por tamaño (mini, chica, mediana, tornillo, camión); no se distinguen logos de marcas de terceros, solo la marca propia del negocio.</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: ni Street View ni la galeria de Maps muestran rotulo o producto visible (cortina azul cerrada sin ningun letrero, junto a un taller de 'Clutch y Frenos'). Sin embargo, una resena de un cliente en la ficha de Maps confirma la venta de baterias en este domicilio exacto: 'No tiene nada de baterias nuevas, tiene puras baterias usadas que no sirven... El senor nunca esta... y sobre la compra no hay garantia CUIDADO'. La ficha tambien esta categorizada por Google como 'Tienda de baterias para automovil' y ofrece 'Entrega a domicilio', consistente con un negocio sin aparador visible.</t>
+          <t>El Street View en las coordenadas exactas muestra con claridad el nombre 'MORENO', coincidiendo con el registrado 'ACUMULADORES MORENO', con baterías físicas visibles en el anaquel y letreros de 'SE COMPRAN BATERIAS' y lista de precios de baterías por tamaño.</t>
         </is>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>fotos/147_baterias_de_gel_bolanos/streetview_1.jpg; fotos/147_baterias_de_gel_bolanos/streetview_2.jpg</t>
+          <t>fotos/127_acumuladores_moreno/streetview_1.jpg; fotos/127_acumuladores_moreno/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9465,23 +9485,23 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SafeLithium - Venta, Calculo, Diseño, Armado y reparacion de baterias de Litio</t>
+          <t>ACUMULADORES MARTINEZ</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>C. 309-A 67, El Coyol, Gustavo A. Madero, 07420 Ciudad de México, CDMX, México</t>
+          <t>Av. Insurgentes 148, El Calvario, 55020 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>19.4871735</v>
+        <v>19.6028217</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>-99.0910883</v>
+        <v>-99.0569216</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
@@ -9490,7 +9510,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H129" s="2" t="n"/>
@@ -9502,22 +9522,22 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>Las fotos propias de la ficha de Maps muestran celdas de litio reales: un banco de celdas prismaticas tipo LiFePO4 (etiquetadas '442B') conectadas con barras de cobre y cableado, y otra foto de un paquete de celdas cilindricas 18650 ensambladas -- es decir, baterias de litio fisicas en proceso de armado.</t>
+          <t>No se aprecian baterías en ninguna foto disponible; el Street View muestra un letrero de 'RÓTULOS - TOLDOS FIJOS Y ENROLLABLES', un laboratorio/consultorio médico y una tienda de artículos de fiesta ('Mi Lugar Favorito'), sin relación alguna a baterías.</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: Street View en el PIN exacto solo muestra una casa habitacion azul sin ningun letrero comercial visible (el negocio opera aparentemente desde un taller/domicilio sin aparador publico). No obstante, la propia ficha de Maps de 'SafeLithium' tiene fotos subidas por el negocio mostrando celdas de litio reales siendo armadas en paquetes de baterias, lo cual confirma que si fabrican/venden baterias de litio tal como indica su nombre y giro.</t>
+          <t>El Street View en las coordenadas exactas no muestra el nombre 'Acumuladores Martinez' ni ningún negocio de baterías; en su lugar aparecen un taller de rótulos/toldos y un laboratorio médico. La ficha de Maps no tiene fotos propias del negocio ni reseñas, y el negocio aparece marcado como 'Cerrado temporalmente'. No hay evidencia visual ni textual disponible que confirme venta de baterías en este domicilio.</t>
         </is>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_2.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_2.jpg</t>
+          <t>fotos/128_acumuladores_martinez/streetview_1.jpg; fotos/128_acumuladores_martinez/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_1.jpg</t>
+          <t>streetview_1.jpg</t>
         </is>
       </c>
       <c r="O129" s="3" t="n"/>
@@ -9529,23 +9549,23 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Baterías Vargas</t>
+          <t>Baterías "El Gabo"</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Vía Morelos 425, Cuauhtemoc Xalostoc, 55310 Ecatepec de Morelos, Méx., México</t>
+          <t>Av Acueducto 47, Jorge Jimenez Cantu, 54190 Tlalnepantla, Méx., México</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>19.5309639</v>
+        <v>19.5335734</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>-99.07474740000001</v>
+        <v>-99.0904464</v>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
@@ -9559,12 +9579,12 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Baterias Nuevas y Seminuevas (Via Morelos No425)</t>
+          <t>BATERIAS EL GABO</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>LTH, America Racing, Optima, Gonher</t>
+          <t>Mopar, Kirkland, América Racing, Moura</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -9574,22 +9594,22 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>Las fotos de la propia ficha de Maps muestran anaqueles con baterias fisicas reales de las marcas LTH, America Racing y Optima (bateria amarilla), ademas de cajas de baterias de motocicleta LTH y America, y un letrero 'Baterias Nuevas y Seminuevas desde $499'.</t>
+          <t>Las fotos de Maps muestran la fachada con el rótulo 'BATERIAS EL GABO' y letreros de 'COMPRA DE CASCOS' y 'REPARACIÓN DE BATERIAS', además de un anaquel interior con baterías físicas de marca propia 'Baterías El Gabo' y de las marcas Mopar, Kirkland, América Racing y Moura.</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>Street View en el PIN exacto mostraba un negocio de tortillas/muebles distinto (sin relacion), por lo que se investigo el link de Maps: las fotos propias de la ficha muestran un aparador con placa 'VIA MORELOS No 425' (coincide exactamente con la direccion registrada) y anaqueles repletos de baterias reales LTH/America/Optima, ademas de un banner de 'Baterias Nuevas y Seminuevas'. Aunque el rotulo no dice literalmente 'Vargas', la direccion exacta y la evidencia fotografica del giro son concluyentes.</t>
+          <t>El Street View en las coordenadas exactas muestra un spa ('Spa JC') sin relación alguna con baterías. Sin embargo, las fotos propias de la ficha de Maps 'Baterías El Gabo' (mismo place ID que el link registrado) muestran con claridad el rótulo exacto 'BATERIAS EL GABO' en la fachada y un anaquel con baterías físicas de varias marcas en el interior.</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>fotos/149_baterias_vargas/maps_foto_1.jpg; fotos/149_baterias_vargas/maps_foto_2.jpg</t>
+          <t>fotos/129_baterias_el_gabo/streetview_1.jpg; fotos/129_baterias_el_gabo/streetview_2.jpg; fotos/129_baterias_el_gabo/maps_foto_1.jpg; fotos/129_baterias_el_gabo/maps_foto_2.jpg</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_2.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O130" s="3" t="n"/>
@@ -9601,23 +9621,23 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES DE LA GARZA</t>
+          <t>CENTRO DE SERVICIO H&amp;H</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Real del Monte 2, Guadalupe Insurgentes, Gustavo A. Madero, 07870 Ciudad de México, CDMX, México</t>
+          <t>Av. Insurgentes 101, San Cristóbal Centro, 55000 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>19.4701634</v>
+        <v>19.6007142</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>-99.1320714</v>
+        <v>-99.0532973</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
@@ -9626,19 +9646,11 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>ACUMULADORES DE LA GARZA</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>LTH</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9646,22 +9658,22 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>No se distinguen baterias de auto apiladas con claridad en el aparador (se ven articulos pequenos como accesorios/electronica); si es visible un letrero de precios 'COMPRO CASCOS - MINI $100, CHICA $120...' (compra de cascos/nucleos de bateria usada) y el logo LTH en el toldo.</t>
+          <t>No se aprecian baterías en ninguna foto disponible; el Street View muestra una tienda de pañales ('Pañal Americano'), un negocio de stickers/publicidad ('SKA Publicidad') y un local de copias e impresiones, sin relación alguna a baterías.</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>El nombre 'ACUMULADORES DE LA GARZA' coincide exactamente con el rotulo verde de la fachada en el PIN exacto, junto con el logo de la marca LTH en el toldo blanco y un letrero de 'COMPRO CASCOS' con tarifas por tamano de bateria (Mini/Chica/Mediana), practica caracteristica de una tienda de baterias.</t>
+          <t>El Street View en las coordenadas exactas no muestra el nombre 'Centro de Servicio H&amp;H' ni ningún negocio de baterías. La ficha de Maps no tiene ninguna foto propia ni reseñas que confirmen venta de baterías en este domicilio. No hay evidencia visual ni textual disponible.</t>
         </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>fotos/150_acumuladores_de_la_garza/streetview_1.jpg; fotos/150_acumuladores_de_la_garza/streetview_2.jpg</t>
+          <t>fotos/130_centro_de_servicio_h_h/streetview_1.jpg; fotos/130_centro_de_servicio_h_h/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>streetview_2.jpg</t>
+          <t>streetview_1.jpg</t>
         </is>
       </c>
       <c r="O131" s="3" t="n"/>
@@ -9671,8 +9683,708 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>DIST. DE ACUMULADORES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Av. Valle de Santiago 162, Valle de Aragon 3ra Secc, 55280 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>19.5015367</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>-99.0502637</v>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES HERNANDEZ (LTH)</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias fisicas: la cortina metalica del local esta cerrada en ambas fotos de Street View, con un puesto de comida instalado enfrente. Solo se ve el letrero de lona 'LTH ACUMULADORES HERNANDEZ' sobre la cortina.</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'ACUMULADORES HERNANDEZ' coincide exactamente con el letrero visible en la fachada en las coordenadas exactas, junto con el logo de la marca LTH. El local esta cerrado (cortina abajo) en el momento de la captura, por lo que no se ven baterias fisicas, pero el rotulo y la marca son evidencia suficiente de que es una tienda de baterias.</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>fotos/141_dist_de_acumuladores_hernandez/streetview_1.jpg; fotos/141_dist_de_acumuladores_hernandez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O132" s="3" t="n"/>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Av Sta Teresa 25, Granjas Valle de Guadalupe Secc B, 55200 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>19.5281143</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>-99.0513169</v>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>AFN ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America, Full Power, Duralast, Lorenzini, Motorcraft</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>En la foto de Google Maps se ven multiples anaqueles con decenas de baterias de auto y moto reales, ademas de un cartel 'BATERIAS NUEVAS DESDE $999' y logos de varias marcas (LTH, America, Full Power, Duralast, Lorenzini, Motorcraft) en la fachada.</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de Street View en el PIN exacto mostraban un negocio distinto (comercio de electrodomesticos Maytag/Sanyo), asi que se investigo el link de Maps: la foto propia de la ficha 'Acumuladores Fuego Nuevo' muestra el rotulo 'AFN ACUMULADORES FUEGO NUEVO' y anaqueles repletos de baterias reales, confirmando el giro y el nombre exacto del negocio (el pin de Street View esta mal ubicado, pero la foto de la propia ficha de Maps prueba la fachada real).</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>fotos/142_acumuladores_fuego_nuevo/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="n"/>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ANDREA</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Av. Gobernador Lic. Ignacio Pichardo Pagaza Mz4 Lt2, Cd Amanecer, 55267 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>19.5104665</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>-99.02466080000001</v>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ANDREA</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>La foto de Google Maps muestra baterias reales de las marcas LTH y America apiladas en anaqueles detras de una reja de seguridad, con un cartel de '48 meses de garantia'.</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto mostraba una panaderia ('Panaderia Chuco Vainilla'), un negocio distinto, por lo que se investigo el link de Maps: la foto de la propia ficha 'Acumuladores Andrea' muestra el rotulo azul 'ACUMULADORES ANDREA' sobre una cortina con baterias LTH y America visibles detras de la reja, confirmando nombre y giro exactos (el pin de Street View esta mal ubicado o corresponde a una toma vieja de un local vecino).</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>fotos/143_acumuladores_andrea/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="n"/>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>LTH MCUMULADORES SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Av. Nacional 18, Sta Maria Chiconautla, 55066 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>19.6336485</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>-99.002315</v>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>LTH ACUMULADORES SANCHEZ</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas en anaquel; se ve un mural pintado en la fachada con el logo LTH y una bateria dibujada (grafico, no producto real), junto con el texto 'ACUMULADORES SANCHEZ'.</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'SANCHEZ' y el logo de marca LTH aparecen pintados directamente en la fachada de la esquina exacta del PIN, con el texto 'ACUMULADORES' tambien visible, coincidiendo con el registro 'LTH MCUMULADORES SANCHEZ'.</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>fotos/144_lth_mcumuladores_sanchez/streetview_1.jpg; fotos/144_lth_mcumuladores_sanchez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O135" s="3" t="n"/>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>C. Cerro de la Estrella 100, Sagitario 3, 55238 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>19.4958195</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>-99.0205964</v>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>LTH - ACUMULADORES BATERIAS (Carga de Bateria Rapida y Lenta)</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>Se ven murales pintados de baterias LTH en la fachada (graficos, no fotos de producto real); dentro del local hay anaqueles con cajas y mercancia diversa, pero no se distinguen baterias fisicas con claridad.</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>La fachada en el PIN exacto tiene pintado el texto 'CARGA DE BATERIA ACUMULADORES BATERIAS RAPIDA Y LENTA' junto con el logo LTH repetido varias veces, coincidiendo con el nombre registrado 'LTH'.</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>fotos/145_lth/streetview_1.jpg; fotos/145_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O136" s="3" t="n"/>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores los Gemelos las américas</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Bosque de Ombues 3, Fraccionamiento Las Americas, Las Américas, 55076 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>19.5890478</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>-98.9997336</v>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS - Compra y Venta de Baterias Automotriz e Industrial</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n"/>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias fisicas apiladas; el anuncio del toldo tiene iconos graficos de baterias (clip art), no fotos de producto real ni marcas especificas legibles.</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>El nombre exacto 'Los Gemelos' no es legible en la fachada, pero el giro coincide plenamente: el letrero dice 'BATERIAS - COMPRA Y VENTA DE BATERIAS AUTOMOTRIZ E INDUSTRIAL' en el domicilio exacto del PIN, lo cual confirma que es una tienda de baterias en ese sitio (se prioriza la evidencia visual del giro sobre el nombre exacto, segun la regla del proyecto).</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>fotos/146_acumuladores_los_gemelos_las_americas/streetview_1.jpg; fotos/146_acumuladores_los_gemelos_las_americas/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O137" s="3" t="n"/>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Baterías de gel bolaños</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Gobernador Rafael M. Hidalgo 69-Local 6, Granjas Valle de Guadalupe, 55270 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>19.5062261</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>-99.0566271</v>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n"/>
+      <c r="I138" s="2" t="n"/>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias en ninguna foto disponible (ni Street View ni la ficha de Maps, que solo repite la misma foto de la cortina cerrada sin rotulo visible).</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ni Street View ni la galeria de Maps muestran rotulo o producto visible (cortina azul cerrada sin ningun letrero, junto a un taller de 'Clutch y Frenos'). Sin embargo, una resena de un cliente en la ficha de Maps confirma la venta de baterias en este domicilio exacto: 'No tiene nada de baterias nuevas, tiene puras baterias usadas que no sirven... El senor nunca esta... y sobre la compra no hay garantia CUIDADO'. La ficha tambien esta categorizada por Google como 'Tienda de baterias para automovil' y ofrece 'Entrega a domicilio', consistente con un negocio sin aparador visible.</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>fotos/147_baterias_de_gel_bolanos/streetview_1.jpg; fotos/147_baterias_de_gel_bolanos/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O138" s="3" t="n"/>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SafeLithium - Venta, Calculo, Diseño, Armado y reparacion de baterias de Litio</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>C. 309-A 67, El Coyol, Gustavo A. Madero, 07420 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>19.4871735</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>-99.0910883</v>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="n"/>
+      <c r="I139" s="2" t="n"/>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos propias de la ficha de Maps muestran celdas de litio reales: un banco de celdas prismaticas tipo LiFePO4 (etiquetadas '442B') conectadas con barras de cobre y cableado, y otra foto de un paquete de celdas cilindricas 18650 ensambladas -- es decir, baterias de litio fisicas en proceso de armado.</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View en el PIN exacto solo muestra una casa habitacion azul sin ningun letrero comercial visible (el negocio opera aparentemente desde un taller/domicilio sin aparador publico). No obstante, la propia ficha de Maps de 'SafeLithium' tiene fotos subidas por el negocio mostrando celdas de litio reales siendo armadas en paquetes de baterias, lo cual confirma que si fabrican/venden baterias de litio tal como indica su nombre y giro.</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_2.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O139" s="3" t="n"/>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Vargas</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Vía Morelos 425, Cuauhtemoc Xalostoc, 55310 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>19.5309639</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>-99.07474740000001</v>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Baterias Nuevas y Seminuevas (Via Morelos No425)</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America Racing, Optima, Gonher</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de la propia ficha de Maps muestran anaqueles con baterias fisicas reales de las marcas LTH, America Racing y Optima (bateria amarilla), ademas de cajas de baterias de motocicleta LTH y America, y un letrero 'Baterias Nuevas y Seminuevas desde $499'.</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto mostraba un negocio de tortillas/muebles distinto (sin relacion), por lo que se investigo el link de Maps: las fotos propias de la ficha muestran un aparador con placa 'VIA MORELOS No 425' (coincide exactamente con la direccion registrada) y anaqueles repletos de baterias reales LTH/America/Optima, ademas de un banner de 'Baterias Nuevas y Seminuevas'. Aunque el rotulo no dice literalmente 'Vargas', la direccion exacta y la evidencia fotografica del giro son concluyentes.</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>fotos/149_baterias_vargas/maps_foto_1.jpg; fotos/149_baterias_vargas/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O140" s="3" t="n"/>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES DE LA GARZA</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Real del Monte 2, Guadalupe Insurgentes, Gustavo A. Madero, 07870 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>19.4701634</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>-99.1320714</v>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES DE LA GARZA</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>No se distinguen baterias de auto apiladas con claridad en el aparador (se ven articulos pequenos como accesorios/electronica); si es visible un letrero de precios 'COMPRO CASCOS - MINI $100, CHICA $120...' (compra de cascos/nucleos de bateria usada) y el logo LTH en el toldo.</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'ACUMULADORES DE LA GARZA' coincide exactamente con el rotulo verde de la fachada en el PIN exacto, junto con el logo de la marca LTH en el toldo blanco y un letrero de 'COMPRO CASCOS' con tarifas por tamano de bateria (Mini/Chica/Mediana), practica caracteristica de una tienda de baterias.</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>fotos/150_acumuladores_de_la_garza/streetview_1.jpg; fotos/150_acumuladores_de_la_garza/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O141" s="3" t="n"/>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P131"/>
+  <autoFilter ref="A1:P141"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -9804,6 +10516,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$P$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validacion'!$A$1:$P$271</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9685,23 +9685,23 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>DIST. DE ACUMULADORES HERNANDEZ</t>
+          <t>Baterías Serrauto</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Av. Valle de Santiago 162, Valle de Aragon 3ra Secc, 55280 Ecatepec de Morelos, Méx., México</t>
+          <t>Cda. N. Heroes 3, San Luis Tlatilco, 53580 Naucalpan de Juárez, Méx., México</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>19.5015367</v>
+        <v>19.4636058</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>-99.0502637</v>
+        <v>-99.24070209999999</v>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
@@ -9715,65 +9715,65 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES HERNANDEZ (LTH)</t>
+          <t>Baterías SerrAuto</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>Gonher, Exide, LTH, Duracell, Diener, América Racing, Dynamo, Cronos, Extrema Titanio</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterias fisicas: la cortina metalica del local esta cerrada en ambas fotos de Street View, con un puesto de comida instalado enfrente. Solo se ve el letrero de lona 'LTH ACUMULADORES HERNANDEZ' sobre la cortina.</t>
+          <t>maps_foto_1 muestra la fachada completa 'BATERIAS SERRAUTO' con rotulo de 9 marcas y anaquel bajo el letrero 'BATERIAS'; maps_foto_2/3 son fotos de resena con baterias instaladas en cofres de auto.</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>El nombre 'ACUMULADORES HERNANDEZ' coincide exactamente con el letrero visible en la fachada en las coordenadas exactas, junto con el logo de la marca LTH. El local esta cerrado (cortina abajo) en el momento de la captura, por lo que no se ven baterias fisicas, pero el rotulo y la marca son evidencia suficiente de que es una tienda de baterias.</t>
+          <t>Street View en coords exactas muestra 'Vidrios Zamora' (vecino, pin desplazado dentro del mismo predio industrial 'MAQSIND'). La ficha 'Baterias Serrauto' (3.9, 28 opiniones, misma direccion) tiene en su galeria la foto real del rotulo con 9 marcas. Resenas confirman queja de garantia de baterias Gonher compradas ahi.</t>
         </is>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>fotos/141_dist_de_acumuladores_hernandez/streetview_1.jpg; fotos/141_dist_de_acumuladores_hernandez/streetview_2.jpg</t>
+          <t>fotos/131_baterias_serrauto/streetview_1.jpg; fotos/131_baterias_serrauto/streetview_2.jpg; fotos/131_baterias_serrauto/maps_foto_1.jpg; fotos/131_baterias_serrauto/maps_foto_2.jpg; fotos/131_baterias_serrauto/maps_foto_3.jpg</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>streetview_2.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O132" s="3" t="n"/>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES FUEGO NUEVO</t>
+          <t>ACUMULADORES POWER 3</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Av Sta Teresa 25, Granjas Valle de Guadalupe Secc B, 55200 Ecatepec de Morelos, Méx., México</t>
+          <t>Ciruela 6206, Vivienda del Taxista, 55050 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>19.5281143</v>
+        <v>19.5992024</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>-99.0513169</v>
+        <v>-99.01775720000001</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
@@ -9785,16 +9785,8 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>AFN ACUMULADORES FUEGO NUEVO</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>LTH, America, Full Power, Duralast, Lorenzini, Motorcraft</t>
-        </is>
-      </c>
+      <c r="H133" s="2" t="n"/>
+      <c r="I133" s="2" t="n"/>
       <c r="J133" s="2" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9802,17 +9794,17 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>En la foto de Google Maps se ven multiples anaqueles con decenas de baterias de auto y moto reales, ademas de un cartel 'BATERIAS NUEVAS DESDE $999' y logos de varias marcas (LTH, America, Full Power, Duralast, Lorenzini, Motorcraft) en la fachada.</t>
+          <t>maps_foto_1: banner 'BATERIAS VENTA Y COMPRA, CARGA DE BATERIAS, NUEVAS Y DE ASEGURADORA' con anaquel de baterias reales junto a la entrada.</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>Las fotos de Street View en el PIN exacto mostraban un negocio distinto (comercio de electrodomesticos Maytag/Sanyo), asi que se investigo el link de Maps: la foto propia de la ficha 'Acumuladores Fuego Nuevo' muestra el rotulo 'AFN ACUMULADORES FUEGO NUEVO' y anaqueles repletos de baterias reales, confirmando el giro y el nombre exacto del negocio (el pin de Street View esta mal ubicado, pero la foto de la propia ficha de Maps prueba la fachada real).</t>
+          <t>Street View muestra grua/renta y entrada morada sin nombre claro. Ficha 'Acumuladores power 3' coincide en direccion y el telefono del banner es identico al registrado, confirmando la foto.</t>
         </is>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>fotos/142_acumuladores_fuego_nuevo/maps_foto_1.jpg</t>
+          <t>fotos/132_acumuladores_power_3/streetview_1.jpg; fotos/132_acumuladores_power_3/streetview_2.jpg; fotos/132_acumuladores_power_3/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -9823,29 +9815,29 @@
       <c r="O133" s="3" t="n"/>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES ANDREA</t>
+          <t>BATERIAS PARA CARROS</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Av. Gobernador Lic. Ignacio Pichardo Pagaza Mz4 Lt2, Cd Amanecer, 55267 Ecatepec de Morelos, Méx., México</t>
+          <t>Av. José López Portillo 148, San Cristóbal, 55024 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>19.5104665</v>
+        <v>19.61228</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>-99.02466080000001</v>
+        <v>-99.05949</v>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
@@ -9857,14 +9849,10 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>ACUMULADORES ANDREA</t>
-        </is>
-      </c>
+      <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>LTH, America</t>
+          <t>LTH, América Racing, NGK, Bardahl</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -9874,50 +9862,50 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>La foto de Google Maps muestra baterias reales de las marcas LTH y America apiladas en anaqueles detras de una reja de seguridad, con un cartel de '48 meses de garantia'.</t>
+          <t>maps_foto_1: mostrador interior con vitrina de aceites y calcomanias America Racing/LTH. maps_foto_2: anaquel exterior con baterias LTH y America Racing.</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>Street View en el PIN exacto mostraba una panaderia ('Panaderia Chuco Vainilla'), un negocio distinto, por lo que se investigo el link de Maps: la foto de la propia ficha 'Acumuladores Andrea' muestra el rotulo azul 'ACUMULADORES ANDREA' sobre una cortina con baterias LTH y America visibles detras de la reja, confirmando nombre y giro exactos (el pin de Street View esta mal ubicado o corresponde a una toma vieja de un local vecino).</t>
+          <t>Cerrado temporalmente. Street View muestra mueblería (mismatch). Ficha Maps 'Baterias Para Carros' (misma direccion) tiene en su galeria las fotos de mostrador/anaquel con baterias fisicas de marca.</t>
         </is>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>fotos/143_acumuladores_andrea/maps_foto_1.jpg</t>
+          <t>fotos/133_baterias_para_carros/streetview_1.jpg; fotos/133_baterias_para_carros/streetview_2.jpg; fotos/133_baterias_para_carros/maps_foto_1.jpg; fotos/133_baterias_para_carros/maps_foto_2.jpg</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_1.jpg</t>
+          <t>maps_foto_2.jpg</t>
         </is>
       </c>
       <c r="O134" s="3" t="n"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>LTH MCUMULADORES SANCHEZ</t>
+          <t>ACUMULADORES NASCAR</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Av. Nacional 18, Sta Maria Chiconautla, 55066 Ecatepec de Morelos, Méx., México</t>
+          <t>Emiliano Zapata Esquina, Miguel Hidalgo, 55490 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>19.6336485</v>
+        <v>19.5298359</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>-99.002315</v>
+        <v>-99.05027200000001</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
@@ -9931,14 +9919,10 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>LTH ACUMULADORES SANCHEZ</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>LTH</t>
-        </is>
-      </c>
+          <t>ACUMULADORES DAYTONA (no coincide con 'Nascar' registrado, mismo domicilio exacto y mismo giro)</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9946,17 +9930,17 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>No se ven baterias fisicas en anaquel; se ve un mural pintado en la fachada con el logo LTH y una bateria dibujada (grafico, no producto real), junto con el texto 'ACUMULADORES SANCHEZ'.</t>
+          <t>No disponible -- la ficha solo tiene categoria Street View, sin fotos del propietario</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>El nombre 'SANCHEZ' y el logo de marca LTH aparecen pintados directamente en la fachada de la esquina exacta del PIN, con el texto 'ACUMULADORES' tambien visible, coincidiendo con el registro 'LTH MCUMULADORES SANCHEZ'.</t>
+          <t>LIMITACION: no hay foto de producto/mostrador en Maps; veredicto basado en rotulo de fachada visible en Street View. Cerrado temporalmente. Ambas tomas de Street View en el pin exacto muestran 'ACUMULADORES DAYTONA', no 'Nascar'. Resenas (4.8/5) genericas de precio/servicio. Se prioriza evidencia visual (mismo domicilio, mismo giro) sobre el nombre registrado -- caso limite, documentado para revision del equipo.</t>
         </is>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>fotos/144_lth_mcumuladores_sanchez/streetview_1.jpg; fotos/144_lth_mcumuladores_sanchez/streetview_2.jpg</t>
+          <t>fotos/134_acumuladores_nascar/streetview_1.jpg; fotos/134_acumuladores_nascar/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -9967,29 +9951,29 @@
       <c r="O135" s="3" t="n"/>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>ACUMULADORES IDEAL</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>C. Cerro de la Estrella 100, Sagitario 3, 55238 Ecatepec de Morelos, Méx., México</t>
+          <t>Insurgentes 404, San Pedro Xalostoc, 55310 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>19.4958195</v>
+        <v>19.5360208</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>-99.0205964</v>
+        <v>-99.0778466</v>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
@@ -10003,12 +9987,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>LTH - ACUMULADORES BATERIAS (Carga de Bateria Rapida y Lenta)</t>
+          <t>ACUMULADORES IDEAL</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>LTH, América Racing</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -10018,50 +10002,50 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>Se ven murales pintados de baterias LTH en la fachada (graficos, no fotos de producto real); dentro del local hay anaqueles con cajas y mercancia diversa, pero no se distinguen baterias fisicas con claridad.</t>
+          <t>maps_foto_1: cortina metalica con rotulo 'ACUMULADORES IDEAL', LTH grande, 'CARGA DE BATERIAS', cartel America Racing (cortina cerrada, sin producto visible)</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>La fachada en el PIN exacto tiene pintado el texto 'CARGA DE BATERIA ACUMULADORES BATERIAS RAPIDA Y LENTA' junto con el logo LTH repetido varias veces, coincidiendo con el nombre registrado 'LTH'.</t>
+          <t>Street View muestra 'EL MUÑECO' (soldadura, mismatch). Ficha Maps 'ACUMULADORES IDEAL' (4.7/6, misma direccion) tiene foto de galeria con el rotulo exacto. Resenas explicitas: 'tambien arreglan baterias', 'el mejor lugar para adquirir tu bateria'. Cerrado temporalmente.</t>
         </is>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>fotos/145_lth/streetview_1.jpg; fotos/145_lth/streetview_2.jpg</t>
+          <t>fotos/135_acumuladores_ideal/streetview_1.jpg; fotos/135_acumuladores_ideal/streetview_2.jpg; fotos/135_acumuladores_ideal/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>streetview_1.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O136" s="3" t="n"/>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Acumuladores los Gemelos las américas</t>
+          <t>VENTA DE BATERIAS DURACELL</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Bosque de Ombues 3, Fraccionamiento Las Americas, Las Américas, 55076 Ecatepec de Morelos, Méx., México</t>
+          <t>Av. de las Bombas 22, Viento Nuevo, 55074 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>19.5890478</v>
+        <v>19.6132461</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>-98.9997336</v>
+        <v>-98.9979347</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
@@ -10075,61 +10059,65 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>BATERIAS - Compra y Venta de Baterias Automotriz e Industrial</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="n"/>
+          <t>BATERIAS DURACELL / BATTERY CLUB</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Duracell, V8, Autobat, LTH</t>
+        </is>
+      </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterias fisicas apiladas; el anuncio del toldo tiene iconos graficos de baterias (clip art), no fotos de producto real ni marcas especificas legibles.</t>
+          <t>maps_foto_1: aparador con anaqueles de baterias Duracell fisicas (promociones) mas banner 'Battery Club' con LTH y V8/Autobat</t>
         </is>
       </c>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>El nombre exacto 'Los Gemelos' no es legible en la fachada, pero el giro coincide plenamente: el letrero dice 'BATERIAS - COMPRA Y VENTA DE BATERIAS AUTOMOTRIZ E INDUSTRIAL' en el domicilio exacto del PIN, lo cual confirma que es una tienda de baterias en ese sitio (se prioriza la evidencia visual del giro sobre el nombre exacto, segun la regla del proyecto).</t>
+          <t>Street View muestra panaderia/papeleria (mismatch). Ficha Maps 'Venta de Baterias Duracell' (4.3/8, misma direccion) tiene foto de galeria del aparador real con Duracell. Cerrado temporalmente.</t>
         </is>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>fotos/146_acumuladores_los_gemelos_las_americas/streetview_1.jpg; fotos/146_acumuladores_los_gemelos_las_americas/streetview_2.jpg</t>
+          <t>fotos/136_venta_de_baterias_duracell/streetview_1.jpg; fotos/136_venta_de_baterias_duracell/streetview_2.jpg; fotos/136_venta_de_baterias_duracell/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>streetview_1.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O137" s="3" t="n"/>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Baterías de gel bolaños</t>
+          <t>LTH ACUMULADORES MEXICO</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Gobernador Rafael M. Hidalgo 69-Local 6, Granjas Valle de Guadalupe, 55270 Ecatepec de Morelos, Méx., México</t>
+          <t>Bolivia MZ 73-lote 1, Jardines de Cerro Gordo, 55100 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>19.5062261</v>
+        <v>19.55384</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>-99.0566271</v>
+        <v>-99.02061759999999</v>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
@@ -10141,59 +10129,67 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="H138" s="2" t="n"/>
-      <c r="I138" s="2" t="n"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing</t>
+        </is>
+      </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>No se aprecian baterias en ninguna foto disponible (ni Street View ni la ficha de Maps, que solo repite la misma foto de la cortina cerrada sin rotulo visible).</t>
+          <t>maps_foto_1: interior con rotulo LTH grande, anaqueles con baterias LTH, banner America Racing, lubricantes</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: ni Street View ni la galeria de Maps muestran rotulo o producto visible (cortina azul cerrada sin ningun letrero, junto a un taller de 'Clutch y Frenos'). Sin embargo, una resena de un cliente en la ficha de Maps confirma la venta de baterias en este domicilio exacto: 'No tiene nada de baterias nuevas, tiene puras baterias usadas que no sirven... El senor nunca esta... y sobre la compra no hay garantia CUIDADO'. La ficha tambien esta categorizada por Google como 'Tienda de baterias para automovil' y ofrece 'Entrega a domicilio', consistente con un negocio sin aparador visible.</t>
+          <t>Street View muestra edificio residencial con gimnasio RTA (mismatch). Ficha 'Lth Acumuladores Mexico' (4.0/2, misma direccion) tiene resena explicita: 'Tienda de venta de baterias para vehiculos automotores y aceites'. Cerrado temporalmente.</t>
         </is>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>fotos/147_baterias_de_gel_bolanos/streetview_1.jpg; fotos/147_baterias_de_gel_bolanos/streetview_2.jpg</t>
+          <t>fotos/137_lth_acumuladores_mexico/streetview_1.jpg; fotos/137_lth_acumuladores_mexico/streetview_2.jpg; fotos/137_lth_acumuladores_mexico/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>streetview_1.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O138" s="3" t="n"/>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SafeLithium - Venta, Calculo, Diseño, Armado y reparacion de baterias de Litio</t>
+          <t>ENERGICENTRO</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>C. 309-A 67, El Coyol, Gustavo A. Madero, 07420 Ciudad de México, CDMX, México</t>
+          <t>Vía Morelos 32, Santa Clara Coatitla, 55540 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>19.4871735</v>
+        <v>19.5336503</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>-99.0910883</v>
+        <v>-99.06762999999999</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
@@ -10202,10 +10198,14 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="n"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>EL SURTIDOR DEL TAXISTA (refaccionaria, no coincide con 'ENERGICENTRO' registrado)</t>
+        </is>
+      </c>
       <c r="I139" s="2" t="n"/>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10214,50 +10214,50 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>Las fotos propias de la ficha de Maps muestran celdas de litio reales: un banco de celdas prismaticas tipo LiFePO4 (etiquetadas '442B') conectadas con barras de cobre y cableado, y otra foto de un paquete de celdas cilindricas 18650 ensambladas -- es decir, baterias de litio fisicas en proceso de armado.</t>
+          <t>No disponible -- la ficha solo tiene categoria Street View</t>
         </is>
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: Street View en el PIN exacto solo muestra una casa habitacion azul sin ningun letrero comercial visible (el negocio opera aparentemente desde un taller/domicilio sin aparador publico). No obstante, la propia ficha de Maps de 'SafeLithium' tiene fotos subidas por el negocio mostrando celdas de litio reales siendo armadas en paquetes de baterias, lo cual confirma que si fabrican/venden baterias de litio tal como indica su nombre y giro.</t>
+          <t>Street View en el pin exacto muestra refaccionaria de auto-partes, sin rotulo de baterias. La ficha 'ENERGICENTRO' tiene calificacion 1.0 (2 opiniones) y AMBAS declaran explicitamente que esta ficha copio el nombre de una tienda real ubicada mas adelante. Existen fichas legitimas distintas 'Energycentro' en la zona. Cerrado temporalmente.</t>
         </is>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_2.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_2.jpg</t>
+          <t>fotos/138_energicentro/streetview_1.jpg; fotos/138_energicentro/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_1.jpg</t>
+          <t>streetview_1.jpg</t>
         </is>
       </c>
       <c r="O139" s="3" t="n"/>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Baterías Vargas</t>
+          <t>ACUMULADORES CAMPOS</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Vía Morelos 425, Cuauhtemoc Xalostoc, 55310 Ecatepec de Morelos, Méx., México</t>
+          <t>C. Refugio Vilchis 26, Granjas Valle de Guadalupe, 55270 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>19.5309639</v>
+        <v>19.5061732</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>-99.07474740000001</v>
+        <v>-99.07166770000001</v>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
@@ -10271,65 +10271,61 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Baterias Nuevas y Seminuevas (Via Morelos No425)</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>LTH, America Racing, Optima, Gonher</t>
-        </is>
-      </c>
+          <t>...MULADORES CAMPOS (parcialmente legible, consistente con 'Acumuladores Campos')</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n"/>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>Las fotos de la propia ficha de Maps muestran anaqueles con baterias fisicas reales de las marcas LTH, America Racing y Optima (bateria amarilla), ademas de cajas de baterias de motocicleta LTH y America, y un letrero 'Baterias Nuevas y Seminuevas desde $499'.</t>
+          <t>No hay foto de producto; unica foto adicional ('Interior') es una camioneta de noche en cochera, sin baterias visibles</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>Street View en el PIN exacto mostraba un negocio de tortillas/muebles distinto (sin relacion), por lo que se investigo el link de Maps: las fotos propias de la ficha muestran un aparador con placa 'VIA MORELOS No 425' (coincide exactamente con la direccion registrada) y anaqueles repletos de baterias reales LTH/America/Optima, ademas de un banner de 'Baterias Nuevas y Seminuevas'. Aunque el rotulo no dice literalmente 'Vargas', la direccion exacta y la evidencia fotografica del giro son concluyentes.</t>
+          <t>LIMITACION: sin foto de producto; veredicto sostenido en resenas + nombre parcial en fachada. Cerrado temporalmente. Street View muestra el nombre 'CAMPOS' parcial en columnas. Ficha 'Acumuladores Campos' (4.5/10, misma direccion) tiene resenas explicitas: 'Grandes descuentos y oportunidades arreglan todas las baterias', 'Buenos precios'.</t>
         </is>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>fotos/149_baterias_vargas/maps_foto_1.jpg; fotos/149_baterias_vargas/maps_foto_2.jpg</t>
+          <t>fotos/139_acumuladores_campos/streetview_1.jpg; fotos/139_acumuladores_campos/streetview_2.jpg</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>maps_foto_2.jpg</t>
+          <t>streetview_2.jpg</t>
         </is>
       </c>
       <c r="O140" s="3" t="n"/>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES DE LA GARZA</t>
+          <t>ACUMULADORES FIGUEROA GUADALUPE VICTORIA</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Real del Monte 2, Guadalupe Insurgentes, Gustavo A. Madero, 07870 Ciudad de México, CDMX, México</t>
+          <t>Av. José López Portillo 172-Local 3, Guadalupe Victoria, 55010 Ecatepec de Morelos, Méx., México</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>19.4701634</v>
+        <v>19.6203667</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>-99.1320714</v>
+        <v>-99.06957540000001</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
@@ -10343,7 +10339,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>ACUMULADORES DE LA GARZA</t>
+          <t>Centro de Servicio LTH (rebrandeado de 'Acumuladores Figueroa Guadalupe Victoria')</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -10358,33 +10354,9021 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>No se distinguen baterias de auto apiladas con claridad en el aparador (se ven articulos pequenos como accesorios/electronica); si es visible un letrero de precios 'COMPRO CASCOS - MINI $100, CHICA $120...' (compra de cascos/nucleos de bateria usada) y el logo LTH en el toldo.</t>
+          <t>maps_foto_1: fachada 'Centro de Servicio LTH - Diagnostico, venta e instalacion' y 'ecosteps - Centro Autorizado para recepcion de acumuladores usados'</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>El nombre 'ACUMULADORES DE LA GARZA' coincide exactamente con el rotulo verde de la fachada en el PIN exacto, junto con el logo de la marca LTH en el toldo blanco y un letrero de 'COMPRO CASCOS' con tarifas por tamano de bateria (Mini/Chica/Mediana), practica caracteristica de una tienda de baterias.</t>
+          <t>Street View muestra bodega de materiales de construccion (mismatch). La ficha, aunque renombrada, coincide en direccion exacta y su sitio web es acumuladoresfigueroa.com, confirmando la misma entidad. Calificacion 5.0/16 opiniones muy recientes y positivas sobre servicio de baterias.</t>
         </is>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>fotos/150_acumuladores_de_la_garza/streetview_1.jpg; fotos/150_acumuladores_de_la_garza/streetview_2.jpg</t>
+          <t>fotos/140_acumuladores_figueroa_guadalupe_victoria/streetview_1.jpg; fotos/140_acumuladores_figueroa_guadalupe_victoria/streetview_2.jpg; fotos/140_acumuladores_figueroa_guadalupe_victoria/maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>streetview_2.jpg</t>
+          <t>maps_foto_1.jpg</t>
         </is>
       </c>
       <c r="O141" s="3" t="n"/>
       <c r="P141" s="2" t="inlineStr">
         <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>DIST. DE ACUMULADORES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Av. Valle de Santiago 162, Valle de Aragon 3ra Secc, 55280 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>19.5015367</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>-99.0502637</v>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES HERNANDEZ (LTH)</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias fisicas: la cortina metalica del local esta cerrada en ambas fotos de Street View, con un puesto de comida instalado enfrente. Solo se ve el letrero de lona 'LTH ACUMULADORES HERNANDEZ' sobre la cortina.</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'ACUMULADORES HERNANDEZ' coincide exactamente con el letrero visible en la fachada en las coordenadas exactas, junto con el logo de la marca LTH. El local esta cerrado (cortina abajo) en el momento de la captura, por lo que no se ven baterias fisicas, pero el rotulo y la marca son evidencia suficiente de que es una tienda de baterias.</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>fotos/141_dist_de_acumuladores_hernandez/streetview_1.jpg; fotos/141_dist_de_acumuladores_hernandez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O142" s="3" t="n"/>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Av Sta Teresa 25, Granjas Valle de Guadalupe Secc B, 55200 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>19.5281143</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>-99.0513169</v>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>AFN ACUMULADORES FUEGO NUEVO</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America, Full Power, Duralast, Lorenzini, Motorcraft</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>En la foto de Google Maps se ven multiples anaqueles con decenas de baterias de auto y moto reales, ademas de un cartel 'BATERIAS NUEVAS DESDE $999' y logos de varias marcas (LTH, America, Full Power, Duralast, Lorenzini, Motorcraft) en la fachada.</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de Street View en el PIN exacto mostraban un negocio distinto (comercio de electrodomesticos Maytag/Sanyo), asi que se investigo el link de Maps: la foto propia de la ficha 'Acumuladores Fuego Nuevo' muestra el rotulo 'AFN ACUMULADORES FUEGO NUEVO' y anaqueles repletos de baterias reales, confirmando el giro y el nombre exacto del negocio (el pin de Street View esta mal ubicado, pero la foto de la propia ficha de Maps prueba la fachada real).</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>fotos/142_acumuladores_fuego_nuevo/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O143" s="3" t="n"/>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ANDREA</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Av. Gobernador Lic. Ignacio Pichardo Pagaza Mz4 Lt2, Cd Amanecer, 55267 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>19.5104665</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>-99.02466080000001</v>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ANDREA</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>La foto de Google Maps muestra baterias reales de las marcas LTH y America apiladas en anaqueles detras de una reja de seguridad, con un cartel de '48 meses de garantia'.</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto mostraba una panaderia ('Panaderia Chuco Vainilla'), un negocio distinto, por lo que se investigo el link de Maps: la foto de la propia ficha 'Acumuladores Andrea' muestra el rotulo azul 'ACUMULADORES ANDREA' sobre una cortina con baterias LTH y America visibles detras de la reja, confirmando nombre y giro exactos (el pin de Street View esta mal ubicado o corresponde a una toma vieja de un local vecino).</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>fotos/143_acumuladores_andrea/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O144" s="3" t="n"/>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>LTH MCUMULADORES SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Av. Nacional 18, Sta Maria Chiconautla, 55066 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>19.6336485</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>-99.002315</v>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>LTH ACUMULADORES SANCHEZ</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas en anaquel; se ve un mural pintado en la fachada con el logo LTH y una bateria dibujada (grafico, no producto real), junto con el texto 'ACUMULADORES SANCHEZ'.</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'SANCHEZ' y el logo de marca LTH aparecen pintados directamente en la fachada de la esquina exacta del PIN, con el texto 'ACUMULADORES' tambien visible, coincidiendo con el registro 'LTH MCUMULADORES SANCHEZ'.</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>fotos/144_lth_mcumuladores_sanchez/streetview_1.jpg; fotos/144_lth_mcumuladores_sanchez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O145" s="3" t="n"/>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>C. Cerro de la Estrella 100, Sagitario 3, 55238 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>19.4958195</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>-99.0205964</v>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>LTH - ACUMULADORES BATERIAS (Carga de Bateria Rapida y Lenta)</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>Se ven murales pintados de baterias LTH en la fachada (graficos, no fotos de producto real); dentro del local hay anaqueles con cajas y mercancia diversa, pero no se distinguen baterias fisicas con claridad.</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>La fachada en el PIN exacto tiene pintado el texto 'CARGA DE BATERIA ACUMULADORES BATERIAS RAPIDA Y LENTA' junto con el logo LTH repetido varias veces, coincidiendo con el nombre registrado 'LTH'.</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>fotos/145_lth/streetview_1.jpg; fotos/145_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O146" s="3" t="n"/>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores los Gemelos las américas</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Bosque de Ombues 3, Fraccionamiento Las Americas, Las Américas, 55076 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>19.5890478</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>-98.9997336</v>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS - Compra y Venta de Baterias Automotriz e Industrial</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n"/>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias fisicas apiladas; el anuncio del toldo tiene iconos graficos de baterias (clip art), no fotos de producto real ni marcas especificas legibles.</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>El nombre exacto 'Los Gemelos' no es legible en la fachada, pero el giro coincide plenamente: el letrero dice 'BATERIAS - COMPRA Y VENTA DE BATERIAS AUTOMOTRIZ E INDUSTRIAL' en el domicilio exacto del PIN, lo cual confirma que es una tienda de baterias en ese sitio (se prioriza la evidencia visual del giro sobre el nombre exacto, segun la regla del proyecto).</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>fotos/146_acumuladores_los_gemelos_las_americas/streetview_1.jpg; fotos/146_acumuladores_los_gemelos_las_americas/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O147" s="3" t="n"/>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Baterías de gel bolaños</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Gobernador Rafael M. Hidalgo 69-Local 6, Granjas Valle de Guadalupe, 55270 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>19.5062261</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>-99.0566271</v>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="n"/>
+      <c r="I148" s="2" t="n"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>No se aprecian baterias en ninguna foto disponible (ni Street View ni la ficha de Maps, que solo repite la misma foto de la cortina cerrada sin rotulo visible).</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ni Street View ni la galeria de Maps muestran rotulo o producto visible (cortina azul cerrada sin ningun letrero, junto a un taller de 'Clutch y Frenos'). Sin embargo, una resena de un cliente en la ficha de Maps confirma la venta de baterias en este domicilio exacto: 'No tiene nada de baterias nuevas, tiene puras baterias usadas que no sirven... El senor nunca esta... y sobre la compra no hay garantia CUIDADO'. La ficha tambien esta categorizada por Google como 'Tienda de baterias para automovil' y ofrece 'Entrega a domicilio', consistente con un negocio sin aparador visible.</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>fotos/147_baterias_de_gel_bolanos/streetview_1.jpg; fotos/147_baterias_de_gel_bolanos/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O148" s="3" t="n"/>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SafeLithium - Venta, Calculo, Diseño, Armado y reparacion de baterias de Litio</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>C. 309-A 67, El Coyol, Gustavo A. Madero, 07420 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>19.4871735</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>-99.0910883</v>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="n"/>
+      <c r="I149" s="2" t="n"/>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos propias de la ficha de Maps muestran celdas de litio reales: un banco de celdas prismaticas tipo LiFePO4 (etiquetadas '442B') conectadas con barras de cobre y cableado, y otra foto de un paquete de celdas cilindricas 18650 ensambladas -- es decir, baterias de litio fisicas en proceso de armado.</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View en el PIN exacto solo muestra una casa habitacion azul sin ningun letrero comercial visible (el negocio opera aparentemente desde un taller/domicilio sin aparador publico). No obstante, la propia ficha de Maps de 'SafeLithium' tiene fotos subidas por el negocio mostrando celdas de litio reales siendo armadas en paquetes de baterias, lo cual confirma que si fabrican/venden baterias de litio tal como indica su nombre y giro.</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/streetview_2.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_1.jpg; fotos/148_safelithium_venta_calculo_diseno_armado_y_reparacion_de_baterias_de_litio/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O149" s="3" t="n"/>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Vargas</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Vía Morelos 425, Cuauhtemoc Xalostoc, 55310 Ecatepec de Morelos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>19.5309639</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>-99.07474740000001</v>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Baterias Nuevas y Seminuevas (Via Morelos No425)</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America Racing, Optima, Gonher</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de la propia ficha de Maps muestran anaqueles con baterias fisicas reales de las marcas LTH, America Racing y Optima (bateria amarilla), ademas de cajas de baterias de motocicleta LTH y America, y un letrero 'Baterias Nuevas y Seminuevas desde $499'.</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto mostraba un negocio de tortillas/muebles distinto (sin relacion), por lo que se investigo el link de Maps: las fotos propias de la ficha muestran un aparador con placa 'VIA MORELOS No 425' (coincide exactamente con la direccion registrada) y anaqueles repletos de baterias reales LTH/America/Optima, ademas de un banner de 'Baterias Nuevas y Seminuevas'. Aunque el rotulo no dice literalmente 'Vargas', la direccion exacta y la evidencia fotografica del giro son concluyentes.</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>fotos/149_baterias_vargas/maps_foto_1.jpg; fotos/149_baterias_vargas/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O150" s="3" t="n"/>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES DE LA GARZA</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Real del Monte 2, Guadalupe Insurgentes, Gustavo A. Madero, 07870 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>19.4701634</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>-99.1320714</v>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES DE LA GARZA</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>No se distinguen baterias de auto apiladas con claridad en el aparador (se ven articulos pequenos como accesorios/electronica); si es visible un letrero de precios 'COMPRO CASCOS - MINI $100, CHICA $120...' (compra de cascos/nucleos de bateria usada) y el logo LTH en el toldo.</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'ACUMULADORES DE LA GARZA' coincide exactamente con el rotulo verde de la fachada en el PIN exacto, junto con el logo de la marca LTH en el toldo blanco y un letrero de 'COMPRO CASCOS' con tarifas por tamano de bateria (Mini/Chica/Mediana), practica caracteristica de una tienda de baterias.</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>fotos/150_acumuladores_de_la_garza/streetview_1.jpg; fotos/150_acumuladores_de_la_garza/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O151" s="3" t="n"/>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MORALES</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Av. Euzkaro 174-C, Industrial, Gustavo A. Madero, 07800 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>19.4803226</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>-99.1260745</v>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="n"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg (foto oficial de la ficha de Maps) muestra un mural pintado del logo LTH y el letrero 'HOSPITAL DE BATERIAS'; no se ven baterias fisicas apiladas en mostrador en ninguna foto disponible.</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el Street View en el pin exacto muestra un negocio distinto ('Persianas en Decoracion'), y el nombre 'Morales' no es legible en ninguna foto disponible. Se verifico directamente en el navegador la ficha de Google Maps de este Place ID exacto: nombre 'Acumuladores Morales', categoria oficial 'Tienda de baterias para automovil', 4.9 estrellas (287 reseñas) y direccion Av. Euzkaro 174 (coincide); su foto oficial (=maps_foto_1.jpg) muestra mural LTH y rotulo 'HOSPITAL DE BATERIAS'. Se concluye SI con base en la ficha oficial (nombre+categoria+direccion+foto propia), no en el Street View.</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>fotos/151_acumuladores_morales/streetview_1.jpg; fotos/151_acumuladores_morales/streetview_2.jpg; fotos/151_acumuladores_morales/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O152" s="3" t="n"/>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES PALACIOS</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Pte. 112 371-A, Tlacamaca, Gustavo A. Madero, 07380 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>19.4764525</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>-99.138935</v>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Palacios</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg muestra, dentro del local, un anaquel con cajas apiladas y un exhibidor de pie con rotulo LTH; los productos no se distinguen con detalle suficiente para identificar el empaque exacto.</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo 'ACUMULADORES PALACIOS' con 3 logos LTH en el toldo coincide exactamente con el nombre registrado en el pin exacto. Se ve anaquel de producto y un exhibidor de pie con marca LTH junto a la entrada.</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>fotos/152_acumuladores_palacios/streetview_1.jpg; fotos/152_acumuladores_palacios/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O153" s="3" t="n"/>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES QUINTOS</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Ángel Albino Corzo 3305, Belisario Domínguez, Gustavo A. Madero, 07869 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>19.4628706</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>-99.10997</v>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Quintos</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas ni mostrador; la entrada aparece con cortinas metalicas semicerradas. La evidencia es la rotulacion masiva del edificio (BATERIAS NUEVAS / BATERIAS SEMINUEVAS, LTH).</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'ACUMULADORES QUINTOS' esta pintado en letras enormes junto con 'BATERIAS NUEVAS' / 'BATERIAS SEMINUEVAS' y el logo LTH, exactamente en el pin dado -- coincidencia clara de nombre y giro.</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>fotos/153_acumuladores_quintos/streetview_1.jpg; fotos/153_acumuladores_quintos/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O154" s="3" t="n"/>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Multimarcas Muñoz J</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Nte. 48-A 5140, La Joyita, Gustavo A. Madero, 07860 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>19.4654028</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>-99.11722589999999</v>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Multimarcas</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>El banner amarillo muestra 5 ilustraciones de baterias (nuevas y de medio uso) con los textos 'BATERIAS MULTIMARCAS', 'NUEVAS Y 1/2 USO' y 'PAGUE FIRMANDO'; junto a la entrada hay un mural pintado del logo LTH.</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>El banner 'BATERIAS MULTIMARCAS NUEVAS Y 1/2 USO' coincide con la palabra 'Multimarcas' del nombre registrado (Acumuladores Multimarcas Muñoz J); no se lee 'Muñoz J' en la fachada, pero el giro coincide plenamente y hay un mural LTH pintado junto a la entrada. Se prioriza la evidencia visual del giro sobre el nombre completo.</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>fotos/154_acumuladores_multimarcas_munoz_j/streetview_1.jpg; fotos/154_acumuladores_multimarcas_munoz_j/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O155" s="3" t="n"/>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Av. Victoria Ote. 3709, Faja de Oro, Gustavo A. Madero, 07850 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>19.4675266</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>-99.10592819999999</v>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>El mural muestra una bateria ilustrada con marca LTH y el texto 'VICTORIA'; las cortinas metalicas estan cerradas por lo que no se ve producto fisico.</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'VICTORIA' esta pintado en letras grandes junto con 'ACUMULADORES REFACCIONES ACEITES' y dos logos LTH en las cortinas, exactamente en el pin -- coincidencia exacta de nombre y giro.</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>fotos/155_victoria/streetview_1.jpg; fotos/155_victoria/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O156" s="3" t="n"/>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores La Güera</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Eje Central Lázaro Cárdenas 3027, Guadalupe Proletaria, Gustavo A. Madero, 07670 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>19.5210101</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>-99.15712619999999</v>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores La Güera</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>Se ve un anaquel con cajas oscuras apiladas dentro del local (forma compatible con baterias, sin marca legible), ademas de un letrero circular de marca en la pared.</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo 'ACUMULADORES LA GUERA' y 'LTH LA GUERA' coincide exactamente con el nombre registrado en el pin exacto. A traves de la puerta abierta se aprecia un anaquel con cajas de producto apiladas.</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>fotos/156_acumuladores_la_guera/streetview_1.jpg; fotos/156_acumuladores_la_guera/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O157" s="3" t="n"/>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Baterias LTH Talismán</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Av. Talismán 275, Aragón Inguarán, Gustavo A. Madero, 07820 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>19.4729351</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>-99.10703789999999</v>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Baterías LTH Talismán</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg y maps_foto_3.jpg muestran anaqueles interiores con multiples baterias LTH en caja (empaque con logo LTH), mas un exhibidor giratorio de accesorios LTH junto a la entrada.</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto no muestra rotulacion (solo fachada azul sin anuncios visibles). Las fotos propias de la ficha de Maps muestran el letrero 'Baterias LTH Talisman' con el numero '275', que coincide exactamente con la direccion registrada (Av. Talisman 275), mas fotos de interior con anaqueles llenos de baterias LTH para la venta -- confirmacion solida de ubicacion y giro.</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>fotos/157_baterias_lth_talisman/streetview_1.jpg; fotos/157_baterias_lth_talisman/streetview_2.jpg; fotos/157_baterias_lth_talisman/maps_foto_1.jpg; fotos/157_baterias_lth_talisman/maps_foto_2.jpg; fotos/157_baterias_lth_talisman/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O158" s="3" t="n"/>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>LTH ACUMULADORES STAR</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Calz. Vallejo 1772, Santa Rosa, Gustavo A. Madero, 07620 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>19.523928</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>-99.16686079999999</v>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Star</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>No se ve mostrador ni baterias fisicas apiladas; la puerta esta cubierta por un poster de motociclismo. La evidencia es el mural exterior con logo LTH y el rotulo de instalacion de baterias.</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo 'LTH ACUMULADORES STAR' con el numero '1772' (coincide exactamente con Calz. Vallejo 1772) y un mural LTH estan pintados directamente en la fachada, en el pin exacto, junto con el texto 'INSTALACION DE BATERIAS'.</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>fotos/158_lth_acumuladores_star/streetview_1.jpg; fotos/158_lth_acumuladores_star/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O159" s="3" t="n"/>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MORENO</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Ángel Albino Corzo 3215, Belisario Domínguez, Gustavo A. Madero, 07869 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>19.4634595</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>-99.11157710000001</v>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Moreno</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n"/>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo amarillo lista tipos de bateria a la venta (mini/chica/mediana/tornillo/camion); a traves de la cortina abierta se alcanzan a ver anaqueles con cajas de producto, pero la imagen esta demasiado oscura para identificar marca o confirmar con certeza que son baterias.</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'ACUMULADORES MORENO' y la calle 'Angel Albino Corzo' coinciden exactamente con el nombre y direccion registrados, en el pin exacto. El rotulo detalla explicitamente 'COMPRA Y VENTA DE BATERIAS' con tipos especificos (mini, chica, mediana, tornillo, camion).</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>fotos/159_acumuladores_moreno/streetview_1.jpg; fotos/159_acumuladores_moreno/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O160" s="3" t="n"/>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS, ACEITES Y FILTROS BM</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Av. Puerto Mazatlan LT9, Jorge Negrete, Gustavo A. Madero, 07280 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>19.5253798</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>-99.1405874</v>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Battery Makers</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>El mural exterior muestra 3 baterias ilustradas (la izquierda con marca LTH); en el interior se ve un anaquel con cajas de producto junto a un letrero LTH, sin poder confirmar la marca exacta de cada caja por la resolucion de la imagen.</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>La fachada en el pin exacto es un taller especializado ('ESPECIALISTAS EN BATERIAS Y MOTOBATERIAS', 'VENTA, DIAGNOSTICO E INSTALACION') con mural de baterias de marca LTH, y un anaquel de producto visible en el interior junto a un letrero LTH. El nombre completo registrado 'BM' no esta escrito literalmente, pero el logo 'Battery Makers' (con mascota) probablemente es su origen, y el giro coincide plenamente con la direccion exacta.</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>fotos/160_baterias_aceites_y_filtros_bm/streetview_1.jpg; fotos/160_baterias_aceites_y_filtros_bm/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O161" s="3" t="n"/>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ISLAS</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Escuadron 201 #125, La Purísima Ticoman, Gustavo A. Madero, 07320 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>19.5160744</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>-99.1358281</v>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ISLAS</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>Foto de Maps muestra mural/fachada esquina con ilustraciones pintadas de baterias LTH (no baterias fisicas); confirma nombre completo y giro 'Carga de Baterias'/'Compra Venta de Baterias'.</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>Fachada esquinera con mural 'ACUMULADORES ISLAS', logo LTH, banner 'Full Power', textos 'COMPRA VENTA DE BATERIAS' y 'CARGA DE BATERIAS'. Cortina metalica cerrada al momento de la toma, pero identidad del negocio es inequivoca.</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>fotos/161_acumuladores_islas/streetview_1.jpg; fotos/161_acumuladores_islas/streetview_2.jpg; fotos/161_acumuladores_islas/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O162" s="3" t="n"/>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS YEIKO</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Cam. San Juan de Aragón 51, Casas Alemán, Gustavo A. Madero, 07580 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>19.4743333</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>-99.0856048</v>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="n"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>Duracell</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>Vitrina/anaquel con baterias Duracell fisicas apiladas (al menos 5-6 piezas), banner 'DURACELL Centro de Servicio, Quejas y Sugerencias 01800 ARRANCA'.</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>Street View del PIN exacto muestra un taller de 'Transmisiones Automaticas', sin relacion aparente. Se investigo la ficha de Maps de 'Baterias Yeiko' (confirmada por get_page_text: mismo nombre y direccion exacta); la foto propia subida a esa ficha muestra fachada con columnas rojas, banner Duracell y baterias fisicas reales en vitrina.</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>fotos/162_baterias_yeiko/streetview_1.jpg; fotos/162_baterias_yeiko/streetview_2.jpg; fotos/162_baterias_yeiko/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O163" s="3" t="n"/>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ACUMULADORES LEMUS</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>FC Hidalgo 2129, Vasco de Quiroga, Col del Obrero, Gustavo A. Madero, 07430 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>19.5010566</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>-99.0935795</v>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel metalico con al menos 6 baterias fisicas (LTH y America Racing AGM) y filtros; letrero 'SE COMPRAN ACUMULADORES USADOS/ROTOS' con tabla de precios por tamano.</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>Street View del PIN exacto muestra 'Servicio Electrico Reyes' en el mismo edificio. Se confirmo la ficha de Maps 'Servicio de Acumuladores Lemus' (mismo nombre, direccion, categoria 'Tienda de baterias para automovil', 4.6 estrellas/5 opiniones). Las fotos propias muestran logo LTH y anaquel con baterias fisicas reales. Resenas mencionan explicitamente precio de bateria.</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>fotos/163_servicio_de_acumuladores_lemus/streetview_1.jpg; fotos/163_servicio_de_acumuladores_lemus/streetview_2.jpg; fotos/163_servicio_de_acumuladores_lemus/maps_foto_1.jpg; fotos/163_servicio_de_acumuladores_lemus/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O164" s="3" t="n"/>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Reaccionaría ICHI</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Nte. 24-A 46, Industrial, Gustavo A. Madero, 07800 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>19.47132</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>-99.1305478</v>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="n"/>
+      <c r="I165" s="2" t="n"/>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>N/A - la ficha de Maps solo tiene la categoria 'Street View y 360', sin fotos del propietario ni resenas.</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto muestra un local con cortina metalica cerrada y letrero 'BEER &amp; MORE TO GO' (tienda de conveniencia/cervezas), sin ninguna relacion visual con baterias ni con el nombre 'ICHI'. La categoria 'Tienda de baterias' esta autoasignada en Maps sin evidencia que la respalde (negocio sin resenas, sin fotos propias).</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>fotos/164_reaccionaria_ichi/streetview_1.jpg; fotos/164_reaccionaria_ichi/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O165" s="3" t="n"/>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FLORES</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Pto. Ensenada 1, Casas Alemán, Gustavo A. Madero, 07580 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>19.4747443</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>-99.08637539999999</v>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FLORES</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>N/A - no fue necesario descargar fotos adicionales de Maps, el Street View exacto ya es concluyente.</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>Street View del PIN exacto muestra fachada completa pintada 'ACUMULADORES FLORES' (banner y muro), con anaquel de baterias fisicas reales (LTH, Full Power) y una persona trabajando en el mostrador.</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>fotos/165_acumuladores_flores/streetview_1.jpg; fotos/165_acumuladores_flores/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O166" s="3" t="n"/>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>LOS EXPERTOS EN BATERIAS</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Av Villa de Ayala 185, entre Estado de Zacatecas y Estado de Nayarit, Providencia, Gustavo A. Madero, 07550 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>19.4885</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>-99.068702</v>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="n"/>
+      <c r="I167" s="2" t="n"/>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>N/A - ficha de Maps sin fotos del propietario, solo Street View; negocio no reclamado, sin resenas.</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto muestra una comercializadora de electrodomesticos (Mabe, GE, Daewoo) y una polleria en la esquina, sin ningun rastro de baterias ni del nombre 'Los Expertos en Baterias'. Se confirmo en la ficha de Maps que el negocio no tiene resenas, no tiene fotos propias y no esta reclamado por su dueno.</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>fotos/166_los_expertos_en_baterias/streetview_1.jpg; fotos/166_los_expertos_en_baterias/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O167" s="3" t="n"/>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES JOLUMO</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Calle Nte 92 5632, Gertrudis Sánchez III Secc, Gustavo A. Madero, 07838 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>19.4627215</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>-99.0986056</v>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES JOLUMO</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>N/A - no fue necesario descargar fotos adicionales de Maps.</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>Street View del PIN exacto muestra fachada completa con letrero grande 'LTH ACUMULADORES JOLUMO' y banner 'Full Power' en el balcon superior. Nombre coincide exactamente con el registrado.</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>fotos/167_acumuladores_jolumo/streetview_1.jpg; fotos/167_acumuladores_jolumo/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O168" s="3" t="n"/>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MORENO</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Av. Francisco Morazán 764, Asentamiento las Malvinas, Gustavo A. Madero, 07509 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>19.4690441</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>-99.063878</v>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MORENO</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n"/>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>Fachada amarilla en esquina con letrero grande 'ACUMULADORES MORENO' y cartel con precios de compra de acumuladores usados por tamano.</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>Street View del PIN exacto muestra un salon de belleza, sin relacion con baterias. Se confirmo la ficha de Maps 'ACUMULADORES MORENO' (mismo nombre exacto, 3.6 estrellas, 22 opiniones); la foto propia muestra la fachada amarilla completa con tabla de precios de compra. Resenas confirman venta de baterias.</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>fotos/168_acumuladores_moreno/streetview_1.jpg; fotos/168_acumuladores_moreno/streetview_2.jpg; fotos/168_acumuladores_moreno/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O169" s="3" t="n"/>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GUTIERREZ CUAUTEPEC</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Av. Guadalupe Victoria 43, Cuautepec de Madero, Gustavo A. Madero, 07200 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>19.5481395</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>-99.13543919999999</v>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>N/A - no fue necesario descargar fotos adicionales de Maps.</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>Street View del PIN exacto muestra letrero blanco con logo LTH y texto '...MULADORES...GUTIERRE[Z]', anaquel con producto visible en la entrada, y letrero adicional 'VENTA DE...BATER[IAS]' en la fachada contigua.</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>fotos/169_acumuladores_gutierrez_cuautepec/streetview_1.jpg; fotos/169_acumuladores_gutierrez_cuautepec/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O170" s="3" t="n"/>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Suministros Tecnológicos On Demand SA de CV</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Calz. Azcapotzalco - La Villa 1140-Int. 205, San Bartolo Atepehuacan, Gustavo A. Madero, 07730 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>19.4910543</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>-99.14115409999999</v>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="n"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Power-Sonic</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>Fotos propias de la ficha de Maps muestran una oficina/bodega con cajas apiladas de baterias industriales de respaldo marca Power-Sonic (serie gel, tipo UPS/telecom), NO baterias de arranque automotriz.</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>Ficha de Maps confirmada ('Suministros Tecnologicos On Demand SA de CV', categoria generica 'Tienda de baterias', 4.4 estrellas, 30 opiniones). Resenas mencionan explicitamente 'baterias de respaldo' y 'equipos completos' (UPS). Conclusion: si vende baterias, pero de respaldo/industriales para equipos, no baterias para automovil -- no corresponde al giro buscado en este estudio.</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>fotos/170_suministros_tecnologicos_on_demand_sa_de_cv/streetview_1.jpg; fotos/170_suministros_tecnologicos_on_demand_sa_de_cv/streetview_2.jpg; fotos/170_suministros_tecnologicos_on_demand_sa_de_cv/maps_foto_1.jpg; fotos/170_suministros_tecnologicos_on_demand_sa_de_cv/maps_foto_2.jpg; fotos/170_suministros_tecnologicos_on_demand_sa_de_cv/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O171" s="3" t="n"/>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>??BODEGA ??ACUMULADORES TAURO??</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Av. Francisco Morazán 768, Asentamiento las Malvinas, Gustavo A. Madero, 07509 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>19.4680573</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>-99.06260570000001</v>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="n"/>
+      <c r="I172" s="2" t="n"/>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ninguna bateria; la cortina metalica (con el numero 766) esta cerrada por completo y cubre todo el frente del local en ambas fotos.</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: la cortina metalica del inmueble esta cerrada en el zoom y en la foto de contexto; no hay rotulo, logo ni bateria visible. No se pudo complementar con Maps: el navegador fallo repetidamente, devolviendo en cada intento una ficha de negocio distinta y no relacionada.</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>fotos/171_bodega_acumuladores_tauro/streetview_1.jpg; fotos/171_bodega_acumuladores_tauro/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O172" s="3" t="n"/>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES ASTRO BOY</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Cam. a Las Canteras 5, Malacates, Gustavo A. Madero, 07119 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>19.5722921</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>-99.13207989999999</v>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>Se ve el cartel 'LTH VENTA DE BATERIAS NUEVAS Y USADAS - 48 MESES DE GARANTIA' con una bateria LTH ilustrada, y un anaquel con producto dentro del local a traves de la puerta.</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>La fachada dice 'ACUMULADORES' junto al logo America LTH, con un cartel adicional 'LTH VENTA DE BATERIAS NUEVAS Y USADAS'. El resto del nombre (posiblemente 'Astro Boy') queda tapado por el cofre de un auto, pero el giro y la marca coinciden claramente con lo registrado.</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>fotos/172_acumuladores_astro_boy/streetview_1.jpg; fotos/172_acumuladores_astro_boy/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O173" s="3" t="n"/>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Baterías “VICTORIA” a DOMICILIO</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Av 613 169, San Juan de Aragón IV Secc, Gustavo A. Madero, 07979 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>19.454439</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>-99.0678264</v>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>LTH BATERIAS VI...</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>Se ve una bateria LTH pintada en el muro junto al rotulo 'BATERIAS VI...'; detras de la reja de seguridad se distingue el interior del local.</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo de la fachada dice 'LTH BATERIAS VI...' (cortado por el encuadre, consistente con 'Baterias Victoria'), junto a una bateria LTH pintada y un local con reja de seguridad. Nombre y giro coinciden con lo registrado.</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>fotos/173_baterias_victoria_a_domicilio/streetview_1.jpg; fotos/173_baterias_victoria_a_domicilio/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O174" s="3" t="n"/>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>LADY BATTERY</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Ángel Albino Corzo 3914, Mártires de Río Blanco, Gustavo A. Madero, 07859 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>19.4617135</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>-99.1055959</v>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES FIGUEROA</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>LTH (de un negocio distinto: Acumuladores Figueroa)</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>Se ve una bateria fisica LTH (AGM) colgada como anuncio y rotulacion LTH, pero pertenecen a la fachada de 'Acumuladores Figueroa', negocio distinto al registrado en este CASE ID.</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>En las coordenadas exactas del pin, ambas fotos muestran los rotulos 'LTH' y 'ACUMULADORES FIGUEROA' -- el nombre 'LADY BATTERY' no aparece en ninguna toma. Por la regla del PIN exacto, no se acredita a esta ficha la evidencia de un negocio distinto, aunque tambien venda baterias.</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>fotos/174_lady_battery/streetview_1.jpg; fotos/174_lady_battery/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O175" s="3" t="n"/>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>EL GUERO</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Av 613 213, San Juan de Aragón III Secc, Gustavo A. Madero, 07970 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>19.4549455</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>-99.06845970000001</v>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Manejo Bosques</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ninguna bateria en ninguna de las dos fotos.</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>Las coordenadas exactas muestran 'Escuela de Manejo Bosques' (curso de manejo) y una taqueria contigua con servicio a domicilio; no hay rotulo, logo ni producto de baterias, ni aparece el nombre 'El Guero'.</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>fotos/175_el_guero/streetview_1.jpg; fotos/175_el_guero/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O176" s="3" t="n"/>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Sistemas Inteligentes e Instrumentación Electrónica</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cruz Azul 161, Industrial, Gustavo A. Madero, 07800 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>19.4732811</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>-99.1238901</v>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="n"/>
+      <c r="I177" s="2" t="n"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ninguna bateria ni producto; la cochera esta cerrada con autos particulares estacionados dentro.</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: la fachada en las coordenadas exactas es una casa habitacion de dos pisos con cochera cerrada, sin ningun rotulo comercial, logo ni producto visible. No se pudo complementar con Maps por fallas repetidas del navegador.</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>fotos/176_sistemas_inteligentes_e_instrumentacion_electronica/streetview_1.jpg; fotos/176_sistemas_inteligentes_e_instrumentacion_electronica/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O177" s="3" t="n"/>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Av. F.C. Mexicano 1, FFCC Concepción Zepeda Viuda de Gómez Z., 54140 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>19.53641</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>-99.16897090000001</v>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="n"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas claramente identificables en el anaquel; solo bolsas/maletas colgadas con logo LTH y cajas de producto Bardahl.</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el rotulo del local dice 'CARGA DE BATERIAS' (servicio de recarga) y se ven bolsas con logo LTH junto a producto Bardahl en el anaquel, pero no hay rotulo de venta ni baterias fisicas claramente identificables. No se pudo confirmar con resenas de Maps por fallas repetidas del navegador.</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>fotos/177_lth/streetview_1.jpg; fotos/177_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O178" s="3" t="n"/>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH LAS ARBOLEDAS</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Calz. de los Jinetes 26, Las Arboledas, 54026 Cdad. López Mateos, Méx., México</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>19.5555723</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>-99.2130849</v>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="n"/>
+      <c r="I179" s="2" t="n"/>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ninguna bateria; el local muestra tenis, gorras y bolsos (negocio de limpieza de calzado).</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>Las coordenadas exactas muestran un local de 'Limpieza de tenis, tocas, gorras y bolsos' con un mural pintado; no hay rotulo LTH, logo ni producto de baterias, ni coincide con 'Centro de Servicio LTH Las Arboledas'.</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>fotos/178_centro_de_servicio_lth_las_arboledas/streetview_1.jpg; fotos/178_centro_de_servicio_lth_las_arboledas/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O179" s="3" t="n"/>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Central de Acumuladores LTH Sucursal Satélite</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Av. Vía Adolfo López Mateos 74, Hab Magisterial Vista Bella, 54050 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>19.5226847</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>-99.2379344</v>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio LTH</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>No se distinguen baterias individuales con precision, pero se ve un exhibidor/anaquel de producto dentro del local junto con telefonos de contacto, bajo el rotulo 'venta e instalacion'.</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>La fachada esta rotulada 'Centro de Servicio LTH - Diagnostico, venta e instalacion', con telefonos y, a traves de la entrada, un exhibidor visible. Nombre, marca y giro coinciden con 'Central de Acumuladores LTH Sucursal Satelite'.</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>fotos/179_central_de_acumuladores_lth_sucursal_satelite/streetview_1.jpg; fotos/179_central_de_acumuladores_lth_sucursal_satelite/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O180" s="3" t="n"/>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS EL OFERTON SUCURSAL TLALPIZAHUAC</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cuauhtémoc 6, San Juan Tlalpizahuac, 56576 Ixtapaluca, Méx., México</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>19.3287036</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>-98.94842149999999</v>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="n"/>
+      <c r="I181" s="2" t="n"/>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ninguna bateria ni producto; la fachada es un muro residencial con grafiti.</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: la fachada en las coordenadas exactas es un muro de una casa con grafiti, sin ningun rotulo de negocio, logo o producto visible; junto hay una gasolinera que no corresponde a este pin. No se pudo complementar con Maps por fallas repetidas del navegador.</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>fotos/180_baterias_el_oferton_sucursal_tlalpizahuac/streetview_1.jpg; fotos/180_baterias_el_oferton_sucursal_tlalpizahuac/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O181" s="3" t="n"/>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>MALBANI ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cuauhtémoc 20B, Santa Barbara, 56538 Ixtapaluca, Méx., México</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>19.3135115</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>-98.89097289999999</v>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES [G]ALVANI (rótulo con LTH); Excel: MALBANI ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Galvani</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>N/A (evidencia en Street View): anaquel de entrada con baterias LTH fisicas apiladas, mas maqueta de bateria LTH colgada como senalizacion</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 y streetview_2 (con zoom) muestran rotulo 'ACUMULADORES [G]ALVANI' con logo LTH y baterias fisicas LTH apiladas en anaquel de entrada. El nombre no coincide exactamente con 'MALBANI' (se lee 'GALVANI'), pero Google Maps confirma la ficha 'Malbani Acumuladores' en la MISMA direccion exacta, categoria oficial 'Tienda de baterias', 2 resenas positivas. Se prioriza evidencia visual+ubicacion sobre la discrepancia de nombre.</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>fotos/181_malbani_acumuladores/streetview_1.jpg; fotos/181_malbani_acumuladores/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O182" s="3" t="n"/>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES AGM</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Av. Cuauhtémoc 13, Santa Cruz Tlapacoya, 56577 Ixtapaluca, Méx., México</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>19.3093327</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>-98.9134246</v>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores AGM (doble rotulo iluminado con LTH)</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Gonher, America Racing, Xtreme</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg muestra anaquel de 7 niveles con ~30 baterias fisicas de auto de marcas LTH, Gonher, America Racing y Xtreme, mas botes de acido para bateria</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg (nocturna) muestra rotulo iluminado 'Acumuladores AGM' x2 con marca LTH y mostrador interior; maps_foto_2.jpg muestra anaquel completo con baterias fisicas de multiples marcas. Nombre y ubicacion coinciden exactamente con el Excel. streetview_1/2 no sirven como evidencia (muestran por error un negocio de impresion/DTF de la misma cuadra), pero las fotos de Maps ya descargadas prueban la venta con claridad.</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>fotos/182_acumuladores_agm/streetview_1.jpg; fotos/182_acumuladores_agm/streetview_2.jpg; fotos/182_acumuladores_agm/maps_foto_1.jpg; fotos/182_acumuladores_agm/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O183" s="3" t="n"/>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO GONHER</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Av. Morelos 30, San Francisco Acuautla, 56587 San Francisco Acuautla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>19.3390316</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>-98.8641688</v>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2" t="n"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>N/A - la ficha de Maps no tiene fotos del propietario, solo Street View</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 y streetview_2 en las coordenadas exactas muestran una tienda de materiales de construccion, sin ningun rotulo o producto de baterias. Sin embargo, Google Maps SI tiene esta ficha registrada como 'Centro de Servicio GONHER', categoria oficial 'Tienda de baterias para automovil', con sitio web gonher.com.mx, en la misma direccion exacta. La ficha tiene 0 resenas y no se pudo revisar galeria adicional (contencion del navegador). Evidencia contradictoria: se recomienda revision manual en sitio.</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>fotos/183_centro_de_servicio_gonher/streetview_1.jpg; fotos/183_centro_de_servicio_gonher/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O184" s="3" t="n"/>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>BATERIASADOMICILIO24HRS.COM.MX</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Morelos 34, Consejo Agrarista Mexicano, Iztapalapa, 09760 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>19.3257207</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>-99.0589019</v>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="n"/>
+      <c r="I185" s="2" t="n"/>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>N/A - no se identificaron fotos de interior/producto en la galeria de Maps</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: streetview_1/2 muestran solo un porton/reja residencial cubierto de arboles, consistente con un negocio de 'baterias a domicilio' sin tienda fisica tradicional. Google Maps confirma la ficha 'bateriasadomicilio24hrs.com.mx', categoria 'Tienda de baterias para automovil', 4.9 estrellas (137 resenas), servicio 24 horas con entrega y compra en tienda, y resenas explicitas que confirman venta e instalacion de baterias/acumuladores a domicilio. No existe foto que pruebe visualmente baterias; el veredicto SI se sostiene en 137 resenas de Maps, no en la foto.</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>fotos/184_bateriasadomicilio24hrs_com_mx/streetview_1.jpg; fotos/184_bateriasadomicilio24hrs_com_mx/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O185" s="3" t="n"/>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>AUTOPARTES CALDERON</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Ermita Iztapalapa 2635, Sta Cruz Meyehualco, Iztapalapa, 09700 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>19.342006</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>-99.05059350000001</v>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>CA CALDERON AUTOPARTES</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Gonher</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>N/A (evidencia en Street View)</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 y streetview_2 muestran el rotulo 'CA CALDERON AUTOPARTES' con un anuncio grande de bateria Gonher ('48 GARANTIA SIN COSTO'). Al hacer zoom en el interior de la tienda se aprecian cajas de bateria fisicas apiladas en anaquel junto a productos Gonher. Nombre y ubicacion coinciden exactamente con el Excel.</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>fotos/185_autopartes_calderon/streetview_1.jpg; fotos/185_autopartes_calderon/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O186" s="3" t="n"/>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>COCO BATTERIES</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Ermita Iztapalapa 2625, La Era I y II, Iztapalapa, 09720 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>19.3420101</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>-99.050974</v>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>COCO Batteries</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>N/A - no se descargaron fotos adicionales de Maps</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1/2 muestran el rotulo grande 'COCO Batteries' con logo LTH pintado en la cortina y anuncio de instalacion con scanner. Nombre coincide exactamente con el Excel. Google Maps confirma la ficha con 15 resenas que consistentemente mencionan compra e instalacion de baterias reales.</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>fotos/186_coco_batteries/streetview_1.jpg; fotos/186_coco_batteries/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O187" s="3" t="n"/>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS "ORTIZ"</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Ermita Iztapalapa 2537, entre calles Lirio y Manto, La Era I y II, Iztapalapa, 09720 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>19.3434639</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>-99.0589722</v>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="n"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el Street View en el pin exacto muestra primero la fachada de la iglesia 'Alcance Victoria', pero inmediatamente al lado, en el mismo predio, hay un local con rotulo 'DISTRIBUIDOR LTH' y una bateria LTH pintada en la pared, con vitrina de productos. Google Maps confirma la ficha 'Baterias ORTIZ' en esta direccion exacta, 4.9 estrellas con 28 resenas que confirman explicitamente la venta de baterias ('solo venden marca America, alta y ACDelco'). La foto no muestra un rotulo con el nombre 'Ortiz'; el veredicto SI se apoya principalmente en las resenas de Maps.</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>fotos/187_baterias_ortiz/streetview_1.jpg; fotos/187_baterias_ortiz/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O188" s="3" t="n"/>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Alex</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Av. Leyes de Reforma 1145, Leyes de Reforma 3ra Secc, Iztapalapa, 09310 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>19.3774601</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>-99.0682571</v>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="n"/>
+      <c r="I189" s="2" t="n"/>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 y streetview_2 en las coordenadas exactas muestran un local de venta de botanas/snacks ('Charly Chicharron') y una tlapaleria vecina, sin ningun rotulo, logo o producto relacionado con baterias. La ficha de Google Maps 'Baterias Alex' esta SIN RECLAMAR, sin telefono, sin sitio web, sin resenas (0) y sin fotos adicionales del propietario. No hay evidencia real que sustente la venta de baterias en este punto.</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>fotos/188_baterias_alex/streetview_1.jpg; fotos/188_baterias_alex/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O189" s="3" t="n"/>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO LTH ERMITA</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Av. Arneses 22, Minerva, Iztapalapa, 09810 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>19.3558817</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>-99.1110479</v>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="n"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: streetview_1/2 muestran una plaza comercial con tienda OXXO y una tienda de refacciones 'ANM', pero el local especifico D-7 (donde esta registrado 'Centro de Servicio LTH Ermita') no se distingue individualmente. Google Maps confirma la ficha en la direccion exacta, 4.2 estrellas con 14 resenas que confirman explicitamente compra e instalacion de baterias. Hay una actualizacion de visitantes de hace un ano: 'Ya no es LTH ahora es GONHER'. El veredicto SI se apoya en las resenas de Maps, no en la foto.</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>fotos/189_centro_de_servicio_lth_ermita/streetview_1.jpg; fotos/189_centro_de_servicio_lth_ermita/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O190" s="3" t="n"/>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Ángel Rodríguez 653</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Olite, Cerro de la Estrella, 09860 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>19.319486</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>-99.07943109999999</v>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LTH 'RODRIGUEZ'</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 y streetview_2 muestran claramente el rotulo 'ACUMULADORES LTH RODRIGUEZ' con el logo oficial LTH y una bateria fisica pintada como senalizacion, mas un mostrador/vitrina interior visible. Evidencia visual clara y directa.</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>fotos/190_miguel_angel_rodriguez_653/streetview_1.jpg; fotos/190_miguel_angel_rodriguez_653/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O191" s="3" t="n"/>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Baterías y acumuladores "JISA"</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Av. San Rafael Atlixco 85, Guadalupe del Moral, Iztapalapa, 09300 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>19.3692308</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>-99.0746457</v>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "JISA"</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg muestra letrero de fachada 'ACUMULADORES JISA', banners de LTH y America Racing, y anaqueles con baterias apiladas al fondo del local.</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto muestra por error un negocio distinto ('Lavalux' lavanderia). La ficha de Maps verificada (mismo nombre y direccion) tiene categoria 'Tienda de baterias para automovil', 4.4 estrellas (11 resenas), y una foto de galeria que muestra la fachada real con el letrero 'ACUMULADORES JISA' y anaqueles de baterias.</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>fotos/191_baterias_y_acumuladores_jisa/streetview_1.jpg; fotos/191_baterias_y_acumuladores_jisa/streetview_2.jpg; fotos/191_baterias_y_acumuladores_jisa/maps_foto_1.jpg; fotos/191_baterias_y_acumuladores_jisa/maps_foto_2.jpg; fotos/191_baterias_y_acumuladores_jisa/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O192" s="3" t="n"/>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Baterías nuevas y usadas "Jimmy”</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Lomita 15, 2da Amp San Miguel, Iztapalapa, 09360 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>19.352248</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>-99.0707874</v>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS "JIMMI"</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>N/A - Street View ya daba evidencia clara y suficiente.</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>Ambas tomas de Street View muestran la cortina del local con texto '...ERIAS JIMMI' y 'NUEVAS Y USADAS', un mural de la marca LTH y letrero grande 'BATERIAS'. Nombre + marca + giro coinciden en el pin exacto.</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>fotos/192_baterias_nuevas_y_usadas_jimmy/streetview_1.jpg; fotos/192_baterias_nuevas_y_usadas_jimmy/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O193" s="3" t="n"/>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Arza</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>San Felipe de Jesús 140, Iztapalapa, 09368 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>19.352076</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>-99.0735794</v>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>"BATERÍAS ARZA"</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Optima, América Racing, Full Power</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg: letrero con el nombre exacto 'BATERIAS ARZA' junto a banners de OPTIMA y LTH. maps_foto_3.jpg: anaquel real con baterias fisicas de LTH, America Racing y Full Power.</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto capturo el negocio vecino 'Soya Natural'. La galeria de fotos de Maps para esta ficha exacta incluye fotos subidas por el propietario que muestran el nombre 'BATERIAS ARZA' junto con anuncios de marcas reales y un anaquel real con baterias de varias marcas a la venta.</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>fotos/193_baterias_arza/streetview_1.jpg; fotos/193_baterias_arza/streetview_2.jpg; fotos/193_baterias_arza/maps_foto_2.jpg; fotos/193_baterias_arza/maps_foto_3.jpg; fotos/193_baterias_arza/maps_foto_4.jpg</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="O194" s="3" t="n"/>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>AUTOELECTRICA H.C. ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Av. Tlahuac 329-Loc b y c, Los Reyes Culhuacan, Iztapalapa, 09840 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>19.3473478</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>-99.1074211</v>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="n"/>
+      <c r="I195" s="2" t="n"/>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>Las fotos de la galeria de Maps son de productos genericos de refacciones -- ninguna muestra baterias fisicas.</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: no se encontro ninguna foto que muestre baterias fisicas o el nombre del negocio en la fachada; el domicilio tiene multiples locales y el encuadre capturo el local contiguo. Sin embargo, la ficha de Maps verificada (mismo nombre exacto 'Autoelectrica H.C. Acumuladores') tiene categoria oficial 'Tienda de baterias para automovil', 3.9 estrellas (8 resenas). El nombre del negocio incluye explicitamente 'ACUMULADORES'. Veredicto SI sostenido en nombre+categoria+resenas, no en foto de producto.</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>fotos/194_autoelectrica_h_c_acumuladores/streetview_1.jpg; fotos/194_autoelectrica_h_c_acumuladores/streetview_2.jpg; fotos/194_autoelectrica_h_c_acumuladores/maps_foto_1.jpg; fotos/194_autoelectrica_h_c_acumuladores/maps_foto_2.jpg; fotos/194_autoelectrica_h_c_acumuladores/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O195" s="3" t="n"/>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>COMPRA Y VENTA DE BATERIAS</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>C. Plutarco Elías Calles 139, Chinam Pac de Juárez, Iztapalapa, 09208 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>19.3738947</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>-99.0419131</v>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="n"/>
+      <c r="I196" s="2" t="n"/>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>N/A - Street View ya mostraba evidencia clara y suficiente.</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el pin exacto muestra letreros grandes 'OFERTA DE BATERIA NUEVA DESDE $1000' y 'COMPRA Y VENTA DE BATERIAS SEMINUEVAS CON GARANTIA'. Se ve anaquel con cajas de producto de bateria a la venta. Confirmado en Maps: categoria 'Tienda de baterias para automovil', 4.6 estrellas (8 resenas).</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>fotos/195_compra_y_venta_de_baterias/streetview_1.jpg; fotos/195_compra_y_venta_de_baterias/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O196" s="3" t="n"/>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>ACOMULADORES REMI LL</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Pabellón 19, La Era I y II, Iztapalapa, 09720 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>19.3429815</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>-99.0578416</v>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>REMI-II</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing, Full Power</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg: fachada completa con letrero 'REMI-II', mural de LTH y 'REFACCIONARIA AUTOMOTRIZ'. maps_foto_2.jpg: anaquel con baterias fisicas de America Racing, LTH y Full Power.</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>Street View y fotos de Maps coinciden: fachada con 'LTH LUBRICANTES', 'REMI-II' y 'REFACCIONARIA AUTOMOTRIZ'. Ficha de Maps confirmada: mismo nombre exacto, categoria 'Tienda de baterias para automovil', 5.0 estrellas.</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>fotos/196_acomuladores_remi_ll/streetview_1.jpg; fotos/196_acomuladores_remi_ll/streetview_2.jpg; fotos/196_acomuladores_remi_ll/maps_foto_1.jpg; fotos/196_acomuladores_remi_ll/maps_foto_2.jpg; fotos/196_acomuladores_remi_ll/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O197" s="3" t="n"/>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS PARA AUTOMOVIL ''SAID''</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>San Rafael Atlixco 5-Manzana 1, Santa Ana Poniente, Tláhuac, 13300 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>19.3070667</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>-99.0441398</v>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="n"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Dynamo, LTH, Full Power, América, Diener, Cronos</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>Fotos subidas por el propietario: bateria marca Dynamo, bateria LTH, collage con multiples marcas.</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto muestra un puesto de 'Pollo Fresco' y un consultorio de psicologia, sin relacion con baterias. La ficha de Maps verificada (mismo nombre exacto 'BATERIAS PARA AUTOMOVIL SAID') tiene categoria 'Tienda de baterias para automovil', 5.0 estrellas, y su galeria de fotos (subidas por el propietario) muestra productos de bateria reales de varias marcas.</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>fotos/197_baterias_para_automovil_said/streetview_1.jpg; fotos/197_baterias_para_automovil_said/streetview_2.jpg; fotos/197_baterias_para_automovil_said/maps_foto_1.jpg; fotos/197_baterias_para_automovil_said/maps_foto_2.jpg; fotos/197_baterias_para_automovil_said/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="O198" s="3" t="n"/>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Sabadel No48, San Juan Estrella, Iztapalapa, 09860 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>19.3287841</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>-99.0679622</v>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg muestra banner grande de LTH, letrero rojo 'COMPRO CASCO' con tabulador de precios, y anaquel con baterias fisicas apiladas dentro del local.</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto solo capto un muro con grafiti, sin negocio visible. La foto de la galeria de Maps para esta ficha exacta (mismo nombre 'Acumuladores' y direccion) muestra claramente un local con banner de LTH y anaquel de baterias fisicas. Ficha confirmada: categoria 'Tienda de baterias para automovil', 4.0 estrellas (7 resenas).</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>fotos/198_acumuladores/streetview_1.jpg; fotos/198_acumuladores/streetview_2.jpg; fotos/198_acumuladores/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O199" s="3" t="n"/>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Muñoz</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Av. Leyes de Reforma 09310, Leyes de Reforma 3ra Secc, Iztapalapa, 09310 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>19.3769344</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>-99.065153</v>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="n"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América, Gonher, Exide</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg (interior) muestra la cortina abierta del local con un anaquel completo de baterias fisicas de multiples marcas organizadas en columnas a ambos lados de la entrada.</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el pin exacto muestra 'Auto Servicio El Triunfo' y una tienda de vinos y licores contiguos. La ficha de Maps verificada (mismo nombre exacto 'Acumuladores Munoz', 5.0 estrellas) tiene una foto de interior que muestra un anaquel real y extenso de baterias fisicas de multiples marcas a la venta.</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>fotos/199_acumuladores_munoz/streetview_1.jpg; fotos/199_acumuladores_munoz/streetview_2.jpg; fotos/199_acumuladores_munoz/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O200" s="3" t="n"/>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA DE ACUMULADORES CGS</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Av. Carlos Hank González MZ21 LT36, 2da Amp Santiago Acahualtepec, Iztapalapa, 09609 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>19.3416812</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>-99.0076227</v>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>...CGS</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="n"/>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>N/A - Street View ya mostraba evidencia clara y suficiente.</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el pin exacto muestra letreros 'VENTA de BATERIA', 'SERVICIO ELECTRICO CHARLY' con '...CGS' parcialmente visible (coincide con 'Distribuidora De Acumuladores CGS'), 'CARGA DE BATERIAS', y un anaquel con cajas de bateria fisicas dentro del local. Confirmado en Maps: mismo nombre exacto, categoria 'Tienda de baterias para automovil', 4.5 estrellas (12 resenas).</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>fotos/200_distribuidora_de_acumuladores_cgs/streetview_1.jpg; fotos/200_distribuidora_de_acumuladores_cgs/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O201" s="3" t="n"/>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Multimarcas Muñoz ryma</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Ermita Iztapalapa 4004, Santa María Aztahuacan, Iztapalapa, 09500 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>19.3453153</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>-99.0219895</v>
+      </c>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS RYMA</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="n"/>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg muestra un letrero amarillo 'BATERIAS Nuevas y 1/2 uso RYMA' con iconos de baterias, un anaquel interior con cajas apiladas compatibles con baterias, y un sandwich board anunciando oferta de baterias con precio y logos Visa/Mastercard.</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>El letrero de la fachada dice 'BATERIAS RYMA', coincidiendo con 'ryma' del nombre registrado ('Acumuladores Multimarcas Muñoz ryma'). Se observa anaquel con producto apilado y publicidad de oferta de baterias directamente en el domicilio del PIN.</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>fotos/201_acumuladores_multimarcas_munoz_ryma/streetview_1.jpg; fotos/201_acumuladores_multimarcas_munoz_ryma/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O202" s="3" t="n"/>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES Y LUBRICANTES PROJACK ETIAN</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Plan de Ayala 906, Zona Urbana Ejidal Santa María Aztahuacan, Iztapalapa, 09570 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>19.3516603</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>-99.0333043</v>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="n"/>
+      <c r="I203" s="2" t="n"/>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg y streetview_2.jpg no muestran ninguna bateria: en el PIN exacto se ve un negocio de tablaroca/materiales para construccion ('TABLAROCA PANEL REY', 'MATERIALES PARA CONSTRUCCION LA NUEVA ERA'), sin relacion visual con baterias.</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: el Street View en las coordenadas exactas muestra una fachada distinta (materiales de construccion/tablaroca), no baterias, y la ficha no tiene fotos de clientes (solo Street View). Sin embargo la ficha de Google Maps 'Acumuladores Y Lubricantes Projack Etian' lo clasifica como 'Tienda de baterias para automovil', con 4.8 estrellas y 6 reseñas reales (2018-2021) que confirman buen servicio y buenos productos; aparece 'Cerrado temporalmente', consistente con un cambio de giro del local.</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>fotos/202_acumuladores_y_lubricantes_projack_etian/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O203" s="3" t="n"/>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Rodríguez</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>C. I MZ29 LT1, Hueso Periférico, Iztapalapa, 09920 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>19.3086723</v>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>-99.08335169999999</v>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg y streetview_2.jpg muestran el banner 'LTH DE VENTA AQUI' y el rotulo 'ACUMULADORES ... LTH RODRIGUEZ' en la fachada; no se distinguen baterias fisicas apiladas con claridad, pero la marca LTH y el nombre coinciden con el negocio.</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo de la fachada dice 'ACUMULADORES ... LTH RODRIGUEZ', coincidiendo exactamente con el nombre registrado 'Acumuladores Rodriguez', con banner de marca LTH ('LTH de venta aqui') y logo 'America Racing'. Evidencia visual clara y coincidente.</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>fotos/203_acumuladores_rodriguez/streetview_1.jpg; fotos/203_acumuladores_rodriguez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O204" s="3" t="n"/>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS CALDERON</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Av. de las Torres 50, Valle de San Lorenzo, Iztapalapa, 09970 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>19.3019573</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>-99.08125010000001</v>
+      </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="n"/>
+      <c r="I205" s="2" t="n"/>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg y streetview_2.jpg no muestran ninguna bateria; en el PIN exacto se ve 'PHARMATERRA - Farmacia y Consultorio Medico', un negocio de giro totalmente distinto.</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra una farmacia ('Pharmaterra'), sin ningun rotulo o producto relacionado con baterias. La ficha de Maps de 'BATERIAS CALDERON' esta sin reclamar y no tiene ninguna reseña, solo la categoria generica 'Tienda de baterias para automovil'. Sin evidencia real que confirme venta de baterias en este domicilio.</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>fotos/204_baterias_calderon/streetview_1.jpg; fotos/204_baterias_calderon/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O205" s="3" t="n"/>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>HERI BATERIAS</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Miguel Hidalgo 27, 1ra Amp Santiago Acahualtepec, Iztapalapa, 09608 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>19.3505444</v>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>-99.008219</v>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES VIRGO</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg muestra un mural con una bateria pintada, logo 'LTH' y los textos 'SE CARGAN BATERIAS' y 'SE COMPRAN...BATERIAS USADAS' en la esquina de la calle Hidalgo (coincide con la direccion registrada 'Miguel Hidalgo 27'); no se ven baterias fisicas apiladas, solo el mural/rotulacion.</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>El nombre en la fachada ('ACUMULADORES VIRGO') no coincide con el registrado ('HERI BATERIAS'), pero el giro (venta/carga de baterias, logo LTH) y la ubicacion (calle Hidalgo, coincide con la direccion) si corresponden, por lo que se prioriza la evidencia visual. Adicionalmente, la ficha de Maps del mismo place ID carga como 'HERI BATERIAS' (categoria 'Tienda de baterias para automovil') con una foto de portada que muestra el rotulo 'BATERIAS HERI', aunque no se pudo descargar esa foto por inestabilidad del navegador.</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>fotos/205_heri_baterias/streetview_1.jpg; fotos/205_heri_baterias/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O206" s="3" t="n"/>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>SE COMPRAN BATERIAS JAGUAR</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>C. 17 29, José López Portillo, Iztapalapa, 09920 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>19.3074667</v>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>-99.07743929999999</v>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES NERI</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="n"/>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg y streetview_2.jpg muestran un rotulo colgante desgastado que dice 'ACUMULADORES NERI' sobre el edificio exacto del PIN, con una segunda linea de texto ilegible por deterioro; no se ven baterias fisicas ni marca especifica.</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr">
+        <is>
+          <t>El nombre en la fachada ('ACUMULADORES NERI') no coincide con el registrado ('SE COMPRAN BATERIAS JAGUAR'), pero el giro (acumuladores/baterias) si corresponde y el rotulo esta directamente en el edificio del PIN, por lo que se prioriza la evidencia visual sobre el nombre. Como referencia adicional (no verificada directamente por falla del navegador), el negocio registrado aparece categorizado en Google Maps como 'Tienda de baterias para automoviles' (2.0 estrellas, 2 reseñas).</t>
+        </is>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>fotos/206_se_compran_baterias_jaguar/streetview_1.jpg; fotos/206_se_compran_baterias_jaguar/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O207" s="3" t="n"/>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GUZMAN</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Prol. Plutarco Elías Calles 85, Chinam Pac de Juárez, Iztapalapa, 09208 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>19.3737862</v>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>-99.04149289999999</v>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="n"/>
+      <c r="I208" s="2" t="n"/>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg y streetview_2.jpg no muestran ninguna bateria ni rotulo legible: el local aparece con cortina metalica verde cerrada y tabiques de construccion apilados en la azotea, sin ningun letrero visible.</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE: no hay ningun rotulo o nombre de negocio legible en ninguna de las dos fotos de Street View (local cerrado/en aparente remodelacion). Se intento verificar en Google Maps pero el navegador fallo repetidamente con resultados de negocios no relacionados (3 intentos), por lo que no se pudo confirmar la ficha ni reseñas. No hay evidencia suficiente para confirmar ni descartar venta de baterias.</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>fotos/207_acumuladores_guzman/streetview_1.jpg; fotos/207_acumuladores_guzman/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O208" s="3" t="n"/>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GHR</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Av. la Turba 10, Dr Francisco Cabrera, Tláhuac, 13230 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>19.2944484</v>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>-99.0618266</v>
+      </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GHR</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg (fov=90, contexto) muestra claramente el toldo 'ACUMULADORES GHR' con logo y, junto a el, un rotulo 'LTH'; streetview_1.jpg (zoom, fov=50) solo alcanza a mostrar el borde del mismo rotulo ('ACU...' y 'LTH') porque quedo encuadrado hacia el local vecino ('Papeleria Eben-Ezer').</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg muestra el toldo con el texto 'ACUMULADORES GHR', coincidiendo exactamente con el nombre registrado, junto con un logo de marca LTH visible en la fachada. Aqui la foto de contexto (fov=90) prueba mejor el veredicto que la de zoom (fov=50), que quedo mal encuadrada.</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>fotos/208_acumuladores_ghr/streetview_1.jpg; fotos/208_acumuladores_ghr/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O209" s="3" t="n"/>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>BATTERY CLUB</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Eje 5 Sur 48, San José Aculco, Iztapalapa, 09410 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>19.3778365</v>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>-99.0987782</v>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="n"/>
+      <c r="I210" s="2" t="n"/>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg y streetview_2.jpg muestran un local rotulado 'MOFLES' y 'SE COMPRAN BIRLOS ROBADOS' / 'SEGUROS DE RIN', sin ningun rotulo, logo o producto de baterias visible.</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra un negocio de mofles y birlos/seguros de rin, un giro automotriz distinto y sin ninguna mencion o producto de baterias. La ficha de Maps 'battery club' aparece 'Cerrado temporalmente' con una sola reseña sin texto (3.0 estrellas), sin ninguna confirmacion de venta de baterias. No hay evidencia real de venta de baterias en este domicilio.</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>fotos/209_battery_club/streetview_1.jpg; fotos/209_battery_club/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O210" s="3" t="n"/>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS PARA AUTO DURACELL</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Av de las Minas Lt 3, Citlalli, Iztapalapa, 09660 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>19.3442906</v>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>-99.0208198</v>
+      </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="n"/>
+      <c r="I211" s="2" t="n"/>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg y streetview_2.jpg no muestran ninguna bateria ni marca Duracell; se ve 'FARMACIA YZA' y, en la foto de contexto, tambien 'ABARROTES Y CREMERIA LA MICHOACANA', ambos negocios establecidos y rotulados sin relacion con baterias.</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en las coordenadas exactas muestra una farmacia (YZA) y una tienda de abarrotes/cremeria, sin ningun rotulo ni producto de 'Baterias para Auto Duracell'. Se intento verificar la ficha de Maps 3 veces pero el navegador fallo/mostro resultados cruzados de un negocio distinto ('Duracell Battery Club' en Tlalnepantla) sin llegar a cargar la ficha correcta, por lo que no se pudieron leer reseñas propias; con la evidencia fotografica disponible no hay soporte para confirmar venta de baterias en este domicilio.</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>fotos/210_baterias_para_auto_duracell/streetview_1.jpg; fotos/210_baterias_para_auto_duracell/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O211" s="3" t="n"/>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GALGO</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Rodolfo Usigli 1163, Sector Popular, Héroes de Churubusco, Iztapalapa, 09090 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>19.363441</v>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>-99.1205382</v>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>Abarrotes ISRADAV (tienda de abarrotes con anuncios Coca-Cola; no se ve 'GALGO' ni ningún producto de baterías)</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="n"/>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>No hay fotos adicionales en la ficha de Maps, solo Street View</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el pin exacto muestra un local de abarrotes 'ISRADAV' con anuncios de Coca-Cola, sin ningun rotulo ni producto de baterias. Sin embargo, la ficha de Google Maps 'Acumuladores GALGO' (direccion verificada, coincide con el Excel) tiene categoria 'Tienda de baterias para automovil' y 8 resenas reales que mencionan explicitamente 'instalacion de la bateria' y servicio a domicilio. Evidencia en conflicto real (texto positivo y especifico vs fachada visual que no corresponde): se deja PENDIENTE para revision humana / posible visita de campo, no se fuerza SI ni NO.</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>fotos/211_acumuladores_galgo/streetview_1.jpg; fotos/211_acumuladores_galgo/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O212" s="3" t="n"/>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES REMI</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Ermita Iztapalapa 2677, La Era I y II, Iztapalapa, 09720 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>19.3419121</v>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>-99.0521407</v>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES REMI (rotulo 'MAYOREO DE ACUMULADORES REMI')</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>REMI, LTH, America Racing</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>N/A (se uso Street View)</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra letrero de techo 'MAYOREO DE ACUMULADORES REMI' con logos America Racing y LTH, banner 'TODO Para Chevy' con baterias impresas, y en streetview_2 se aprecia una bateria fisica LTH exhibida en vitrina junto al acceso. Nombre coincide exactamente con el Excel.</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>fotos/212_acumuladores_remi/streetview_1.jpg; fotos/212_acumuladores_remi/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O213" s="3" t="n"/>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS UVAN ERMITA</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Eje 8 Sur 1146, Santa María Aztahuacan, Iztapalapa, 09560 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>19.350678</v>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>-99.01769729999999</v>
+      </c>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>DEPOSITO DE CERVEZA "RAMIREZ" (fachada con logos Modelo, Corona, Bud Light, y letrero 'SE RENTA LOCAL')</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="n"/>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>No se pudo acceder a la pestana 'Interior' de fotos de Maps por contencion del navegador</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el pin exacto muestra un deposito de cerveza 'RAMIREZ' con letrero 'SE RENTA LOCAL', sin nombre ni producto de baterias. La ficha de Google Maps 'Baterias UVAN Ermita' (direccion verificada) tiene sitio web propio 'uvanbattery.com', categoria 'Tienda de baterias' y 5 resenas recientes ('gran variedad de marcas'). Evidencia en conflicto real: se deja PENDIENTE, no se inventa una conciliacion sin poder probarla.</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>fotos/213_baterias_uvan_ermita/streetview_1.jpg; fotos/213_baterias_uvan_ermita/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O214" s="3" t="n"/>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GHR</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Av Guillermo Prieto 208, Miguel Hidalgo, Tláhuac, 13200 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>19.2898469</v>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>-99.0408628</v>
+      </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GHR (edificio azul, rotulo 'Compra VENTA', letrero vertical 'BATERIAS', banner LTH 'VENTA DE BATERIAS')</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America, Full Power</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>N/A (se uso Street View, evidencia suficiente)</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra fachada azul con cornisa amarilla, rotulo 'Compra VENTA', letrero vertical rojo 'BATERIAS', y banner LTH 'VENTA DE BATERIAS' con anaquel de baterias fisicas visibles. DUPLICADO CONFIRMADO: es el MISMO negocio fisico que CASE ID 260 'Baterias Raquel' (ya validado SI) -- ambas fichas comparten la direccion identica 'Av Guillermo Prieto 208' y coordenadas casi identicas (diferencia de ~2 metros), y las fotos muestran el mismo edificio azul con el mismo toldo/anaquel LTH.</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>fotos/214_acumuladores_ghr/streetview_1.jpg; fotos/214_acumuladores_ghr/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O215" s="3" t="n"/>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores López</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Av. Floresta 15, Floresta, 56420 Los Reyes Acaquilpan, Méx., México</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>19.3677112</v>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>-98.9848183</v>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>LOPEZ. ACUMULADORES (rotulo verde con logo LTH)</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>LTH, America</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>N/A (se uso Street View, evidencia suficiente)</t>
+        </is>
+      </c>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 muestra el edificio desde un angulo sin el rotulo visible (cortinas de garage), pero streetview_2 (mismo edificio, otro angulo) muestra claramente el rotulo verde 'LOPEZ. ACUMULADORES' con dos logos LTH y un logo 'America' parcial junto a la entrada. Nombre coincide con el Excel ('Acumuladores Lopez').</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>fotos/215_acumuladores_lopez/streetview_1.jpg; fotos/215_acumuladores_lopez/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O216" s="3" t="n"/>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GHR</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Av. la Turba 822, Miguel Hidalgo, Tláhuac, 13200 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>19.2863727</v>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>-99.04475549999999</v>
+      </c>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>Tienda de audio para autos / gimnasio de box (murales de kickboxing/MMA, rotulos 'ESTEREOS', 'BOCINAS', 'ACCESORIOS'); NO se ve 'GHR' ni ningun producto de baterias</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="n"/>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el pin exacto (Av. la Turba 822, direccion DISTINTA a la de CASE 214, ~560m de separacion) muestra un negocio de estereos para auto / accesorios con murales de box, sin ningun rotulo de 'GHR' ni de baterias. La ficha de Maps trae categoria 'Tienda de baterias' y 1 resena generica, pero se aplica la regla del PIN exacto: si la fachada en el pin no muestra el nombre/producto, se clasifica NO.</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>fotos/216_acumuladores_ghr/streetview_1.jpg; fotos/216_acumuladores_ghr/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O217" s="3" t="n"/>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Baterías “HERSA”</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Av. Agustín Yañez 1510, Sector Popular, Popular, Iztapalapa, 09060 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>19.36555</v>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>-99.11615810000001</v>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>Bateria "HERSA" (rotulo rojo 'VENTA DE BATERIAS HERSA')</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t>N/A (se uso Street View, evidencia suficiente)</t>
+        </is>
+      </c>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra rotulo rojo grande 'VENTA DE BATERIAS HERSA' con logo LTH, banner '48 MESES DE GARANTIA', y baterias fisicas apiladas afuera del local ademas de anaquel con baterias adentro. Nombre coincide exactamente con el Excel.</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>fotos/217_baterias_hersa/streetview_1.jpg; fotos/217_baterias_hersa/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O218" s="3" t="n"/>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>AUTO ELECTRICA GRUPO RIVHER</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Gral. Radamés Gaxiola Andrade 552, Sector Popular, Escuadrón 201, Iztapalapa, 09060 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>19.3650027</v>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>-99.1135386</v>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>AUTO ELECTRICA GRUPO RIVHER (toldo azul con logo LTH)</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>N/A (se uso Street View)</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra el toldo azul con el nombre 'AUTO ELECTRICA GRUPO RIVHER' y el logo de la marca LTH repetido en el toldo. Nombre coincide exactamente con el Excel. Es un taller de electrico automotriz con afiliacion de marca de baterias LTH, aunque la cortina esta cerrada en la foto.</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>fotos/218_auto_electrica_grupo_rivher/streetview_1.jpg; fotos/218_auto_electrica_grupo_rivher/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O219" s="3" t="n"/>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Duracell</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Perforistas 15, San José Aculco, Iztapalapa, 09410 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>19.378268</v>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>-99.0986922</v>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>Vivienda particular con mural religioso y porton amarillo; SIN ningun rotulo comercial ni de baterias</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="n"/>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>No hay fotos adicionales en Maps (solo Street View)</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 y streetview_2 muestran una fachada claramente residencial (mural religioso, porton), sin ningun indicio comercial. La ficha de Maps 'Baterias Duracell' (direccion verificada) confirma categoria 'Tienda de baterias' pero solo tiene 1 resena de hace 4 anos sin texto visible, y ninguna foto adicional a Street View. No se puede confirmar con evidencia real disponible.</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>fotos/219_baterias_duracell/streetview_1.jpg; fotos/219_baterias_duracell/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O220" s="3" t="n"/>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Beto</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Eje 5 Sur 68, Apatlaco, Iztapalapa, 09430 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>19.3793983</v>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>-99.11403129999999</v>
+      </c>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>No se lee 'Beto' en la fachada (cortina roja cerrada), pero hay un letrero fijo en la pared que dice 'VENTA DE BATERIAS...' (confirmado mediante zoom/crop de la foto)</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="n"/>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>N/A (se uso Street View + zoom local)</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1 muestra, en una vista amplia, un letrero oscuro parcialmente oculto por un arbol y una sombrilla; al recortar y ampliar esa zona se lee claramente 'VENTA DE BATERIAS' en la primera linea del letrero. La ficha de Google Maps 'Baterias Beto' (direccion verificada, mismo predio con nomenclatura de calle alterna) tiene 2 resenas que mencionan baterias directamente, incluyendo 'No sirven sus baterias' -- una resena negativa que confirma el producto cuenta como evidencia de venta.</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>fotos/220_baterias_beto/streetview_1.jpg; fotos/220_baterias_beto/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O221" s="3" t="n"/>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Baterías a cambio</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Canal de Chalco 772, Valle de San Lorenzo, Iztapalapa, 09970 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>19.2975018</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>-99.0811533</v>
+      </c>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="n"/>
+      <c r="I222" s="2" t="n"/>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>No se distingue ninguna bateria fisica en streetview_1.jpg ni streetview_2.jpg: la cortina metalica esta cerrada y el rotulo visible es de 'AutoCar' (cables de alta corriente, kits de instalacion, car audio), no del negocio buscado.</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ninguna foto local (Street View) prueba visualmente la venta de baterias -la cortina esta cerrada y el rotulo visible corresponde a 'AutoCar', no a 'Baterias a cambio'-. El veredicto SI se sostiene en la ficha de Maps del mismo place ID del LINK dado (categoria 'Tienda de baterias', 5.0 estrellas, 2 reseñas), incluyendo la reseña de Ulises Varela: 'Compren 3 baterías y todas funcionan a día de hoy perfectamente, recomendado', evidencia textual real y directa de venta de baterias atada a esta ficha exacta.</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>fotos/221_baterias_a_cambio/streetview_1.jpg; fotos/221_baterias_a_cambio/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O222" s="3" t="n"/>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>BATERÍAS FERODA</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Ruben Jaramillo 19, Desarrollo Urbano Quetzalcóatl, Iztapalapa, 62587 Ciudad de México, Mor., México</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>19.3175219</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>-99.0423986</v>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="n"/>
+      <c r="I223" s="2" t="n"/>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ninguna bateria; las fotos muestran un puesto de pizzas ('Pizza Brother's') y una polleria con productos Tyson en el domicilio exacto, sin relacion con baterias.</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto muestra el puesto 'Pizza Brother's' y una polleria 'Tyson', no el rotulo 'BATERÍAS FERODA'. La ficha de Maps no tiene ninguna reseña (0 opiniones) ni fotos adicionales verificables; solo trae la categoria autoasignada 'Tienda de baterias', insuficiente por si sola. Aplica la regla del PIN exacto.</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>fotos/222_baterias_feroda/streetview_1.jpg; fotos/222_baterias_feroda/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O223" s="3" t="n"/>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>HERMANOS H. B.</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Felipe Angeles s/n, Lomas de Zaragoza, Iztapalapa, 09620 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>19.3566501</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>-98.9977964</v>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>HERMANOS H.B.</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg muestra un anaquel metalico con multiples piezas rectangulares oscuras apiladas, consistente con baterias de auto en exhibicion, bajo el rotulo 'HERMANOS H.B.' y el logo 'LTH ACUMULADORES'.</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'HERMANOS H.B.' coincide exactamente con la fachada en el PIN exacto, junto con el rotulo 'LTH ACUMULADORES' y un anaquel con producto apilado visible en ambas fotos de Street View.</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>fotos/223_hermanos_h_b/streetview_1.jpg; fotos/223_hermanos_h_b/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O224" s="3" t="n"/>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LA 9</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Calle 9 141, Valle de los Reyes, 56430 Los Reyes Acaquilpan, Méx., México</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>19.369276</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>-98.9744378</v>
+      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>ACOMULADORES "LA 9"</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="n"/>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas porque la cortina metalica esta cerrada; el rotulo en la cortina dice explicitamente 'ACOMULADORES LA 9 - RECARGA DE BATERIAS LENTA Y RAPIDA'.</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>El nombre coincide con el registrado ('La 9'), y el rotulo de la fachada en el PIN exacto ofrece explicitamente recarga y servicio de baterias, visible en streetview_1.jpg. Evidencia textual directa en la fachada.</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>fotos/224_acumuladores_la_9/streetview_1.jpg; fotos/224_acumuladores_la_9/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O225" s="3" t="n"/>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>AUTO PRO</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Carr. Federal Texcoco-México 334, Col. La Magdalena Atlicpac, 56525 La Magdalena Atlicpac, Méx., México</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>19.3669962</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>-98.9489688</v>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="n"/>
+      <c r="I226" s="2" t="n"/>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>No se identifica ningun producto de baterias en streetview_1.jpg/streetview_2.jpg; el local en el PIN exacto es un taller de impresion de lonas ('LONA IMPRESA', tarjetas y volantes).</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE: Street View en el PIN exacto muestra 'LONA IMPRESA', sin relacion con baterias y sin mostrar el nombre 'Auto Pro'. La ficha de Maps si esta categorizada como 'Tienda de baterias para automovil' y tiene 2 reseñas 5 estrellas recientes, pero ninguna menciona baterias explicitamente y no se pudieron revisar fotos de producto. Evidencia insuficiente.</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>fotos/225_auto_pro/streetview_1.jpg; fotos/225_auto_pro/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O226" s="3" t="n"/>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GOFER</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Calle 9 387, Valle de los Reyes, 56430 Los Reyes Acaquilpan, Méx., México</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="n">
+        <v>19.3667194</v>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>-98.975921</v>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>GOFER (rotulo superior "ACUMULADORES")</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas en exhibicion (cortina cerrada); la cortina metalica tiene pintada a gran escala una bateria de marca LTH, bajo un rotulo verde 'ACUMULADORES'.</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'GOFER' coincide exactamente con el registrado ('ACUMULADORES GOFER'), junto con el rotulo 'ACUMULADORES' y el logo de marca LTH pintado directamente en la cortina del local, en el PIN exacto.</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>fotos/226_acumuladores_gofer/streetview_1.jpg; fotos/226_acumuladores_gofer/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O227" s="3" t="n"/>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Battery Center Tecomitl – Baterías para Auto usadas y nuevas y Entrega a Domicilio</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>Juana de Arco 6, Tecaxtitla, Milpa Alta, 12100 San Antonio Tecómitl, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="n">
+        <v>19.2253611</v>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>-98.99343519999999</v>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="n"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>America Racing, Checker</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K228" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ningun producto en streetview_1.jpg/streetview_2.jpg (lote de consignacion de autos 'EMPORIO' en el PIN exacto). No hay fotos de producto disponibles porque es un negocio de entrega a domicilio sin aparador fisico.</t>
+        </is>
+      </c>
+      <c r="L228" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ninguna foto (Street View) prueba visualmente la venta de baterias -el PIN exacto muestra un lote de consignacion de autos 'Emporio'-, consistente con que 'Battery Center Tecomitl' opera bajo modelo de entrega a domicilio sin local publico. El veredicto SI se sostiene en el sitio web oficial ligado a esta ficha de Maps (batterycentertecomitl.mex.tl), que describe explicitamente venta e instalacion de baterias nuevas, marcas America Racing y Checker, precios, garantia hasta 24 meses, y testimonio de cliente.</t>
+        </is>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>fotos/227_battery_center_tecomitl_baterias_para_auto_usadas_y_nuevas_y_entrega_a_domicilio/streetview_1.jpg; fotos/227_battery_center_tecomitl_baterias_para_auto_usadas_y_nuevas_y_entrega_a_domicilio/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O228" s="3" t="n"/>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "CORA"</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Blvd. Jose Lopez Portillo Sur 246, Cruztitla, Milpa Alta, 12100 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="n">
+        <v>19.2111278</v>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>-98.9971048</v>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="n"/>
+      <c r="I229" s="2" t="n"/>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ningun producto ni rotulo; solo un porton metalico negro cerrado sin identificacion visible.</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE: Street View en el PIN exacto muestra un porton cerrado sin ningun rotulo ni nombre visible. La ficha de Maps del mismo place ID no tiene reseñas (0 opiniones) y su galeria solo ofrece 'Street View y 360°' (sin fotos de interior ni del propietario). Insuficiente para confirmar ni descartar.</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>fotos/228_acumuladores_cora/streetview_1.jpg; fotos/228_acumuladores_cora/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O229" s="3" t="n"/>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>SERVICIO BECERRA TECAMACHALCO (POLANCO, CONDESA, DEL VALLE)</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>C. Atlaltunco 90, San Miguel Tecamachalco, Lomas de Tecamachalco, 53970 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="n">
+        <v>19.4237171</v>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>-99.2325467</v>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>SERVICIO BECERRA - TECAMACHALCO | POLANCO | DEL VALLE</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas en exhibicion (es un mural/rotulo pintado en el muro exterior); se aprecia una ilustracion grande de una bateria de marca LTH y el logo 'FULL POWER' pintados junto con el nombre y telefonos del negocio.</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>El nombre 'SERVICIO BECERRA' con las zonas 'TECAMACHALCO | POLANCO | DEL VALLE' coincide exactamente con el registrado, junto con logos de marca LTH y Full Power pintados en el muro del PIN exacto.</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>fotos/229_servicio_becerra_tecamachalco_polanco_condesa_del_valle/streetview_1.jpg; fotos/229_servicio_becerra_tecamachalco_polanco_condesa_del_valle/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O230" s="3" t="n"/>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Baterías naucalpan acumuladores mega</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Mega San Mateo, Manzana 033, Bosques de Moctezuma, 53279 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>19.4813908</v>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>-99.2513747</v>
+      </c>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="n"/>
+      <c r="I231" s="2" t="n"/>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>No se identifican baterias fisicas con claridad; el encuadre principal muestra una carpinteria y una vidrieria. En el borde izquierdo de streetview_2.jpg se alcanza a ver, cortado, un rotulo rojo con la palabra 'BATERIAS', pero el encuadre no es concluyente.</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View en el PIN exacto esta encuadrado sobre 'CARPINTERIA Y BARNIZ' y 'VIDRIO Y ALUMINIO'; el rotulo de baterias solo se alcanza a ver cortado en el borde. El veredicto SI se sostiene en la ficha de Maps del mismo place ID (4.8 estrellas, 62 reseñas), con multiples reseñas explicitas sobre el servicio de baterias ('Excelente atencion, en menos de media hora cambiaron la bateria'; 'Muy buen servicio, baterias de calidad').</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>fotos/230_baterias_naucalpan_acumuladores_mega/streetview_1.jpg; fotos/230_baterias_naucalpan_acumuladores_mega/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O231" s="3" t="n"/>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES-CHAMAPA</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>Carr. Toluca - Naucalpan 82, San Rafael Chamapa Segunda Secc, 53660 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>19.4571673</v>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>-99.26204370000001</v>
+      </c>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="n"/>
+      <c r="I232" s="2" t="n"/>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>N/A - ficha solo tiene fotos de Street View, sin 'Del propietario' ni 'Interior'</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: confirmado en Google Maps nombre 'ACUMULADORES-CHAMAPA' y direccion, categoria 'Tienda de baterias para automovil', 2 resenas 5.0 sin texto. Las 2 fotos disponibles (unicas en la ficha) muestran un edificio azul con persiana roja cerrada y auto estacionado tapando la fachada. No hay rotulo, logo ni producto visible, y no hay fotos adicionales ni resenas con texto. Evidencia insuficiente para SI o NO.</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>fotos/231_acumuladores_chamapa/streetview_1.jpg; fotos/231_acumuladores_chamapa/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O232" s="3" t="n"/>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "PISCIS"</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Av. Niños Heroes 107, San Luis Tlatilco, 53580 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>19.4578411</v>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>-99.2446446</v>
+      </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES PISCIS</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>N/A - evidencia suficiente en Street View</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra rotulo 'ACUMULADORES PISCIS' tanto en el letrero exterior como pintado sobre el mostrador interior, con bateria LTH ilustrada, cartel 'SE COMPRAN BATERIAS USADAS'. Coincidencia exacta de PIN y nombre.</t>
+        </is>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>fotos/232_acumuladores_piscis/streetview_1.jpg; fotos/232_acumuladores_piscis/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O233" s="3" t="n"/>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS MADRID</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>C. Ramos Millán 24, Naucalpan Centro, 53000 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="n">
+        <v>19.4756084</v>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>-99.2343484</v>
+      </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS "PACMAN" - Francisco Madrid</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Duracell, Gonher, Full Power, LTH, V8, Xtreme, Autobat, America</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>Mostrador/anaquel con ~15-20 baterias de auto de varias marcas con etiquetas de promocion; foto de fachada con auto promocional con librado 'DURACELL' y bateria inflable gigante.</t>
+        </is>
+      </c>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t>Street View del PIN exacto muestra una vidrieria/aluminio, negocio distinto. La ficha de Google Maps de 'BATERIAS MADRID' (mismo telefono impreso en tarjeta) trae fotos que muestran una tarjeta de presentacion real: 'BATERIAS PACMAN - Francisco Madrid'. El nombre real del negocio es 'Baterias Pacman' del propietario de apellido Madrid (explica el registro 'BATERIAS MADRID').</t>
+        </is>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>fotos/233_baterias_madrid/streetview_1.jpg; fotos/233_baterias_madrid/streetview_2.jpg; fotos/233_baterias_madrid/maps_foto_1.jpg; fotos/233_baterias_madrid/maps_foto_2.jpg; fotos/233_baterias_madrid/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="O234" s="3" t="n"/>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS EL DODO</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Av. México numero 5, El Mirador, 53050 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="n">
+        <v>19.4783056</v>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>-99.2352551</v>
+      </c>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS EL DODO</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>N/A - evidencia suficiente en Street View</t>
+        </is>
+      </c>
+      <c r="L235" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra rotulo 'BATERIAS EL DODO' con telefono de contacto, mostrador con baterias LTH visibles, cartel 'FUERZA EN SU MAXIMA POTENCIA' de marca America, banner 'LTH 48 MESES DE GARANTIA'.</t>
+        </is>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>fotos/234_baterias_el_dodo/streetview_1.jpg; fotos/234_baterias_el_dodo/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N235" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O235" s="3" t="n"/>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Baterías para auto Trotsky</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>Av. de las Huertas 4, Las Huertas 3ra Secc, 53427 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="n">
+        <v>19.4614785</v>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>-99.2851635</v>
+      </c>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES (rotulo, nombre completo confirmado en ficha de Maps: Trotsky)</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Gonher, America, Xtreme, TBS</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t>Mostrador/anaquel interior con baterias de marca LTH, Gonher, America y Xtreme; cartel exterior 'VENTA DE BATERIAS - LTH Xtreme TBS America'.</t>
+        </is>
+      </c>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t>Ficha de Google Maps confirma nombre 'Baterias para auto Trotsky' y direccion exacta. Fotos de la propia ficha muestran fachada con rotulo 'ACUMULADORES' + logo LTH, y foto del mostrador interior con baterias LTH/Gonher/America/Xtreme. Resenas confirman con texto.</t>
+        </is>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>fotos/235_baterias_para_auto_trotsky/streetview_1.jpg; fotos/235_baterias_para_auto_trotsky/streetview_2.jpg; fotos/235_baterias_para_auto_trotsky/maps_foto_1.jpg; fotos/235_baterias_para_auto_trotsky/maps_foto_2.jpg; fotos/235_baterias_para_auto_trotsky/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="O236" s="3" t="n"/>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LYAN</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>MEX 3 170, San Mateo Nopala, 53220 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="n">
+        <v>19.5027986</v>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>-99.2666808</v>
+      </c>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>ACOMULADORES LYAN</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América, Gonher, Xtreme, Full Power</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K237" s="3" t="inlineStr">
+        <is>
+          <t>Mostrador interior con 4 anaqueles llenos de baterias de marca America, LTH, Gonher y Xtreme (~20-25 piezas).</t>
+        </is>
+      </c>
+      <c r="L237" s="3" t="inlineStr">
+        <is>
+          <t>Street View en las coordenadas exactas solo mostraba el local vecino de 'SERVICIO ELECTRICO'. La propia ficha de Google Maps 'Acumuladores LYAN' (misma direccion, mismo telefono) trae fotos que muestran claramente el rotulo 'ACOMULADORES LYAN' y foto de mostrador interior con anaqueles llenos de baterias de multiples marcas.</t>
+        </is>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>fotos/236_acumuladores_lyan/streetview_1.jpg; fotos/236_acumuladores_lyan/streetview_2.jpg; fotos/236_acumuladores_lyan/maps_foto_1.jpg; fotos/236_acumuladores_lyan/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O237" s="3" t="n"/>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>CASA DE LA BATERIA -MOLINITO-</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>2da. Cda. de Rio Hondo 20, El Molinito, 53530 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="n">
+        <v>19.4554284</v>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>-99.23841470000001</v>
+      </c>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>LA CASA DE LA BATERIA</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>Vitrina/reja con anaquel de baterias de marca LTH y America (~15 piezas) junto a rotulo 'LA CASA DE LA BATERIA'.</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>Negocio marcado 'Cerrado temporalmente' en Google Maps (no descalifica). Street View en el PIN exacto solo mostraba un 'CONSULTORIO MEDICO' con un letrero pequeno 'LTH'. La ficha de Maps 'Casa de la bateria -MOLINITO-' (misma direccion) trae una foto que muestra el rotulo completo 'LA CASA DE LA BATERIA' con logo LTH y mostrador con baterias visibles. Resena confirma con texto.</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>fotos/237_casa_de_la_bateria_molinito/streetview_1.jpg; fotos/237_casa_de_la_bateria_molinito/streetview_2.jpg; fotos/237_casa_de_la_bateria_molinito/maps_foto_1.jpg; fotos/237_casa_de_la_bateria_molinito/maps_foto_2.jpg; fotos/237_casa_de_la_bateria_molinito/maps_foto_3.jpg</t>
+        </is>
+      </c>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O238" s="3" t="n"/>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Baterías MADRID 2</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Blvd. Luis Donaldo Colosio 799, San Rafael Chamapa Primera Secc, 53664 Ciudad de México, Méx., México</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="n">
+        <v>19.4569539</v>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>-99.26113410000001</v>
+      </c>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>SERVICIO OVNI (segunda sucursal de la cadena 'Madrid', ver CASE ID 233)</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América, Duralast, Leopard</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>Mostrador exterior con rejas verdes cargadas de baterias de auto de marcas LTH, America, Duralast y Leopard (~30-40 piezas), cartel 'VENTA DE BATERIAS NUEVAS Y USADAS'.</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>El nombre en la fachada es 'SERVICIO OVNI', no 'Baterias Madrid 2'. Sin embargo el telefono de la ficha es identico al de CASE ID 233 'BATERIAS MADRID' (negocio de Francisco Madrid), confirmando que es una segunda sucursal de la misma cadena/propietario. Reseña de un cliente confirma directamente la venta de baterias.</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>fotos/238_baterias_madrid_2/streetview_1.jpg; fotos/238_baterias_madrid_2/streetview_2.jpg; fotos/238_baterias_madrid_2/maps_foto_1.jpg; fotos/238_baterias_madrid_2/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O239" s="3" t="n"/>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>TURBO BATERIAS SUC. SAN MATEO NAUCALPAN</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Cam. Real a San Mateo 53, Santiago Occipaco, 53250 Ciudad de México, Méx., México</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="n">
+        <v>19.4949844</v>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>-99.25333209999999</v>
+      </c>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="n"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>N/A - evidencia suficiente en Street View, ficha solo tiene fotos de Street View.</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>Ficha de Google Maps confirma nombre exacto 'Turbo Baterias suc. San Mateo Naucalpan' y direccion, categoria 'Tienda de baterias para automovil'. Las 2 fotos muestran claramente un mostrador con anaqueles de baterias LTH, cartel 'SE COMPRAN CASCOS DE BATERIA' y un mural 'AMERICA RACING' junto al logo LTH.</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>fotos/239_turbo_baterias_suc_san_mateo_naucalpan/streetview_1.jpg; fotos/239_turbo_baterias_suc_san_mateo_naucalpan/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O240" s="3" t="n"/>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores Méndez Santiago Occipaco</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Cam. a San Mateo Nopala 121, Santiago Occipaco, 53250 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="n">
+        <v>19.5023657</v>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>-99.25830430000001</v>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES... (nombre completo 'Mendez' cortado en el encuadre)</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>N/A - evidencia suficiente en Street View</t>
+        </is>
+      </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra fachada pintada con 'ACUMULADORES' en letras grandes, logo LTH, cartel 'SE COMPRAN BATERIAS USADAS A BUEN PRECIO' e icono de bateria+motocicleta. Ficha de Maps confirma nombre 'Acumuladores Mendez Santiago Occipaco' y direccion, 4.4 estrellas / 11 resenas.</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>fotos/240_acumuladores_mendez_santiago_occipaco/streetview_1.jpg; fotos/240_acumuladores_mendez_santiago_occipaco/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O241" s="3" t="n"/>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>TurboBaterias suc.Acatlán</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>P.º de los Mexicas 125, Sta Cruz Acatlan, 53150 Ciudad de México, Méx., México</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>19.4826469</v>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>-99.240202</v>
+      </c>
+      <c r="F242" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>TurboBaterias suc.Acatlán</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América, Full Power, X-treme</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t>Foto de la galeria de Maps (verificada): exhibidor metalico verde con mas de 20 baterias de auto en caja de varias marcas tras cortina metalica azul.</t>
+        </is>
+      </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>Street View en el PIN exacto solo mostraba un edificio de 'Asociacion de Policias' y un anuncio pequeno de LTH, sin nombre del negocio. Se revisó la galeria completa de la ficha de Maps 'TurboBaterias suc.Acatlan' y se confirmo (via mini-mapa incrustado) que la foto principal muestra un exhibidor callejero repleto de baterias de varias marcas.</t>
+        </is>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>fotos/241_turbobaterias_suc_acatlan/streetview_1.jpg; fotos/241_turbobaterias_suc_acatlan/streetview_2.jpg; fotos/241_turbobaterias_suc_acatlan/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O242" s="3" t="n"/>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LTH</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Av. de los Arcos 115, Loma Colorada, Loma Colorada Primera Secc, 53420 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="n">
+        <v>19.4649172</v>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>-99.2697095</v>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K243" s="3" t="inlineStr">
+        <is>
+          <t>Sin fotos adicionales en la galeria de Maps; no se aprecia producto en ninguna toma.</t>
+        </is>
+      </c>
+      <c r="L243" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: la cortina metalica esta cerrada en ambas tomas, pero el toldo dice claramente 'ACUMULADORES', coincidiendo con el nombre registrado 'ACUMULADORES LTH'. En Google Maps la ficha esta categorizada como 'Tienda de baterias para automovil', con 4 resenas y 5.0 estrellas; una resena dice explicitamente 'Muy buenos acumuladores'. No se ve mostrador ni producto fisico por la cortina cerrada; el veredicto SI se sostiene en el rotulo + resenas + categoria de Maps.</t>
+        </is>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>fotos/242_acumuladores_lth/streetview_1.jpg; fotos/242_acumuladores_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O243" s="3" t="n"/>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>DURACELL AV.MEXICAS</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>P.º de los Mexicas 44-32, Sta Cruz Acatlan, 53150 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="n">
+        <v>19.4851435</v>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>-99.2426287</v>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>AT&amp;T Laboratorio de Celulares (no coincide con 'Duracell')</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="n"/>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>Sin fotos adicionales en la galeria de Maps; no hay imagenes de producto.</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE: el PIN exacto de Street View muestra un local de reparacion de celulares en ambas tomas, sin ningun rastro del nombre 'Duracell'. La ficha de Google Maps 'duracell av.mexicas' si existe como negocio propio: categorizada como 'Tienda de baterias para automovil', con 'Entrega a domicilio', pero solo 1 resena generica sin mencionar baterias y sin fotos adicionales. Posible negocio de entrega a domicilio sin aparador visible, pero no hay evidencia suficiente para confirmar ni descartar.</t>
+        </is>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>fotos/243_duracell_av_mexicas/streetview_1.jpg; fotos/243_duracell_av_mexicas/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O244" s="3" t="n"/>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Av. Vía Adolfo López Mateos 4, Santa Cruz del Monte, 53110 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="n">
+        <v>19.5134294</v>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>-99.246009</v>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>ACUMU[LADORES]... (parcialmente cubierto por banners publicitarios)</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>LTH, GONHER</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K245" s="3" t="inlineStr">
+        <is>
+          <t>N/A - no se reviso galeria adicional de Maps; Street View fue concluyente.</t>
+        </is>
+      </c>
+      <c r="L245" s="3" t="inlineStr">
+        <is>
+          <t>La fachada muestra un rotulo negro 'ACUMU...' junto con el logo de LTH y una manta de la marca GONHER ('4 anos de garantia'), ademas de banners de garantia tipicos de refaccionarias de baterias. El local funciona como refaccionaria/taller con anaqueles de producto, coincidiendo con el giro de 'ACUMULADORES SANTA CRUZ'.</t>
+        </is>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>fotos/244_acumuladores_santa_cruz/streetview_1.jpg; fotos/244_acumuladores_santa_cruz/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O245" s="3" t="n"/>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES POWER FLASH</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Calz. de Las Armas 6, 10 de Abril, 53320 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="n">
+        <v>19.487869</v>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>-99.21720139999999</v>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES POWER FLASH</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>N/A - Street View fue concluyente y muestra mostrador con baterias.</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>Fachada pintada con el nombre completo 'ACUMULADORES POWER FLASH', leyenda 'COMPRO TODO TIPO DE BATERIAS', logo de LTH y banner de America visibles junto a un vano con baterias en exhibicion. Coincidencia total de nombre y giro.</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>fotos/245_acumuladores_power_flash/streetview_1.jpg; fotos/245_acumuladores_power_flash/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O246" s="3" t="n"/>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GUSTAVO BAZ</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Av. Dr. Gustavo Baz 305, La Loma, 54060 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="n">
+        <v>19.5322364</v>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>-99.2073857</v>
+      </c>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES GUSTAVO BAZ (opera en 'local 8' dentro del edificio 'CARBEN')</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg (verificado como la foto de portada real de la ficha): vitrina con cartel de LTH 'VENTA AQUI', con motos en exhibicion y producto de bateria parcialmente visible en anaquel lateral.</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el PIN exacto muestra solo el edificio 'CARBEN' (nombre del inmueble), sin rotulo del negocio porque opera en 'local 8'. Se verifico la ficha de Google Maps: 14 resenas, 5.0 estrellas, categoria 'Tienda de baterias para automovil', resenas explicitas sobre calidad en las baterias.</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>fotos/246_acumuladores_gustavo_baz/streetview_1.jpg; fotos/246_acumuladores_gustavo_baz/streetview_2.jpg; fotos/246_acumuladores_gustavo_baz/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O247" s="3" t="n"/>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Central de baterías</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Av. Dr. Gustavo Baz 40, Xocoyahualco, 54080 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="n">
+        <v>19.5104947</v>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>-99.218343</v>
+      </c>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ACUMULADORES</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg: fachada con manta 'CENTRAL DE ACUMULADORES - COMPRO BATERIAS USADAS', con banderines de 'BATERIAS AMERICA' y 'LTH'. maps_foto_2.jpg: interior con anaqueles repletos de decenas de baterias LTH, America Racing, ACDelco y Extrema.</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>El Street View en el PIN exacto no muestra el negocio (aparecen 'Rotulos Arte/Toldos' y 'Frene a Tiempo'). Se confirmo que las fotos de Maps SI pertenecen a esta ficha exacta: el telefono impreso en la manta de la fachada coincide EXACTO con el telefono registrado en esta ficha de Maps. NOTA: este negocio podria estar muy cerca (~38m) de CASE ID 253 'SUPERDISTRIBUIDORA DE ACUMULADORES FLASH' (ya validado SI); son negocios distintos y contiguos -- la evidencia aqui documentada es propia de esta ficha (coincidencia de telefono), no prestada de la ficha de 253.</t>
+        </is>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>fotos/247_central_de_baterias/streetview_1.jpg; fotos/247_central_de_baterias/streetview_2.jpg; fotos/247_central_de_baterias/maps_foto_1.jpg; fotos/247_central_de_baterias/maps_foto_2.jpg</t>
+        </is>
+      </c>
+      <c r="N248" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O248" s="3" t="n"/>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES MIRANDA</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Av. Pdte. Juárez 12, Puente de Vigas, 54090 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>19.5133742</v>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>-99.2137481</v>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>...UMULADORES MIRANDA (ACUMULADORES MIRANDA)</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América Racing</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>N/A - Street View fue concluyente.</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>Fachada muestra el rotulo 'ACUMULADORES MIRANDA' junto con un logo grande de LTH pintado sobre la cortina metalica, banner de 'America Racing' y leyenda 'CARGA DE BATERIAS'. Coincide exactamente con el nombre registrado.</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>fotos/248_acumuladores_miranda/streetview_1.jpg; fotos/248_acumuladores_miranda/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O249" s="3" t="n"/>
+      <c r="P249" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>XBATT</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>Fuente de Las Pirámides 16-Piso 4, Lomas de Tecamachalco, 53950 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>19.4277209</v>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>-99.22592880000001</v>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="n"/>
+      <c r="I250" s="2" t="n"/>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>Sin fotos adicionales en la galeria de Maps (solo Street View).</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE: la direccion registrada es un piso 4 (oficina) dentro de un edificio; ambas tomas de Street View muestran solo un anuncio publicitario ajeno, sin fachada del negocio visible. La ficha de Google Maps 'Xbatt' esta marcada como 'Cerrado temporalmente', 1 resena sin texto visible, sin fotos adicionales. No hay evidencia visual ni textual suficiente para confirmar el giro exacto ni que el negocio este operando.</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>fotos/249_xbatt/streetview_1.jpg; fotos/249_xbatt/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N250" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O250" s="3" t="n"/>
+      <c r="P250" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS CONSERVICIOA DOMICILIO</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Colina de Las Nieves 93a, Boulevares, 53140 Naucalpan de Juárez, Méx., México</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>19.4935298</v>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>-99.24541019999999</v>
+      </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="n"/>
+      <c r="I251" s="2" t="n"/>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>Sin fotos adicionales en la galeria de Maps (solo Street View).</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE: la direccion registrada es 'Local B'; Street View no muestra ningun rotulo, logo o producto de baterias -- solo un muro liso y, en otra toma, una cafeteria/tienda de tisanas no relacionada (posible 'Local A' vecino). La ficha de Google Maps 'baterias conservicioa domicilio' tiene sitio web propio (dominio coincide con el nombre del negocio) pero no cargo al intentar visitarlo. Sin resenas y sin fotos adicionales en Maps. Es plausible que sea un servicio a domicilio sin aparador publico, pero no hay evidencia que lo confirme.</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>fotos/250_baterias_conservicioa_domicilio/streetview_1.jpg; fotos/250_baterias_conservicioa_domicilio/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N251" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O251" s="3" t="n"/>
+      <c r="P251" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS PARA AUTOS LTH ALPES</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>Av Convento de Sta Monica 84, Hab Jardines de Santa Monica, 54050 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="n">
+        <v>19.5346477</v>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>-99.2266338</v>
+      </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>TALLER MECANICO AUTOMOTRIZ</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg muestra el frente del taller con letreros 'BATERIAS' y 'VENTA', el logo LTH repetido y anuncios de LTH y Full Power con imagenes de producto.</t>
+        </is>
+      </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>Streetview_1 y streetview_2 muestran una escena interior no relacionada. La foto de Maps (maps_foto_1.jpg) si corresponde inequivocamente a este domicilio: el rotulo dice 'AV. CONVENTO D SANTA MONICA No. 84' (coincide exacto) y exhibe fuertemente LTH y Full Power con 'BATERIAS'/'VENTA'. El nombre visible es 'Taller Mecánico Automotriz', distinto al registrado, pero el giro y domicilio coinciden.</t>
+        </is>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>fotos/251_baterias_para_autos_lth_alpes/streetview_1.jpg; fotos/251_baterias_para_autos_lth_alpes/streetview_2.jpg; fotos/251_baterias_para_autos_lth_alpes/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O252" s="3" t="n"/>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LUNA</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>De Los Maestros 51, San Andrés Atenco Ampliacion, 54040 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="n">
+        <v>19.5391304</v>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>-99.2224734</v>
+      </c>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES LUNA</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Xtreme</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>No se distinguen con certeza baterias fisicas apiladas, pero el rotulo 'ACUMULADORES LUNA' junto con el logo LTH y publicidad de la marca Xtreme confirman el giro del negocio.</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo verde 'ACUMULADORES LUNA' es visible e identico al nombre registrado en ambas fotos de Street View, junto con el logo de LTH y publicidad de baterias Xtreme ('de venta aqui', '100% garantia').</t>
+        </is>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>fotos/252_acumuladores_luna/streetview_1.jpg; fotos/252_acumuladores_luna/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O253" s="3" t="n"/>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>SUPERDISTRIBUIDORA DE ACUMULADORES FLASH</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>Av. Dr. Gustavo Baz 346, Xocoyahualco, 54080 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>19.5102159</v>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>-99.2185533</v>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n"/>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>LTH, América</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg muestra un rotulo grande sobre la cortina con 'BATERIAS', logo LTH y 'LUBRICANTES', con imagenes impresas de una bateria LTH y una bateria America.</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>Street View muestra negocios vecinos, solo un banderin 'LTH'/'BATERIA...' cortado en el borde. La foto de Maps ya descargada (maps_foto_1.jpg) si corresponde a este domicilio y confirma rotulo 'BATERIAS' con marcas LTH y America.</t>
+        </is>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>fotos/253_superdistribuidora_de_acumuladores_flash/streetview_1.jpg; fotos/253_superdistribuidora_de_acumuladores_flash/streetview_2.jpg; fotos/253_superdistribuidora_de_acumuladores_flash/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N254" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O254" s="3" t="n"/>
+      <c r="P254" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Baterías siddharta</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>C. Fray Pedro de Gante 398, Santa Ursula, 56150 Texcoco de Mora, Méx., México</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="n">
+        <v>19.505478</v>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>-98.88480199999999</v>
+      </c>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>Centro de Servicio Gonher - Distribuidor Siddharta</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>GONHER</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas en exhibicion, pero el rotulo principal dice explicitamente 'CENTRO DE SERVICIO... BATERIAS GONHER... DISTRIBUIDOR SIDDHARTA' con una imagen grande de una bateria GONHER.</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo coincide casi literalmente con el nombre registrado ('Distribuidor Siddharta' = 'Baterías siddharta') y anuncia explicitamente 'BATERIAS GONHER' con imagen de producto, en el domicilio exacto.</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>fotos/254_baterias_siddharta/streetview_1.jpg; fotos/254_baterias_siddharta/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N255" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O255" s="3" t="n"/>
+      <c r="P255" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "HEROT" BOYEROS</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Úrsulo Galván 1a, Salitreria, 56150 Salitrería, Méx., México</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="n">
+        <v>19.495291</v>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>-98.8842439</v>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="n"/>
+      <c r="I256" s="2" t="n"/>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ninguna bateria en ninguna de las dos fotos de Street View; se ven llantas de motocicleta apiladas, cascos/accesorios y rotulos 'REFACCIONARIA MOTOTEK' y 'ALTA MECANICA'.</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>En las coordenadas exactas, ambas fotos de Street View y la miniatura de la propia ficha de Maps muestran una refaccionaria de motocicletas, sin el nombre 'Herot Boyeros' ni ninguna marca o producto de baterias visible. La ficha de Maps categoriza el lugar como tienda de baterias pero no se pudo verificar con fotos adicionales ni reseñas.</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>fotos/255_acumuladores_herot_boyeros/streetview_1.jpg; fotos/255_acumuladores_herot_boyeros/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O256" s="3" t="n"/>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>LUBRITLAHUAC S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Av. Tlahuac 4, Ojo de Agua, Tláhuac, 13450 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="n">
+        <v>19.287379</v>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>-99.01379900000001</v>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>EL JEFE DE JEFES</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power, América</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas apiladas en mostrador; se ven tres anuncios de marca instalados directamente en la fachada del edificio (Full Power y America en los pisos superiores, LTH en el logo circular junto a la entrada).</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>En el domicilio exacto se ven tres rotulos de marcas reales (Full Power, America, LTH) instalados en la propia fachada del edificio, consistente con el giro de 'Lubritlahuac'. El nombre visible a pie de calle es 'El Jefe de Jefes', distinto al registrado; se prioriza el giro y ubicacion. LIMITACION: no se pudo confirmar con reseñas o mas fotos de Maps por inestabilidad del navegador.</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>fotos/256_lubritlahuac_s_a_de_c_v/streetview_1.jpg; fotos/256_lubritlahuac_s_a_de_c_v/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O257" s="3" t="n"/>
+      <c r="P257" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS TROJAN MEXICO</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Av. Sur del Comercio 51, La Soledad, Tláhuac, 13508 San Juan Ixtayopan, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="n">
+        <v>19.2374855</v>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>-98.9950896</v>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="n"/>
+      <c r="I258" s="2" t="n"/>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>No se ve ningun negocio, rotulo ni bateria en ninguna de las dos fotos; ambas muestran unicamente una barda pintada con un mural, sin fachada comercial visible.</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: en las coordenadas exactas, Street View solo muestra una barda pintada con un mural de agradecimiento, sin ningun local comercial, rotulo o producto visible -- no se puede determinar el giro del punto. No se pudo verificar por navegador (inestabilidad repetida); no existe foto de Maps descargada. Se recomienda reintentar la verificacion.</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>fotos/257_baterias_trojan_mexico/streetview_1.jpg; fotos/257_baterias_trojan_mexico/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O258" s="3" t="n"/>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Durcell</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Calz. Tlahuac - Tulyehualco 8307, Los Reyes, Tláhuac, 13094 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="n">
+        <v>19.2652705</v>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>-99.00731450000001</v>
+      </c>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="n"/>
+      <c r="I259" s="2" t="n"/>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>No se ven baterias fisicas ni el nombre 'Durcell' en ninguna foto. La fachada en el punto exacto es una cortina metalica cerrada y cubierta de grafiti, junto a una tienda de abarrotes y un letrero de 'Se renta'.</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: la cortina metalica en el punto exacto esta cerrada, cubierta de grafiti y sin rotulo identificable; los negocios reconocibles alrededor no estan relacionados con baterias. No se pudo verificar por navegador (inestabilidad repetida) ni existe foto de Maps descargada.</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>fotos/258_baterias_durcell/streetview_1.jpg; fotos/258_baterias_durcell/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O259" s="3" t="n"/>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES "ENEO"</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Av. Tlahuac 7404, Santa Cecilia, Tláhuac, 13010 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="n">
+        <v>19.2780605</v>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>-99.0070788</v>
+      </c>
+      <c r="F260" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>Acumuladores ENEO</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>No se distinguen baterias fisicas apiladas con claridad (personas y una motoneta frente al local obstruyen la vista); se lee un letrero 'CARGA DE BATERIAS' y anuncios de las marcas Full Power y LTH en la fachada.</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>El rotulo 'Acumulado[res]...ENEO' coincide exactamente con el nombre registrado, junto con logos de Full Power y LTH y un letrero de servicio 'Carga de baterias', en el domicilio exacto.</t>
+        </is>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>fotos/259_acumuladores_eneo/streetview_1.jpg; fotos/259_acumuladores_eneo/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O260" s="3" t="n"/>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Raquel</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Av Guillermo Prieto 208, Miguel Hidalgo, Tláhuac, 13200 Ciudad de México, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="n">
+        <v>19.2898624</v>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>-99.0408805</v>
+      </c>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="n"/>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Full Power, América</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>Se ven baterias fisicas apiladas en anaqueles metalicos dentro del local (visibles en ambas fotos), bajo un letrero rojo grande 'VENTA DE BATERIAS' con el logo de LTH, y rotulos de las marcas Full Power y America en el toldo superior.</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>Evidencia clara: rotulo 'Compra Venta... Postes y Parchado', banner 'VENTA DE BATERIAS' con LTH, marcas Full Power y America, y baterias fisicas visibles en anaqueles. DUPLICADO DETECTADO: el domicilio y coordenadas (19.2898624,-99.0408805) son practicamente identicos a los del CASE ID 214 'ACUMULADORES GHR' (19.2898469,-99.0408628, mismo domicilio 'Av Guillermo Prieto 208'), y las fotos de Street View de ambos CASE ID muestran el mismo edificio azul, mismo toldo y mismo banner rojo -- son la MISMA ubicacion fisica con dos fichas de Maps distintas.</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>fotos/260_baterias_raquel/streetview_1.jpg; fotos/260_baterias_raquel/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O261" s="3" t="n"/>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>BATERIAS TROJAN DISTRIBUIDOR</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Reforma Agraria 5b, La Asunción, Tláhuac, 13530 San Juan Ixtayopan, CDMX, México</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="n">
+        <v>19.2398988</v>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>-98.9928869</v>
+      </c>
+      <c r="F262" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>Golf Cars Mexico (venta/renta/servicio de carritos de golf)</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="n"/>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>No aplica - ninguna foto muestra baterias</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>streetview_1/2 muestran un muro/porton residencial sin identificacion. maps_foto_1.jpg confirma que el PIN exacto corresponde a 'Golf Cars Mexico': venta/renta/servicio de carritos de golf. No hay ningun indicio de venta de baterias de auto en la fachada.</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>fotos/261_baterias_trojan_distribuidor/streetview_1.jpg; fotos/261_baterias_trojan_distribuidor/streetview_2.jpg; fotos/261_baterias_trojan_distribuidor/maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t>maps_foto_1.jpg</t>
+        </is>
+      </c>
+      <c r="O262" s="3" t="n"/>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>DURACELL BATTERY CLUB</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Blvd. Adolfo Lopez Mateos 8, Francisco Villa, 54059 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>19.540814</v>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>-99.2319176</v>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>AutoZone (rotulo exterior); ficha de Maps aclara 'Ubicado en: Refaccionaria AutoZone'</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Duracell</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>No se obtuvo foto de producto - la unica foto disponible en Maps es la misma toma de Street View con un tractor bloqueando la fachada</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View muestra el edificio de AutoZone, con un tractor bloqueando la entrada. La ficha de Google Maps de 'Duracell Battery Club' confirma categoria 'Tienda de baterias para automovil', direccion coincidente y el dato explicito 'Ubicado en: Refaccionaria AutoZone' (4.7 estrellas, 27 resenas) -- es un mostrador/kiosco de la marca Duracell dentro de esta tienda AutoZone. Ninguna foto disponible prueba visualmente el producto Duracell por la obstruccion.</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>fotos/262_duracell_battery_club/streetview_1.jpg; fotos/262_duracell_battery_club/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O263" s="3" t="n"/>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA FLASH II</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Av. Dr. Gustavo Baz 223, Miguel Hidalgo, 54060 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>19.5263962</v>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>-99.2087872</v>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="n"/>
+      <c r="I264" s="2" t="n"/>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t>No se pudo revisar galeria completa por contencion del navegador con otros agentes concurrentes</t>
+        </is>
+      </c>
+      <c r="L264" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: Street View muestra un edificio oscuro de dos pisos con un letrero azul pequeno no legible. La ficha de Google Maps para 'Distribuidora Flash II' confirma nombre exacto, direccion identica, categoria oficial 'Tienda de baterias para automovil' y resenas positivas sobre precio y servicio a domicilio rapido. No se logro confirmar visualmente el producto por mala iluminacion en Street View y por contencion del navegador.</t>
+        </is>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>fotos/263_distribuidora_flash_ii/streetview_1.jpg; fotos/263_distribuidora_flash_ii/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O264" s="3" t="n"/>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Baterías Pirules LTH</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Blvrd Popocatépetl 87, Valle Dorado, 54040 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>19.5457427</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>-99.2170448</v>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>Baterias Pirules (banner) + logo LTH</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>LTH, Pirules</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>Banner grande muestra el texto 'BATERIAS AUTOMOTRICES, DIAGNOSTICO CON SCANNER, MOTOBATERIAS' junto a imagenes de baterias LTH; letrero adicional anuncia 10% de descuento en 'Baterias Pirules'</t>
+        </is>
+      </c>
+      <c r="L265" s="3" t="inlineStr">
+        <is>
+          <t>Ambas tomas de Street View muestran con total claridad el banner 'Baterias Pirules' con el logo circular LTH repetido, texto de servicios, telefono de contacto. Coincide exactamente con el nombre registrado. Evidencia solida y directa.</t>
+        </is>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>fotos/264_baterias_pirules_lth/streetview_1.jpg; fotos/264_baterias_pirules_lth/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O265" s="3" t="n"/>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL DE ACUMULADORES TEQUEXQUINAHUAC</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Av. Dr. Gustavo Baz 10, U.H. IMSS Tlalnepantla, 54030 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>19.5570637</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>-99.2039575</v>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="n"/>
+      <c r="I266" s="2" t="n"/>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>No se logro revisar galeria de Maps por contencion del navegador</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>LIMITACION: ambas tomas de Street View muestran una avenida amplia sin fachada identificable. La ficha de Google Maps para 'Central de acumuladores TEQUEXQUINAHUAC' confirma nombre exacto, direccion identica, categoria oficial 'Tienda de baterias para automovil', y una resena directa: 'Pesima atencion de la sra. En vez de convencerme de comprar la bateria, me convencio de no comprar' -- evidencia textual de que el negocio efectivamente vende baterias. No existe foto que pruebe visualmente el producto; el veredicto se sostiene en la resena y la categoria oficial de Maps.</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>fotos/265_central_de_acumuladores_tequexquinahuac/streetview_1.jpg; fotos/265_central_de_acumuladores_tequexquinahuac/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O266" s="3" t="n"/>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES CENTELLA</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>De Los Maestros 10, Leandro Valle, 54040 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="n">
+        <v>19.5397271</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>-99.2191461</v>
+      </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>'...ENTELLA' parcialmente visible en mural (coincide con Acumuladores Centella), logo LTH visible</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>LTH</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>Rotulo azul con logo LTH sobre la entrada; letrero adicional dice 'ACUMULADORES VIEJOS' (compra de baterias usadas)</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t>Ambas tomas de Street View muestran, junto a una vulcanizadora con llantas apiladas, un local con logo LTH y texto mural parcialmente cubierto que termina en '...ENTELLA' (coincide con 'Centella'), ademas de un cartel de 'ACUMULADORES VIEJOS' que confirma la compra/venta de acumuladores en el sitio.</t>
+        </is>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>fotos/266_acumuladores_centella/streetview_1.jpg; fotos/266_acumuladores_centella/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O267" s="3" t="n"/>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE SERVICIO EXIDE</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Av. Jesús Reyes Heroles 37, Hab Valle Ceylan, 54150 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="n">
+        <v>19.5350405</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>-99.1806638</v>
+      </c>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>'CENTRO DE SERVICIO MULTIMARCAS' (no se ve el nombre 'Exide' en la fachada actual)</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>Duracell, ACDelco, LTH, America</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>Anaquel completo con decenas de baterias Duracell y ACDelco apiladas por modelo/tamano; banderines de 'America Baterias' y 'LTH'</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>Ambas tomas de Street View muestran un aparador/exhibidor azul lleno de baterias fisicas de multiples marcas, rotulacion grande 'DURACELL' y 'CENTRO DE SERVICIO MULTIMARCAS'. La direccion coincide exactamente. El nombre registrado es 'Centro de Servicio Exide' pero el rotulo visible ahora es de Duracell/multimarcas -- discrepancia de marca documentada, pero el giro y ubicacion son inequivocos.</t>
+        </is>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>fotos/267_centro_de_servicio_exide/streetview_1.jpg; fotos/267_centro_de_servicio_exide/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O268" s="3" t="n"/>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>UCCE</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Valle de Bravo 34, Tlalnemex, 54070 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>19.5261864</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>-99.20585800000001</v>
+      </c>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>'UCCE' (letrero pequeno sobre cortina metalica de una nave/bodega industrial)</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="n"/>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K269" s="3" t="inlineStr">
+        <is>
+          <t>No se encontro ninguna foto adicional en la galeria de Maps</t>
+        </is>
+      </c>
+      <c r="L269" s="3" t="inlineStr">
+        <is>
+          <t>Ambas tomas de Street View muestran una nave/bodega industrial con cortinas metalicas, sin ningun producto o exhibidor visible; solo un letrero pequeno 'UCCE'. La ficha de Google Maps confirma direccion identica y categoria 'Tienda de baterias' (sin 'para automovil'). Las resenas son genericas ('componentes electronicos', 'atencion rapida') y no mencionan baterias de auto especificamente. Podria ser un distribuidor de componentes electricos industriales, no automotrices -- insuficiente para confirmar o descartar.</t>
+        </is>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>fotos/268_ucce/streetview_1.jpg; fotos/268_ucce/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N269" s="2" t="inlineStr">
+        <is>
+          <t>streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="O269" s="3" t="n"/>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>REFACCIONARIA REYES</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>De Los Maestros 65, Leandro Valle, 54040 Tlalnepantla, Méx., México</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="n">
+        <v>19.5387675</v>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>-99.2244822</v>
+      </c>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>'AUTOELECTRICA REYES' (no 'Refaccionaria Reyes' exacto, pero mismo apellido/ubicacion)</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>Exide</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K270" s="3" t="inlineStr">
+        <is>
+          <t>Rotulo grande con logo 'EXIDE Batteries' y fotografia de una bateria de producto</t>
+        </is>
+      </c>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t>Ambas tomas de Street View muestran claramente el rotulo 'AUTOELECTRICA REYES' con un logo grande de 'EXIDE Batteries' (imagen de producto incluida). El nombre registrado es 'Refaccionaria Reyes'; el rotulo real dice 'Autoelectrica Reyes' -- mismo apellido familiar y misma direccion exacta, giro inequivoco.</t>
+        </is>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>fotos/269_refaccionaria_reyes/streetview_1.jpg; fotos/269_refaccionaria_reyes/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O270" s="3" t="n"/>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>ACUMULADORES REMY</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Ote 36-A 189, Providencia, 56616 Xico, Méx., México</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="n">
+        <v>19.2805128</v>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>-98.9220529</v>
+      </c>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>Ver en Maps</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>'Carniceria y Torteria' / 'Tortilleria' (negocio de comida, sin relacion con baterias)</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="n"/>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>No aplica - no se encontraron fotos adicionales en Maps</t>
+        </is>
+      </c>
+      <c r="L271" s="3" t="inlineStr">
+        <is>
+          <t>Ambas tomas de Street View muestran, en el PIN exacto, una carniceria/torteria y una tortilleria contiguas -- giro completamente distinto. La ficha de Maps de 'Acumuladores Remy' tiene direccion aproximada ligeramente distinta a la registrada, sugiriendo geocodificado impreciso. Las 2 resenas existentes son genericas y no aportan evidencia. Aplicando la regla del PIN exacto: NO.</t>
+        </is>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>fotos/270_acumuladores_remy/streetview_1.jpg; fotos/270_acumuladores_remy/streetview_2.jpg</t>
+        </is>
+      </c>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>streetview_1.jpg</t>
+        </is>
+      </c>
+      <c r="O271" s="3" t="n"/>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P141"/>
+  <autoFilter ref="A1:P271"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -10526,6 +19510,136 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId270"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -1298,7 +1298,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Street View bloqueado por un arbol y un puesto de comida en primer plano; fachada no visible. No hay fotos adicionales de Maps. Se confirma por resena de cliente: 'No sirven sus baterias' (2 anos) -- confirma que el negocio vende baterias, aunque cuestiona la calidad. Otras resenas ('Economicas y buenas, recomendable al 100') tambien consistentes con venta de baterias. LIMITACION: no existe ninguna foto (ni Street View ni de Maps) que muestre baterias o la fachada con claridad para este negocio -- solo hay 1 foto de Street View bloqueada. El veredicto SI se sostiene unicamente en la resena de texto ("No sirven sus baterias"), sin respaldo fotografico. Senalado para que el equipo lo confirme si lo considera insuficiente.</t>
+          <t>CORREGIDO A NO (2026-09-12): ni Street View (bloqueado por arbol y puesto de comida) ni la galeria de Maps muestran ninguna evidencia visual (sin rotulo, sin logo, sin producto). El veredicto SI anterior se sostenia solo en resenas de texto ('No sirven sus baterias', 'Economicas y buenas'), lo cual ya no se acepta como evidencia suficiente sin respaldo fotografico. LIMITACION: no existe ninguna foto en toda la ficha que pruebe visualmente la venta de baterias.</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1327,7 +1327,7 @@
       <c r="O12" s="3" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H24" s="2" t="n"/>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H35" s="2" t="n"/>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H74" s="2" t="n"/>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: el Street View en las coordenadas exactas solo muestra un muro con grafiti, sin fachada ni letrero del negocio. Sin embargo, la ficha de Google Maps con el nombre EXACTO 'Baterias sr Santiago Apostol' (4.5, 4 opiniones, 'Tienda de baterías para automóvil') confirma la venta: reseñas dicen explícitamente 'me vendió la batería' y que el vendedor 'llegó a mi domicilio', consistente con un negocio de venta/instalación a domicilio. Aparece 'Cerrado temporalmente' en Maps.</t>
+          <t>CORREGIDO A NO (2026-09-12): el Street View en las coordenadas exactas solo muestra un muro con grafiti, sin fachada ni letrero del negocio, y no hay fotos adicionales en la ficha de Maps. El veredicto SI anterior se sostenia solo en resenas de texto ('me vendio la bateria'), lo cual ya no se acepta como evidencia suficiente sin ninguna foto que muestre nombre, logo o producto.</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
       <c r="O74" s="3" t="n"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H77" s="2" t="n"/>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: el Street View en el pin exacto muestra el local con cortina cerrada y letrero 'SE RENTA', sin nombre de negocio visible. La ficha de Google Maps para 'Acomuladores Gutiérrez' en la dirección EXACTA registrada (P.º del Bosque Mz 49-Lt 19, Bosques de Morelos, Cuautitlán Izcalli) aparece 'Abierto', con calificación 4.8 (20 opiniones) y reseñas que mencionan explícitamente 'las baterías que venden' y 'entrega a domicilio', confirmando la venta pese a que la foto disponible no la muestra.</t>
+          <t>CORREGIDO A NO (2026-09-12): el Street View en el pin exacto muestra el local con cortina cerrada y letrero 'SE RENTA' (sin nombre del negocio), y no hay fotos adicionales en la ficha de Maps que muestren producto, logo o rotulo. El veredicto SI anterior se sostenia solo en resenas de texto, lo cual ya no se acepta sin evidencia fotografica.</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5879,7 +5879,7 @@
       <c r="O77" s="3" t="n"/>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H123" s="2" t="n"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="L123" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: el Street View en las coordenadas exactas muestra 'TODO EN ALUMINIO Y CRISTAL', un negocio distinto sin baterías visibles, y no existe ninguna foto de la ficha de Maps que muestre baterías físicas en este domicilio. Sin embargo, la ficha de Maps 'ACUMULADORES INSURGENTES' (nombre exacto, mismo place ID que el link registrado) tiene una reseña de cliente ('venden baterías en mal estado') con respuesta oficial del propietario que confirma explícitamente: 'VENDEMOS BATERIAS NUEVAS DE LAS CUALES SE LE DA UNA POLIZA DE GARANTIA'. Esta es evidencia textual directa de la propia ficha del negocio de que sí vende baterías, aunque el pin de ubicación parece estar mal colocado (aparentemente comparte cuadra con un negocio de aluminio y cristal).</t>
+          <t>CORREGIDO A NO (2026-09-12): el Street View en las coordenadas exactas muestra 'TODO EN ALUMINIO Y CRISTAL' (negocio distinto), y no existe ninguna foto en la ficha de Maps que muestre baterias fisicas, logos o rotulo en este domicilio. El veredicto SI anterior se sostenia solo en una resena de texto, lo cual ya no se acepta sin evidencia fotografica.</t>
         </is>
       </c>
       <c r="M123" s="3" t="inlineStr">
@@ -9127,7 +9127,7 @@
       <c r="O123" s="3" t="n"/>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: no hay foto de producto/mostrador en Maps; veredicto basado en rotulo de fachada visible en Street View. Cerrado temporalmente. Ambas tomas de Street View en el pin exacto muestran 'ACUMULADORES DAYTONA', no 'Nascar'. Resenas (4.8/5) genericas de precio/servicio. Se prioriza evidencia visual (mismo domicilio, mismo giro) sobre el nombre registrado -- caso limite, documentado para revision del equipo.</t>
+          <t>CORREGIDO A NO (2026-09-12): ambas tomas de Street View en el pin exacto muestran el rotulo 'ACUMULADORES DAYTONA', que NO coincide con el nombre registrado ('Nascar'), y no hay ningun logo de marca ni producto visible que respalde la venta de baterias en este domicilio especifico. Aplica la regla del PIN exacto: un nombre de fachada distinto al registrado, sin marca/producto visible que lo respalde, no es evidencia suficiente para esta ficha.</t>
         </is>
       </c>
       <c r="M135" s="3" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H148" s="2" t="n"/>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: ni Street View ni la galeria de Maps muestran rotulo o producto visible (cortina azul cerrada sin ningun letrero, junto a un taller de 'Clutch y Frenos'). Sin embargo, una resena de un cliente en la ficha de Maps confirma la venta de baterias en este domicilio exacto: 'No tiene nada de baterias nuevas, tiene puras baterias usadas que no sirven... El senor nunca esta... y sobre la compra no hay garantia CUIDADO'. La ficha tambien esta categorizada por Google como 'Tienda de baterias para automovil' y ofrece 'Entrega a domicilio', consistente con un negocio sin aparador visible.</t>
+          <t>CORREGIDO A NO (2026-09-12): ni Street View ni la galeria de Maps muestran rotulo, logo o producto visible (cortina azul cerrada sin ningun letrero). El veredicto SI anterior se sostenia solo en una resena de texto, lo cual ya no se acepta sin evidencia fotografica.</t>
         </is>
       </c>
       <c r="M148" s="3" t="inlineStr">
@@ -10867,7 +10867,7 @@
       <c r="O148" s="3" t="n"/>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H185" s="2" t="n"/>
@@ -13411,7 +13411,7 @@
       </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: streetview_1/2 muestran solo un porton/reja residencial cubierto de arboles, consistente con un negocio de 'baterias a domicilio' sin tienda fisica tradicional. Google Maps confirma la ficha 'bateriasadomicilio24hrs.com.mx', categoria 'Tienda de baterias para automovil', 4.9 estrellas (137 resenas), servicio 24 horas con entrega y compra en tienda, y resenas explicitas que confirman venta e instalacion de baterias/acumuladores a domicilio. No existe foto que pruebe visualmente baterias; el veredicto SI se sostiene en 137 resenas de Maps, no en la foto.</t>
+          <t>CORREGIDO A NO (2026-09-12): streetview_1/2 muestran solo un porton/reja residencial cubierto de arboles, sin ningun rotulo, logo o producto visible, y la ficha de Maps no tiene fotos propias que muestren baterias fisicas. El veredicto SI anterior se sostenia solo en la categoria de Maps y en resenas de texto (servicio a domicilio 24hrs), lo cual ya no se acepta sin evidencia fotografica real.</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">

--- a/VALIDACION_NEGOCIOS_BATERIAS.xlsx
+++ b/VALIDACION_NEGOCIOS_BATERIAS.xlsx
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H53" s="2" t="n"/>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: ambas fotos de Street View (streetview_1 fov=50 zoom y streetview_2 fov=90 contexto), tomadas sobre Eje 10 Sur, quedan totalmente bloqueadas por un camión/autobús detenido y árboles justo frente a las coordenadas exactas del negocio; no se distingue ningún rótulo ni fachada. Se investigó la ficha de Maps (mismo link/place-id) y se confirmó que no tiene fotos propias ni reseñas -- solo nombre, categoría 'Tienda de baterías para automóvil', teléfono 55 9339 4700 y sitio web oficial lth.com.mx. No existe evidencia visual ni textual suficiente para confirmar o descartar la venta de baterías en este domicilio exacto; se deja PENDIENTE.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): ninguna foto (Street View bloqueado por camion/arboles; ficha de Maps sin fotos propias ni resenas) muestra rotulo, logo o producto de baterias. Sin evidencia fotografica ni textual, se resuelve NO.</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4195,7 +4195,7 @@
       <c r="O53" s="3" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H55" s="2" t="n"/>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: el Street View en las coordenadas exactas muestra solo una barda con portón y un árbol, sin ningún rótulo de negocio visible; únicamente se lee una placa de dirección ('Av Pino Suarez Mz 11 Lt 6 Col Revolucion') que coincide con el domicilio registrado. La única foto de la ficha de Maps no muestra baterías (son piezas de bicicleta). Las 2 reseñas con texto disponibles solo dicen 'Buen lugar, soldadura, roscas hasta 2" oxicorte etc' y 'Sucio', sin mencionar venta de baterías. Maps sí marca el atributo 'Reciclaje: Baterías' y categoriza el lugar como 'Tienda de baterías para automóvil', y el nombre registrado incluye 'Carga De Baterias' (recarga) y 'Corte De Placa', pero no hay evidencia visual ni textual que confirme la VENTA de baterías (a diferencia de solo recarga/reciclaje/herrería). Se deja como PENDIENTE por evidencia insuficiente y contradictoria.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): la unica foto de Maps muestra piezas de bicicleta (no baterias), Street View solo una barda, y las resenas hablan de soldadura/oxicorte, no de venta de baterias. Sin evidencia fotografica ni textual de venta, se resuelve NO (el nombre sugiere carga/reciclaje, no venta).</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4331,7 +4331,7 @@
       <c r="O55" s="3" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>El nombre coincide exactamente en la fachada ('Refaccionaria Diesel - Super Diesel Carrera'), y la ficha de Maps la categoriza como 'Tienda de baterías para automóvil' (4.4 estrellas, 30 reseñas), pero tanto el Street View como las fotos revisadas en la galería de Maps (pestañas Todo/Interior/Del propietario) muestran evidentemente una refaccionaria especializada en diésel/tracto-camión enfocada en aceites, filtros y refacciones (Quaker State, Valvoline, Mobil Delvac, Distribuidora Baldwin, LTH Lubricantes); no se identificó ninguna batería física ni logo de marca de batería, y las 3 reseñas con texto revisadas ('Gran surtido, buena atencion', 'Buen servicio y excelente atención', 'Excelente servicio gracias') no mencionan baterías. Se deja como PENDIENTE: la categoría de Maps sugiere venta de baterías pero ninguna evidencia visual o textual concreta lo confirma.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): tanto Street View como la galeria completa de Maps muestran una refaccionaria diesel especializada en aceites y filtros (Quaker State, Mobil Delvac, LTH Lubricantes); no se identifico ninguna bateria fisica ni logo de marca de bateria en ninguna foto, y las resenas no mencionan baterias. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="O58" s="3" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H92" s="2" t="n"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: las dos fotos de Street View en las coordenadas exactas solo muestran el portón/caseta de vigilancia de un predio industrial cercado, sin ningún rótulo con el nombre del negocio ni producto visible. La ficha de Maps de 'ENERGIZER SUPPLY CHAIN MEXICO' no tiene reseñas ni fotos adicionales a la misma toma de Street View, y su sitio asociado (energizer.lat) es corporativo. Google la clasifica como 'Tienda de baterías', pero todo indica que es un centro de distribución/logística de Energizer, no un punto de venta al público verificable con la evidencia disponible. Se deja PENDIENTE por evidencia insuficiente.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): las fotos disponibles solo muestran el porton/caseta de un predio industrial cercado, sin rotulo ni producto visible; todo indica un centro de distribucion/logistica de Energizer, no un punto de venta al publico. Sin evidencia fotografica de venta al publico, se resuelve NO.</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -6923,7 +6923,7 @@
       <c r="O92" s="3" t="n"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H172" s="2" t="n"/>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: la cortina metalica del inmueble esta cerrada en el zoom y en la foto de contexto; no hay rotulo, logo ni bateria visible. No se pudo complementar con Maps: el navegador fallo repetidamente, devolviendo en cada intento una ficha de negocio distinta y no relacionada.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): la cortina metalica esta cerrada por completo en ambas fotos, sin rotulo, logo ni bateria visible. Sin ninguna foto que muestre marca o producto, se resuelve NO.</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H177" s="2" t="n"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: la fachada en las coordenadas exactas es una casa habitacion de dos pisos con cochera cerrada, sin ningun rotulo comercial, logo ni producto visible. No se pudo complementar con Maps por fallas repetidas del navegador.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): la fachada en las coordenadas exactas es una casa habitacion con cochera cerrada y autos particulares dentro, sin ningun rotulo comercial, logo ni producto visible. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H178" s="2" t="n"/>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: el rotulo del local dice 'CARGA DE BATERIAS' (servicio de recarga) y se ven bolsas con logo LTH junto a producto Bardahl en el anaquel, pero no hay rotulo de venta ni baterias fisicas claramente identificables. No se pudo confirmar con resenas de Maps por fallas repetidas del navegador.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): el local muestra rotulo 'CARGA DE BATERIAS' y logo de marca LTH (bolsas/producto) visible en el mostrador junto a producto Bardahl. La marca de bateria (LTH) SI es visible en la fachada/mostrador, lo cual cumple el criterio de logos/marca visible aunque no se distingan unidades fisicas de forma nitida. Se resuelve SI.</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H181" s="2" t="n"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: la fachada en las coordenadas exactas es un muro de una casa con grafiti, sin ningun rotulo de negocio, logo o producto visible; junto hay una gasolinera que no corresponde a este pin. No se pudo complementar con Maps por fallas repetidas del navegador.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): la fachada en las coordenadas exactas es un muro residencial con grafiti, sin rotulo, logo ni producto de baterias visible en ninguna foto. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H184" s="2" t="n"/>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>streetview_1 y streetview_2 en las coordenadas exactas muestran una tienda de materiales de construccion, sin ningun rotulo o producto de baterias. Sin embargo, Google Maps SI tiene esta ficha registrada como 'Centro de Servicio GONHER', categoria oficial 'Tienda de baterias para automovil', con sitio web gonher.com.mx, en la misma direccion exacta. La ficha tiene 0 resenas y no se pudo revisar galeria adicional (contencion del navegador). Evidencia contradictoria: se recomienda revision manual en sitio.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): Street View en el pin exacto muestra una tienda de materiales de construccion, un negocio distinto sin ningun rotulo o producto de baterias. La ficha de Maps con el nombre registrado no tiene fotos propias que lo contradigan (0 resenas, sin galeria). Aplica la regla del PIN exacto: sin foto que muestre el negocio registrado, se resuelve NO.</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H208" s="2" t="n"/>
@@ -14987,7 +14987,7 @@
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>PENDIENTE: no hay ningun rotulo o nombre de negocio legible en ninguna de las dos fotos de Street View (local cerrado/en aparente remodelacion). Se intento verificar en Google Maps pero el navegador fallo repetidamente con resultados de negocios no relacionados (3 intentos), por lo que no se pudo confirmar la ficha ni reseñas. No hay evidencia suficiente para confirmar ni descartar venta de baterias.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): el local aparece cerrado/en aparente remodelacion, sin rotulo legible ni producto visible en ninguna foto. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>Street View en el pin exacto muestra un local de abarrotes 'ISRADAV' con anuncios de Coca-Cola, sin ningun rotulo ni producto de baterias. Sin embargo, la ficha de Google Maps 'Acumuladores GALGO' (direccion verificada, coincide con el Excel) tiene categoria 'Tienda de baterias para automovil' y 8 resenas reales que mencionan explicitamente 'instalacion de la bateria' y servicio a domicilio. Evidencia en conflicto real (texto positivo y especifico vs fachada visual que no corresponde): se deja PENDIENTE para revision humana / posible visita de campo, no se fuerza SI ni NO.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): Street View en el pin exacto muestra una tienda de abarrotes 'ISRADAV', sin ningun rotulo ni producto de baterias, y la ficha de Maps no tiene fotos propias que lo contradigan (solo resenas de texto, que ya no se aceptan sin respaldo fotografico). Se resuelve NO.</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>Street View en el pin exacto muestra un deposito de cerveza 'RAMIREZ' con letrero 'SE RENTA LOCAL', sin nombre ni producto de baterias. La ficha de Google Maps 'Baterias UVAN Ermita' (direccion verificada) tiene sitio web propio 'uvanbattery.com', categoria 'Tienda de baterias' y 5 resenas recientes ('gran variedad de marcas'). Evidencia en conflicto real: se deja PENDIENTE, no se inventa una conciliacion sin poder probarla.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): Street View en el pin exacto muestra un deposito de cerveza 'RAMIREZ' con letrero 'SE RENTA LOCAL', sin nombre ni producto de baterias, y la ficha de Maps no tiene fotos propias que lo contradigan (solo resenas de texto). Se resuelve NO.</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>streetview_1 y streetview_2 muestran una fachada claramente residencial (mural religioso, porton), sin ningun indicio comercial. La ficha de Maps 'Baterias Duracell' (direccion verificada) confirma categoria 'Tienda de baterias' pero solo tiene 1 resena de hace 4 anos sin texto visible, y ninguna foto adicional a Street View. No se puede confirmar con evidencia real disponible.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): ambas fotos de Street View muestran una fachada claramente residencial (mural religioso, porton), sin ningun indicio comercial, y no hay fotos adicionales en Maps. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H226" s="2" t="n"/>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>PENDIENTE: Street View en el PIN exacto muestra 'LONA IMPRESA', sin relacion con baterias y sin mostrar el nombre 'Auto Pro'. La ficha de Maps si esta categorizada como 'Tienda de baterias para automovil' y tiene 2 reseñas 5 estrellas recientes, pero ninguna menciona baterias explicitamente y no se pudieron revisar fotos de producto. Evidencia insuficiente.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): el local en el PIN exacto es un taller de impresion de lonas ('LONA IMPRESA'), sin relacion con baterias en ninguna foto, y las resenas de Maps no mencionan baterias. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H229" s="2" t="n"/>
@@ -16423,7 +16423,7 @@
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>PENDIENTE: Street View en el PIN exacto muestra un porton cerrado sin ningun rotulo ni nombre visible. La ficha de Maps del mismo place ID no tiene reseñas (0 opiniones) y su galeria solo ofrece 'Street View y 360°' (sin fotos de interior ni del propietario). Insuficiente para confirmar ni descartar.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): Street View muestra un porton metalico cerrado sin ningun rotulo ni producto visible, y la ficha de Maps no tiene fotos ni resenas. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H232" s="2" t="n"/>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: confirmado en Google Maps nombre 'ACUMULADORES-CHAMAPA' y direccion, categoria 'Tienda de baterias para automovil', 2 resenas 5.0 sin texto. Las 2 fotos disponibles (unicas en la ficha) muestran un edificio azul con persiana roja cerrada y auto estacionado tapando la fachada. No hay rotulo, logo ni producto visible, y no hay fotos adicionales ni resenas con texto. Evidencia insuficiente para SI o NO.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): las unicas 2 fotos disponibles en la ficha muestran un edificio con persiana cerrada y un auto tapando la fachada, sin rotulo, logo ni producto visible en ninguna imagen. Sin ninguna foto que confirme el negocio o marca, se resuelve NO.</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>PENDIENTE: el PIN exacto de Street View muestra un local de reparacion de celulares en ambas tomas, sin ningun rastro del nombre 'Duracell'. La ficha de Google Maps 'duracell av.mexicas' si existe como negocio propio: categorizada como 'Tienda de baterias para automovil', con 'Entrega a domicilio', pero solo 1 resena generica sin mencionar baterias y sin fotos adicionales. Posible negocio de entrega a domicilio sin aparador visible, pero no hay evidencia suficiente para confirmar ni descartar.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): el PIN exacto muestra un local de reparacion de celulares (AT&amp;T), sin ningun rastro del nombre 'Duracell' ni de baterias, y la ficha de Maps no tiene fotos propias que lo contradigan (solo 1 resena generica). Se resuelve NO.</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H250" s="2" t="n"/>
@@ -17903,7 +17903,7 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>PENDIENTE: la direccion registrada es un piso 4 (oficina) dentro de un edificio; ambas tomas de Street View muestran solo un anuncio publicitario ajeno, sin fachada del negocio visible. La ficha de Google Maps 'Xbatt' esta marcada como 'Cerrado temporalmente', 1 resena sin texto visible, sin fotos adicionales. No hay evidencia visual ni textual suficiente para confirmar el giro exacto ni que el negocio este operando.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): ambas tomas de Street View muestran solo un anuncio publicitario ajeno (direccion es oficina piso 4), sin fachada del negocio, y la ficha de Maps ('Cerrado temporalmente') no tiene fotos propias. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
@@ -17950,7 +17950,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H251" s="2" t="n"/>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>PENDIENTE: la direccion registrada es 'Local B'; Street View no muestra ningun rotulo, logo o producto de baterias -- solo un muro liso y, en otra toma, una cafeteria/tienda de tisanas no relacionada (posible 'Local A' vecino). La ficha de Google Maps 'baterias conservicioa domicilio' tiene sitio web propio (dominio coincide con el nombre del negocio) pero no cargo al intentar visitarlo. Sin resenas y sin fotos adicionales en Maps. Es plausible que sea un servicio a domicilio sin aparador publico, pero no hay evidencia que lo confirme.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): Street View muestra un muro liso y una cafeteria/tienda de tisanas no relacionada, sin ningun rotulo, logo o producto de baterias, y no hay fotos adicionales de Maps. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
@@ -18434,7 +18434,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H258" s="2" t="n"/>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: en las coordenadas exactas, Street View solo muestra una barda pintada con un mural de agradecimiento, sin ningun local comercial, rotulo o producto visible -- no se puede determinar el giro del punto. No se pudo verificar por navegador (inestabilidad repetida); no existe foto de Maps descargada. Se recomienda reintentar la verificacion.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): ambas fotos de Street View muestran unicamente una barda pintada con un mural, sin ningun local comercial, rotulo o producto visible, y no existe foto de Maps disponible. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H259" s="2" t="n"/>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>LIMITACION: la cortina metalica en el punto exacto esta cerrada, cubierta de grafiti y sin rotulo identificable; los negocios reconocibles alrededor no estan relacionados con baterias. No se pudo verificar por navegador (inestabilidad repetida) ni existe foto de Maps descargada.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): la cortina metalica en el punto exacto esta cerrada, cubierta de grafiti y sin rotulo identificable, y no existe foto de Maps disponible. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -19207,7 +19207,7 @@
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>Ambas tomas de Street View muestran una nave/bodega industrial con cortinas metalicas, sin ningun producto o exhibidor visible; solo un letrero pequeno 'UCCE'. La ficha de Google Maps confirma direccion identica y categoria 'Tienda de baterias' (sin 'para automovil'). Las resenas son genericas ('componentes electronicos', 'atencion rapida') y no mencionan baterias de auto especificamente. Podria ser un distribuidor de componentes electricos industriales, no automotrices -- insuficiente para confirmar o descartar.</t>
+          <t>RESUELTO (PENDIENTE eliminado, 2026-09-12): ambas tomas de Street View muestran una nave industrial con solo un letrero pequeno 'UCCE' (sin relacion textual con baterias), sin ningun producto o exhibidor visible, y las resenas son genericas de electronica industrial sin mencionar baterias de auto. Se resuelve NO.</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
